--- a/穂果記録.xlsx
+++ b/穂果記録.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2cfbf2d641072903/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="65" documentId="13_ncr:1_{10E40B7B-DF6A-48E8-839B-5B2C8E703596}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{063637B2-971B-4B69-BCFA-63CF47656677}"/>
+  <xr:revisionPtr revIDLastSave="66" documentId="13_ncr:1_{10E40B7B-DF6A-48E8-839B-5B2C8E703596}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C556A254-4D65-43A1-8621-2915437DD145}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="22">
   <si>
     <t>日付</t>
     <rPh sb="0" eb="2">
@@ -109,20 +109,6 @@
     <t>鈴鹿</t>
     <rPh sb="0" eb="2">
       <t>スズカ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>距離 (m)</t>
-    <rPh sb="0" eb="2">
-      <t>キョリ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>タイム (秒)</t>
-    <rPh sb="5" eb="6">
-      <t>ビョウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -637,16 +623,16 @@
         <v>7</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="I1" s="1" t="s">
-        <v>15</v>
-      </c>
       <c r="J1" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:12">
@@ -654,7 +640,7 @@
         <v>45823</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C2" s="1">
         <v>50</v>
@@ -693,7 +679,7 @@
         <v>45956</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C3" s="1">
         <v>50</v>
@@ -717,7 +703,7 @@
         <v>46033</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C4" s="1">
         <v>50</v>
@@ -737,7 +723,7 @@
         <v>46075</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C5" s="1">
         <v>50</v>
@@ -760,7 +746,7 @@
         <v>46130</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C6" s="1">
         <v>50</v>
@@ -819,34 +805,34 @@
   <sheetData>
     <row r="1" spans="1:16">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>7</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="I1" s="1" t="s">
-        <v>15</v>
-      </c>
       <c r="J1" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:16">
@@ -854,7 +840,7 @@
         <v>45788</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C2" s="1">
         <v>50</v>
@@ -893,7 +879,7 @@
         <v>45815</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C3" s="1">
         <v>50</v>
@@ -917,7 +903,7 @@
         <v>45823</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C4" s="1">
         <v>50</v>
@@ -937,7 +923,7 @@
         <v>45844</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C5" s="1">
         <v>50</v>
@@ -960,7 +946,7 @@
         <v>45956</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C6" s="1">
         <v>50</v>
@@ -983,7 +969,7 @@
         <v>45984</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C7" s="1">
         <v>50</v>
@@ -1003,7 +989,7 @@
         <v>46075</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C8" s="1">
         <v>50</v>
@@ -1023,7 +1009,7 @@
         <v>46130</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C9" s="1">
         <v>50</v>
@@ -1071,7 +1057,7 @@
   <sheetData>
     <row r="1" spans="1:18">
       <c r="A1" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>3</v>
@@ -1089,28 +1075,28 @@
         <v>7</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="I1" s="1" t="s">
-        <v>15</v>
-      </c>
       <c r="J1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="M1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="K1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>15</v>
-      </c>
       <c r="N1" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="2" spans="1:18">
@@ -1118,7 +1104,7 @@
         <v>45788</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C2" s="1">
         <v>50</v>
@@ -1173,7 +1159,7 @@
         <v>45815</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C3" s="1">
         <v>50</v>
@@ -1197,7 +1183,7 @@
         <v>45844</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C4" s="1">
         <v>50</v>
@@ -1217,7 +1203,7 @@
         <v>45942</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C5" s="1">
         <v>50</v>
@@ -1240,7 +1226,7 @@
         <v>45955</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C6" s="1">
         <v>50</v>
@@ -1263,7 +1249,7 @@
         <v>45984</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C7" s="1">
         <v>50</v>
@@ -1283,7 +1269,7 @@
         <v>45984</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C8" s="1">
         <v>100</v>
@@ -1303,7 +1289,7 @@
         <v>46033</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C9" s="1">
         <v>50</v>
@@ -1323,7 +1309,7 @@
         <v>46053</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C10" s="1">
         <v>50</v>
@@ -1343,7 +1329,7 @@
         <v>46075</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C11" s="1">
         <v>50</v>
@@ -1363,7 +1349,7 @@
         <v>46130</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C12" s="1">
         <v>50</v>
@@ -1417,7 +1403,7 @@
   <sheetData>
     <row r="1" spans="1:17">
       <c r="A1" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>3</v>
@@ -1435,16 +1421,16 @@
         <v>7</v>
       </c>
       <c r="G1" s="10" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H1" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="J1" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="J1" s="10" t="s">
-        <v>15</v>
-      </c>
       <c r="K1" s="10" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:17">
@@ -1452,7 +1438,7 @@
         <v>45788</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C2" s="1">
         <v>50</v>
@@ -1492,7 +1478,7 @@
         <v>45816</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C3" s="1">
         <v>50</v>
@@ -1516,7 +1502,7 @@
         <v>45823</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C4" s="1">
         <v>50</v>
@@ -1536,7 +1522,7 @@
         <v>45844</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C5" s="1">
         <v>50</v>
@@ -1559,7 +1545,7 @@
         <v>45942</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C6" s="1">
         <v>50</v>
@@ -1582,7 +1568,7 @@
         <v>45955</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C7" s="1">
         <v>50</v>
@@ -1602,7 +1588,7 @@
         <v>46033</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C8" s="1">
         <v>50</v>
@@ -1622,7 +1608,7 @@
         <v>46053</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C9" s="1">
         <v>50</v>
@@ -1642,7 +1628,7 @@
         <v>46074</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C10" s="1">
         <v>50</v>
@@ -1662,7 +1648,7 @@
         <v>46130</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C11" s="1">
         <v>50</v>
@@ -1734,16 +1720,16 @@
         <v>7</v>
       </c>
       <c r="I1" s="7" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J1" s="7" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="K1" s="7" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="O1" s="7" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:15">
@@ -1751,7 +1737,7 @@
         <v>45710</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C2" s="1">
         <v>200</v>
@@ -1760,7 +1746,7 @@
         <v>6</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F2" s="1">
         <v>283.08999999999997</v>
@@ -1805,7 +1791,7 @@
         <v>45808</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C3" s="1">
         <v>200</v>
@@ -1857,7 +1843,7 @@
         <v>45899</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C4" s="1">
         <v>200</v>
@@ -1906,7 +1892,7 @@
         <v>45991</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C5" s="1">
         <v>200</v>
@@ -1957,7 +1943,7 @@
         <v>46081</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C6" s="1">
         <v>200</v>
@@ -2051,13 +2037,13 @@
         <v>7</v>
       </c>
       <c r="K1" s="7" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="L1" s="7" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="M1" s="7" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:16">
@@ -2065,7 +2051,7 @@
         <v>45710</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C2" s="1">
         <v>200</v>
@@ -2118,7 +2104,7 @@
         <v>45808</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C3" s="1">
         <v>200</v>
@@ -2168,7 +2154,7 @@
         <v>45899</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C4" s="1">
         <v>200</v>
@@ -2215,7 +2201,7 @@
         <v>45991</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C5" s="1">
         <v>200</v>
@@ -2264,7 +2250,7 @@
         <v>46081</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C6" s="1">
         <v>200</v>

--- a/穂果記録.xlsx
+++ b/穂果記録.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2cfbf2d641072903/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="66" documentId="13_ncr:1_{10E40B7B-DF6A-48E8-839B-5B2C8E703596}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C556A254-4D65-43A1-8621-2915437DD145}"/>
+  <xr:revisionPtr revIDLastSave="67" documentId="13_ncr:1_{10E40B7B-DF6A-48E8-839B-5B2C8E703596}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2875EBF8-7800-4943-916C-CBD2634F5426}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5808" yWindow="996" windowWidth="13716" windowHeight="9960" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="バッタ" sheetId="1" r:id="rId1"/>
@@ -1654,7 +1654,7 @@
         <v>50</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E11" s="1">
         <v>40.28</v>

--- a/穂果記録.xlsx
+++ b/穂果記録.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2cfbf2d641072903/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2cfbf2d641072903/Desktop/スイミングダッシュボード/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="67" documentId="13_ncr:1_{10E40B7B-DF6A-48E8-839B-5B2C8E703596}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2875EBF8-7800-4943-916C-CBD2634F5426}"/>
+  <xr:revisionPtr revIDLastSave="85" documentId="13_ncr:1_{10E40B7B-DF6A-48E8-839B-5B2C8E703596}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E8B12E55-F9E8-4E73-A9C0-40845B2EA64A}"/>
   <bookViews>
-    <workbookView xWindow="5808" yWindow="996" windowWidth="13716" windowHeight="9960" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="バッタ" sheetId="1" r:id="rId1"/>
@@ -201,10 +201,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="176" formatCode="yyyy&quot;年&quot;m&quot;月&quot;d&quot;日&quot;;@"/>
     <numFmt numFmtId="177" formatCode="0.00_ "/>
     <numFmt numFmtId="178" formatCode="0.00_);[Red]\(0.00\)"/>
+    <numFmt numFmtId="187" formatCode="mm:ss.00"/>
   </numFmts>
   <fonts count="4">
     <font>
@@ -278,7 +279,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -310,6 +311,9 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="187" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -325,10 +329,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1132,7 +1132,7 @@
       </c>
       <c r="J2" s="5">
         <f>INDEX(A:A, MATCH(_xlfn.MINIFS(E:E, D:D, "長水路"), E:E, 0))</f>
-        <v>46075</v>
+        <v>45984</v>
       </c>
       <c r="K2" s="1">
         <f>_xlfn.MINIFS(E:E, C:C, 100, D:D, "短水路")</f>
@@ -1144,11 +1144,11 @@
       </c>
       <c r="M2" s="1">
         <f>_xlfn.MINIFS(E:E, C:C, 100, D:D, "長水路")</f>
-        <v>101.11</v>
+        <v>1.1702546296296296E-3</v>
       </c>
       <c r="N2" s="5">
         <f>INDEX(A:A, MATCH(_xlfn.MINIFS(E:E, D:D, "長水路"), E:E, 0))</f>
-        <v>46075</v>
+        <v>45984</v>
       </c>
       <c r="R2" s="1" t="s">
         <v>5</v>
@@ -1277,8 +1277,8 @@
       <c r="D8" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="E8" s="1">
-        <v>101.11</v>
+      <c r="E8" s="11">
+        <v>1.1702546296296296E-3</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>9</v>

--- a/穂果記録.xlsx
+++ b/穂果記録.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2cfbf2d641072903/Desktop/スイミングダッシュボード/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shimo\OneDrive\Desktop\スイミングダッシュボード\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="85" documentId="13_ncr:1_{10E40B7B-DF6A-48E8-839B-5B2C8E703596}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E8B12E55-F9E8-4E73-A9C0-40845B2EA64A}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBE8A225-3594-412E-B9A9-0CE6028D707E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="バッタ" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,6 @@
     <sheet name="ブレ" sheetId="3" r:id="rId3"/>
     <sheet name="フリー" sheetId="4" r:id="rId4"/>
     <sheet name="メドレー" sheetId="5" r:id="rId5"/>
-    <sheet name="メドレー (2)" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="25">
   <si>
     <t>日付</t>
     <rPh sb="0" eb="2">
@@ -172,20 +171,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>200m ベストタイム(短水路)</t>
-    <rPh sb="12" eb="15">
-      <t>タンスイロ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>200m 更新日</t>
-    <rPh sb="5" eb="8">
-      <t>コウシンビ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>4'39"09</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -194,6 +179,26 @@
     <rPh sb="0" eb="1">
       <t>ショウ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>D</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>4'02"71</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>3'37"53</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>3'21"34</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>3'14"47</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -204,10 +209,10 @@
   <numFmts count="4">
     <numFmt numFmtId="176" formatCode="yyyy&quot;年&quot;m&quot;月&quot;d&quot;日&quot;;@"/>
     <numFmt numFmtId="177" formatCode="0.00_ "/>
-    <numFmt numFmtId="178" formatCode="0.00_);[Red]\(0.00\)"/>
-    <numFmt numFmtId="187" formatCode="mm:ss.00"/>
+    <numFmt numFmtId="178" formatCode="mm:ss.00"/>
+    <numFmt numFmtId="183" formatCode="yyyy/m/d;@"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -229,14 +234,6 @@
       <family val="3"/>
       <charset val="128"/>
     </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Meiryo UI"/>
-      <family val="3"/>
-      <charset val="128"/>
-    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -252,7 +249,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -260,26 +257,11 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -296,22 +278,13 @@
     <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="178" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="187" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="183" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -636,7 +609,7 @@
       </c>
     </row>
     <row r="2" spans="1:12">
-      <c r="A2" s="2">
+      <c r="A2" s="5">
         <v>45823</v>
       </c>
       <c r="B2" s="1" t="s">
@@ -675,7 +648,7 @@
       </c>
     </row>
     <row r="3" spans="1:12">
-      <c r="A3" s="2">
+      <c r="A3" s="5">
         <v>45956</v>
       </c>
       <c r="B3" s="1" t="s">
@@ -699,7 +672,7 @@
       </c>
     </row>
     <row r="4" spans="1:12">
-      <c r="A4" s="2">
+      <c r="A4" s="5">
         <v>46033</v>
       </c>
       <c r="B4" s="1" t="s">
@@ -719,7 +692,7 @@
       </c>
     </row>
     <row r="5" spans="1:12">
-      <c r="A5" s="2">
+      <c r="A5" s="5">
         <v>46075</v>
       </c>
       <c r="B5" s="1" t="s">
@@ -742,11 +715,11 @@
       </c>
     </row>
     <row r="6" spans="1:12">
-      <c r="A6" s="2">
+      <c r="A6" s="5">
         <v>46130</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C6" s="1">
         <v>50</v>
@@ -836,7 +809,7 @@
       </c>
     </row>
     <row r="2" spans="1:16">
-      <c r="A2" s="2">
+      <c r="A2" s="5">
         <v>45788</v>
       </c>
       <c r="B2" s="1" t="s">
@@ -875,7 +848,7 @@
       </c>
     </row>
     <row r="3" spans="1:16">
-      <c r="A3" s="2">
+      <c r="A3" s="5">
         <v>45815</v>
       </c>
       <c r="B3" s="1" t="s">
@@ -899,7 +872,7 @@
       </c>
     </row>
     <row r="4" spans="1:16">
-      <c r="A4" s="2">
+      <c r="A4" s="5">
         <v>45823</v>
       </c>
       <c r="B4" s="1" t="s">
@@ -919,7 +892,7 @@
       </c>
     </row>
     <row r="5" spans="1:16">
-      <c r="A5" s="2">
+      <c r="A5" s="5">
         <v>45844</v>
       </c>
       <c r="B5" s="1" t="s">
@@ -942,7 +915,7 @@
       </c>
     </row>
     <row r="6" spans="1:16">
-      <c r="A6" s="2">
+      <c r="A6" s="5">
         <v>45956</v>
       </c>
       <c r="B6" s="1" t="s">
@@ -965,7 +938,7 @@
       </c>
     </row>
     <row r="7" spans="1:16">
-      <c r="A7" s="2">
+      <c r="A7" s="5">
         <v>45984</v>
       </c>
       <c r="B7" s="1" t="s">
@@ -985,7 +958,7 @@
       </c>
     </row>
     <row r="8" spans="1:16">
-      <c r="A8" s="2">
+      <c r="A8" s="5">
         <v>46075</v>
       </c>
       <c r="B8" s="1" t="s">
@@ -1005,11 +978,11 @@
       </c>
     </row>
     <row r="9" spans="1:16">
-      <c r="A9" s="2">
+      <c r="A9" s="5">
         <v>46130</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C9" s="1">
         <v>50</v>
@@ -1046,7 +1019,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5195340D-D996-47EB-BD33-2E94CF2465C1}">
-  <dimension ref="A1:R12"/>
+  <dimension ref="A1:R17"/>
   <sheetFormatPr defaultColWidth="14.8984375" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="15.796875" style="2" bestFit="1" customWidth="1"/>
@@ -1100,7 +1073,7 @@
       </c>
     </row>
     <row r="2" spans="1:18">
-      <c r="A2" s="2">
+      <c r="A2" s="5">
         <v>45788</v>
       </c>
       <c r="B2" s="1" t="s">
@@ -1155,7 +1128,7 @@
       </c>
     </row>
     <row r="3" spans="1:18">
-      <c r="A3" s="2">
+      <c r="A3" s="5">
         <v>45815</v>
       </c>
       <c r="B3" s="1" t="s">
@@ -1179,7 +1152,7 @@
       </c>
     </row>
     <row r="4" spans="1:18">
-      <c r="A4" s="2">
+      <c r="A4" s="5">
         <v>45844</v>
       </c>
       <c r="B4" s="1" t="s">
@@ -1199,7 +1172,7 @@
       </c>
     </row>
     <row r="5" spans="1:18">
-      <c r="A5" s="2">
+      <c r="A5" s="5">
         <v>45942</v>
       </c>
       <c r="B5" s="1" t="s">
@@ -1222,7 +1195,7 @@
       </c>
     </row>
     <row r="6" spans="1:18">
-      <c r="A6" s="2">
+      <c r="A6" s="5">
         <v>45955</v>
       </c>
       <c r="B6" s="1" t="s">
@@ -1245,7 +1218,7 @@
       </c>
     </row>
     <row r="7" spans="1:18">
-      <c r="A7" s="2">
+      <c r="A7" s="5">
         <v>45984</v>
       </c>
       <c r="B7" s="1" t="s">
@@ -1265,7 +1238,7 @@
       </c>
     </row>
     <row r="8" spans="1:18">
-      <c r="A8" s="2">
+      <c r="A8" s="5">
         <v>45984</v>
       </c>
       <c r="B8" s="1" t="s">
@@ -1277,7 +1250,7 @@
       <c r="D8" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="E8" s="11">
+      <c r="E8" s="7">
         <v>1.1702546296296296E-3</v>
       </c>
       <c r="F8" s="1" t="s">
@@ -1285,7 +1258,7 @@
       </c>
     </row>
     <row r="9" spans="1:18">
-      <c r="A9" s="2">
+      <c r="A9" s="5">
         <v>46033</v>
       </c>
       <c r="B9" s="1" t="s">
@@ -1305,7 +1278,7 @@
       </c>
     </row>
     <row r="10" spans="1:18">
-      <c r="A10" s="2">
+      <c r="A10" s="5">
         <v>46053</v>
       </c>
       <c r="B10" s="1" t="s">
@@ -1325,7 +1298,7 @@
       </c>
     </row>
     <row r="11" spans="1:18">
-      <c r="A11" s="2">
+      <c r="A11" s="5">
         <v>46075</v>
       </c>
       <c r="B11" s="1" t="s">
@@ -1345,11 +1318,11 @@
       </c>
     </row>
     <row r="12" spans="1:18">
-      <c r="A12" s="2">
+      <c r="A12" s="5">
         <v>46130</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C12" s="1">
         <v>50</v>
@@ -1362,6 +1335,11 @@
       </c>
       <c r="F12" s="1" t="s">
         <v>8</v>
+      </c>
+    </row>
+    <row r="17" spans="8:8">
+      <c r="H17" s="1" t="s">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -1420,21 +1398,21 @@
       <c r="F1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="10" t="s">
+      <c r="G1" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="H1" s="10" t="s">
+      <c r="H1" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="J1" s="10" t="s">
+      <c r="J1" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="K1" s="10" t="s">
+      <c r="K1" s="6" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:17">
-      <c r="A2" s="2">
+      <c r="A2" s="5">
         <v>45788</v>
       </c>
       <c r="B2" s="1" t="s">
@@ -1474,7 +1452,7 @@
       </c>
     </row>
     <row r="3" spans="1:17">
-      <c r="A3" s="2">
+      <c r="A3" s="5">
         <v>45816</v>
       </c>
       <c r="B3" s="1" t="s">
@@ -1498,7 +1476,7 @@
       </c>
     </row>
     <row r="4" spans="1:17">
-      <c r="A4" s="2">
+      <c r="A4" s="5">
         <v>45823</v>
       </c>
       <c r="B4" s="1" t="s">
@@ -1518,7 +1496,7 @@
       </c>
     </row>
     <row r="5" spans="1:17">
-      <c r="A5" s="2">
+      <c r="A5" s="5">
         <v>45844</v>
       </c>
       <c r="B5" s="1" t="s">
@@ -1541,7 +1519,7 @@
       </c>
     </row>
     <row r="6" spans="1:17">
-      <c r="A6" s="2">
+      <c r="A6" s="5">
         <v>45942</v>
       </c>
       <c r="B6" s="1" t="s">
@@ -1564,7 +1542,7 @@
       </c>
     </row>
     <row r="7" spans="1:17">
-      <c r="A7" s="2">
+      <c r="A7" s="5">
         <v>45955</v>
       </c>
       <c r="B7" s="1" t="s">
@@ -1584,7 +1562,7 @@
       </c>
     </row>
     <row r="8" spans="1:17">
-      <c r="A8" s="2">
+      <c r="A8" s="5">
         <v>46033</v>
       </c>
       <c r="B8" s="1" t="s">
@@ -1604,7 +1582,7 @@
       </c>
     </row>
     <row r="9" spans="1:17">
-      <c r="A9" s="2">
+      <c r="A9" s="5">
         <v>46053</v>
       </c>
       <c r="B9" s="1" t="s">
@@ -1624,7 +1602,7 @@
       </c>
     </row>
     <row r="10" spans="1:17">
-      <c r="A10" s="2">
+      <c r="A10" s="5">
         <v>46074</v>
       </c>
       <c r="B10" s="1" t="s">
@@ -1644,11 +1622,11 @@
       </c>
     </row>
     <row r="11" spans="1:17">
-      <c r="A11" s="2">
+      <c r="A11" s="5">
         <v>46130</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C11" s="1">
         <v>50</v>
@@ -1685,22 +1663,14 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F93145A-20C7-4E83-AE6C-04CD541B3421}">
-  <dimension ref="A1:O8"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr defaultColWidth="14.8984375" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="15.796875" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="5" width="14.8984375" style="1"/>
-    <col min="6" max="6" width="14.8984375" style="6"/>
-    <col min="7" max="8" width="14.8984375" style="1"/>
-    <col min="9" max="9" width="23" style="1" customWidth="1"/>
-    <col min="10" max="10" width="14.8984375" style="5"/>
-    <col min="11" max="11" width="21.8984375" style="1" customWidth="1"/>
-    <col min="12" max="14" width="14.8984375" style="1"/>
-    <col min="15" max="15" width="23" style="1" customWidth="1"/>
-    <col min="16" max="16384" width="14.8984375" style="1"/>
+    <col min="2" max="16384" width="14.8984375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="15">
+    <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1716,24 +1686,12 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="J1" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="K1" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="O1" s="7" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15">
-      <c r="A2" s="2">
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="8">
         <v>45710</v>
       </c>
       <c r="B2" s="1" t="s">
@@ -1746,48 +1704,17 @@
         <v>6</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="F2" s="1">
-        <v>283.08999999999997</v>
-      </c>
-      <c r="G2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="H2" s="4">
-        <f>TIME(0, L2, M2)</f>
-        <v>3.2754629629629631E-3</v>
-      </c>
-      <c r="I2" s="8">
-        <f>_xlfn.MINIFS(F:F, C:C, 200, D:D, "短水路")</f>
-        <v>194.47</v>
-      </c>
-      <c r="J2" s="9">
-        <f>INDEX(A:A, MATCH(_xlfn.MINIFS(F:F, D:D, "短水路"), F:F, 0))</f>
-        <v>46081</v>
-      </c>
-      <c r="K2" s="8">
-        <f>_xlfn.MINIFS(F2:F2, C2:C2, 200, D2:D2, "短水路")</f>
-        <v>283.08999999999997</v>
-      </c>
-      <c r="L2" s="8">
-        <f>INT(K2/60)</f>
-        <v>4</v>
-      </c>
-      <c r="M2" s="8">
-        <f>MOD(K2,60)</f>
-        <v>43.089999999999975</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="O2" s="8">
-        <f>_xlfn.MINIFS(F:F, D:D, 200, E:E, "短水路")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15">
-      <c r="A3" s="2">
+      <c r="I2" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" s="8">
         <v>45808</v>
       </c>
       <c r="B3" s="1" t="s">
@@ -1799,47 +1726,18 @@
       <c r="D3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="4">
-        <f>H3</f>
-        <v>2.8009259259259259E-3</v>
-      </c>
-      <c r="F3" s="1">
-        <v>242.71</v>
-      </c>
-      <c r="G3" s="1" t="s">
+      <c r="E3" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="H3" s="4">
-        <f>TIME(0, L3, M3)</f>
-        <v>2.8009259259259259E-3</v>
-      </c>
-      <c r="I3" s="8">
-        <f>INT(I2/60)</f>
-        <v>3</v>
-      </c>
-      <c r="J3" s="9"/>
-      <c r="K3" s="8">
-        <f>_xlfn.MINIFS(F3:F3, C3:C3, 200, D3:D3, "短水路")</f>
-        <v>242.71</v>
-      </c>
-      <c r="L3" s="8">
-        <f t="shared" ref="L3:L6" si="0">INT(K3/60)</f>
-        <v>4</v>
-      </c>
-      <c r="M3" s="8">
-        <f t="shared" ref="M3:M5" si="1">MOD(K3,60)</f>
-        <v>2.710000000000008</v>
-      </c>
-      <c r="N3" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="O3" s="8">
-        <f>INT(O2/60)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15">
-      <c r="A4" s="2">
+      <c r="I3" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" s="8">
         <v>45899</v>
       </c>
       <c r="B4" s="1" t="s">
@@ -1851,44 +1749,15 @@
       <c r="D4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E4" s="4">
-        <f>H4</f>
-        <v>2.5115740740740741E-3</v>
-      </c>
-      <c r="F4" s="1">
-        <v>217.53</v>
-      </c>
-      <c r="G4" s="1" t="s">
+      <c r="E4" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="H4" s="4">
-        <f>TIME(0, L4, M4)</f>
-        <v>2.5115740740740741E-3</v>
-      </c>
-      <c r="I4" s="8">
-        <f>MOD(I2,60)</f>
-        <v>14.469999999999999</v>
-      </c>
-      <c r="J4" s="9"/>
-      <c r="K4" s="8">
-        <f>_xlfn.MINIFS(F4:F4, C4:C4, 200, D4:D4, "短水路")</f>
-        <v>217.53</v>
-      </c>
-      <c r="L4" s="8">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="M4" s="8">
-        <f t="shared" si="1"/>
-        <v>37.53</v>
-      </c>
-      <c r="O4" s="8">
-        <f>MOD(O2,60)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15">
-      <c r="A5" s="2">
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" s="8">
         <v>45991</v>
       </c>
       <c r="B5" s="1" t="s">
@@ -1900,46 +1769,18 @@
       <c r="D5" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E5" s="4">
-        <f>H5</f>
-        <v>2.3263888888888887E-3</v>
-      </c>
-      <c r="F5" s="1">
-        <v>201.34</v>
-      </c>
-      <c r="G5" s="1" t="s">
+      <c r="E5" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="F5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="H5" s="4">
-        <f>TIME(0, L5, M5)</f>
-        <v>2.3263888888888887E-3</v>
-      </c>
-      <c r="I5" s="4">
-        <f>TIME(0, I3, I4)</f>
-        <v>2.2453703703703702E-3</v>
-      </c>
-      <c r="K5" s="8">
-        <f>_xlfn.MINIFS(F5:F5, C5:C5, 200, D5:D5, "短水路")</f>
-        <v>201.34</v>
-      </c>
-      <c r="L5" s="8">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="M5" s="8">
-        <f t="shared" si="1"/>
-        <v>21.340000000000003</v>
-      </c>
-      <c r="N5" s="1" t="s">
+      <c r="I5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="O5" s="4">
-        <f>TIME(0, O3, O4)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15">
-      <c r="A6" s="2">
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" s="8">
         <v>46081</v>
       </c>
       <c r="B6" s="1" t="s">
@@ -1951,357 +1792,24 @@
       <c r="D6" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E6" s="4">
-        <f>H6</f>
-        <v>2.2453703703703702E-3</v>
-      </c>
-      <c r="F6" s="1">
-        <v>194.47</v>
-      </c>
-      <c r="G6" s="1" t="s">
+      <c r="E6" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F6" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="H6" s="4">
-        <f>TIME(0, L6, M6)</f>
-        <v>2.2453703703703702E-3</v>
-      </c>
-      <c r="K6" s="8">
-        <f>_xlfn.MINIFS(F6:F6, C6:C6, 200, D6:D6, "短水路")</f>
-        <v>194.47</v>
-      </c>
-      <c r="L6" s="8">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="M6" s="8">
-        <f t="shared" ref="M6" si="2">MOD(K6,60)</f>
-        <v>14.469999999999999</v>
-      </c>
-      <c r="N6" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15">
-      <c r="I8" s="4"/>
-      <c r="K8" s="4"/>
-      <c r="O8" s="4"/>
+      <c r="I6" s="1" t="s">
+        <v>9</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D181 E7:E181" xr:uid="{FCD6C6B0-9EE2-40C6-BADA-61DB1F834B29}">
-      <formula1>$N$2:$N$3</formula1>
+      <formula1>$I$2:$I$3</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:H20" xr:uid="{4F3B2A47-C23A-4C80-87FE-9C03E8B410ED}">
-      <formula1>$N$5:$N$6</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4928F6EC-4FFB-4765-A340-E5D844852EEC}">
-  <dimension ref="A1:P8"/>
-  <sheetFormatPr defaultColWidth="14.8984375" defaultRowHeight="14.4"/>
-  <cols>
-    <col min="1" max="1" width="15.796875" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="7" width="14.8984375" style="1"/>
-    <col min="8" max="8" width="14.8984375" style="6"/>
-    <col min="9" max="10" width="14.8984375" style="1"/>
-    <col min="11" max="11" width="23" style="1" customWidth="1"/>
-    <col min="12" max="12" width="14.8984375" style="5"/>
-    <col min="13" max="13" width="21.8984375" style="1" customWidth="1"/>
-    <col min="14" max="16" width="14.8984375" style="1"/>
-    <col min="17" max="17" width="9.8984375" style="1" customWidth="1"/>
-    <col min="18" max="16384" width="14.8984375" style="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:16" ht="15">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="K1" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="L1" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="M1" s="7" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16">
-      <c r="A2" s="2">
-        <v>45710</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C2" s="1">
-        <v>200</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2" s="4">
-        <f>J2</f>
-        <v>3.2754629629629631E-3</v>
-      </c>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4"/>
-      <c r="H2" s="1">
-        <v>283.08999999999997</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J2" s="4">
-        <f>TIME(0, N2, O2)</f>
-        <v>3.2754629629629631E-3</v>
-      </c>
-      <c r="K2" s="8">
-        <f>_xlfn.MINIFS(H:H, C:C, 200, D:D, "短水路")</f>
-        <v>194.47</v>
-      </c>
-      <c r="L2" s="9">
-        <f>INDEX(A:A, MATCH(_xlfn.MINIFS(H:H, D:D, "短水路"), H:H, 0))</f>
-        <v>46081</v>
-      </c>
-      <c r="M2" s="8">
-        <f>_xlfn.MINIFS(H2:H2, C2:C2, 200, D2:D2, "短水路")</f>
-        <v>283.08999999999997</v>
-      </c>
-      <c r="N2" s="8">
-        <f>INT(M2/60)</f>
-        <v>4</v>
-      </c>
-      <c r="O2" s="8">
-        <f>MOD(M2,60)</f>
-        <v>43.089999999999975</v>
-      </c>
-      <c r="P2" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16">
-      <c r="A3" s="2">
-        <v>45808</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C3" s="1">
-        <v>200</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E3" s="4">
-        <f>J3</f>
-        <v>2.8009259259259259E-3</v>
-      </c>
-      <c r="F3" s="4"/>
-      <c r="G3" s="4"/>
-      <c r="H3" s="1">
-        <v>242.71</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J3" s="4">
-        <f>TIME(0, N3, O3)</f>
-        <v>2.8009259259259259E-3</v>
-      </c>
-      <c r="K3" s="8">
-        <f>INT(K2/60)</f>
-        <v>3</v>
-      </c>
-      <c r="L3" s="9"/>
-      <c r="M3" s="8">
-        <f>_xlfn.MINIFS(H3:H3, C3:C3, 200, D3:D3, "短水路")</f>
-        <v>242.71</v>
-      </c>
-      <c r="N3" s="8">
-        <f t="shared" ref="N3:N6" si="0">INT(M3/60)</f>
-        <v>4</v>
-      </c>
-      <c r="O3" s="8">
-        <f t="shared" ref="O3:O6" si="1">MOD(M3,60)</f>
-        <v>2.710000000000008</v>
-      </c>
-      <c r="P3" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16">
-      <c r="A4" s="2">
-        <v>45899</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" s="1">
-        <v>200</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E4" s="4">
-        <f>J4</f>
-        <v>2.5115740740740741E-3</v>
-      </c>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4"/>
-      <c r="H4" s="1">
-        <v>217.53</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J4" s="4">
-        <f>TIME(0, N4, O4)</f>
-        <v>2.5115740740740741E-3</v>
-      </c>
-      <c r="K4" s="8">
-        <f>MOD(K2,60)</f>
-        <v>14.469999999999999</v>
-      </c>
-      <c r="L4" s="9"/>
-      <c r="M4" s="8">
-        <f>_xlfn.MINIFS(H4:H4, C4:C4, 200, D4:D4, "短水路")</f>
-        <v>217.53</v>
-      </c>
-      <c r="N4" s="8">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="O4" s="8">
-        <f t="shared" si="1"/>
-        <v>37.53</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16">
-      <c r="A5" s="2">
-        <v>45991</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5" s="1">
-        <v>200</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E5" s="4">
-        <f>J5</f>
-        <v>2.3263888888888887E-3</v>
-      </c>
-      <c r="F5" s="4"/>
-      <c r="G5" s="4"/>
-      <c r="H5" s="1">
-        <v>201.34</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J5" s="4">
-        <f>TIME(0, N5, O5)</f>
-        <v>2.3263888888888887E-3</v>
-      </c>
-      <c r="K5" s="4">
-        <f>TIME(0, K3, K4)</f>
-        <v>2.2453703703703702E-3</v>
-      </c>
-      <c r="M5" s="8">
-        <f>_xlfn.MINIFS(H5:H5, C5:C5, 200, D5:D5, "短水路")</f>
-        <v>201.34</v>
-      </c>
-      <c r="N5" s="8">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="O5" s="8">
-        <f t="shared" si="1"/>
-        <v>21.340000000000003</v>
-      </c>
-      <c r="P5" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16">
-      <c r="A6" s="2">
-        <v>46081</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C6" s="1">
-        <v>200</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E6" s="4">
-        <f>J6</f>
-        <v>2.2453703703703702E-3</v>
-      </c>
-      <c r="F6" s="4"/>
-      <c r="G6" s="4"/>
-      <c r="H6" s="1">
-        <v>194.47</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J6" s="4">
-        <f>TIME(0, N6, O6)</f>
-        <v>2.2453703703703702E-3</v>
-      </c>
-      <c r="M6" s="8">
-        <f>_xlfn.MINIFS(H6:H6, C6:C6, 200, D6:D6, "短水路")</f>
-        <v>194.47</v>
-      </c>
-      <c r="N6" s="8">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="O6" s="8">
-        <f t="shared" si="1"/>
-        <v>14.469999999999999</v>
-      </c>
-      <c r="P6" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16">
-      <c r="K8" s="4"/>
-      <c r="M8" s="4"/>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1"/>
-  <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2:J20" xr:uid="{9B43BB41-A730-463A-95A6-B6EBE8188ECC}">
-      <formula1>$P$5:$P$6</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:G181" xr:uid="{2E851504-0A0F-4FD5-8D2A-98ECFA809F0B}">
-      <formula1>$P$2:$P$3</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:H20" xr:uid="{4F3B2A47-C23A-4C80-87FE-9C03E8B410ED}">
+      <formula1>$I$5:$I$6</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/穂果記録.xlsx
+++ b/穂果記録.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shimo\OneDrive\Desktop\スイミングダッシュボード\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2cfbf2d641072903/Desktop/スイミングダッシュボード/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBE8A225-3594-412E-B9A9-0CE6028D707E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{CBE8A225-3594-412E-B9A9-0CE6028D707E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4CA161DF-7F66-4B4E-8F0A-6AFDF726FEC3}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="バッタ" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="24">
   <si>
     <t>日付</t>
     <rPh sb="0" eb="2">
@@ -179,10 +179,6 @@
     <rPh sb="0" eb="1">
       <t>ショウ</t>
     </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>D</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -210,7 +206,7 @@
     <numFmt numFmtId="176" formatCode="yyyy&quot;年&quot;m&quot;月&quot;d&quot;日&quot;;@"/>
     <numFmt numFmtId="177" formatCode="0.00_ "/>
     <numFmt numFmtId="178" formatCode="mm:ss.00"/>
-    <numFmt numFmtId="183" formatCode="yyyy/m/d;@"/>
+    <numFmt numFmtId="179" formatCode="yyyy/m/d;@"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -284,7 +280,7 @@
     <xf numFmtId="178" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="183" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -302,6 +298,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1019,7 +1019,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5195340D-D996-47EB-BD33-2E94CF2465C1}">
-  <dimension ref="A1:R17"/>
+  <dimension ref="A1:R12"/>
   <sheetFormatPr defaultColWidth="14.8984375" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="15.796875" style="2" bestFit="1" customWidth="1"/>
@@ -1335,11 +1335,6 @@
       </c>
       <c r="F12" s="1" t="s">
         <v>8</v>
-      </c>
-    </row>
-    <row r="17" spans="8:8">
-      <c r="H17" s="1" t="s">
-        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -1727,7 +1722,7 @@
         <v>6</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>8</v>
@@ -1750,7 +1745,7 @@
         <v>6</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>8</v>
@@ -1770,7 +1765,7 @@
         <v>6</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>8</v>
@@ -1793,7 +1788,7 @@
         <v>6</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>8</v>

--- a/穂果記録.xlsx
+++ b/穂果記録.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2cfbf2d641072903/Desktop/スイミングダッシュボード/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{CBE8A225-3594-412E-B9A9-0CE6028D707E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4CA161DF-7F66-4B4E-8F0A-6AFDF726FEC3}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{CBE8A225-3594-412E-B9A9-0CE6028D707E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6E0DD88B-30B8-4B2B-8805-3D6E86956CCD}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="22">
   <si>
     <t>日付</t>
     <rPh sb="0" eb="2">
@@ -150,23 +150,6 @@
     <t>小5</t>
     <rPh sb="0" eb="1">
       <t>ショウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>100m 更新日</t>
-    <rPh sb="5" eb="8">
-      <t>コウシンビ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>50m ベストタイム(短水路)</t>
-    <rPh sb="11" eb="12">
-      <t>タン</t>
-    </rPh>
-    <rPh sb="12" eb="14">
-      <t>スイロ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -719,7 +702,7 @@
         <v>46130</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C6" s="1">
         <v>50</v>
@@ -982,7 +965,7 @@
         <v>46130</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C9" s="1">
         <v>50</v>
@@ -1019,16 +1002,16 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5195340D-D996-47EB-BD33-2E94CF2465C1}">
-  <dimension ref="A1:R12"/>
+  <dimension ref="A1:J12"/>
   <sheetFormatPr defaultColWidth="14.8984375" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="15.796875" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="18" width="14.8984375" style="1"/>
-    <col min="19" max="19" width="9.8984375" style="1" customWidth="1"/>
-    <col min="20" max="16384" width="14.8984375" style="1"/>
+    <col min="2" max="10" width="14.8984375" style="1"/>
+    <col min="11" max="11" width="9.8984375" style="1" customWidth="1"/>
+    <col min="12" max="16384" width="14.8984375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18">
+    <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
         <v>10</v>
       </c>
@@ -1047,32 +1030,8 @@
       <c r="F1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="2" spans="1:18">
+    </row>
+    <row r="2" spans="1:10">
       <c r="A2" s="5">
         <v>45788</v>
       </c>
@@ -1091,43 +1050,11 @@
       <c r="F2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="G2" s="1">
-        <f>_xlfn.MINIFS(E:E, C:C, 50, D:D, "短水路")</f>
-        <v>46.9</v>
-      </c>
-      <c r="H2" s="5">
-        <f>INDEX(A:A, MATCH(_xlfn.MINIFS(E:E, D:D, "短水路"), E:E, 0))</f>
-        <v>46053</v>
-      </c>
-      <c r="I2" s="1">
-        <f>_xlfn.MINIFS(E:E, C:C, 50, D:D, "長水路")</f>
-        <v>47.42</v>
-      </c>
-      <c r="J2" s="5">
-        <f>INDEX(A:A, MATCH(_xlfn.MINIFS(E:E, D:D, "長水路"), E:E, 0))</f>
-        <v>45984</v>
-      </c>
-      <c r="K2" s="1">
-        <f>_xlfn.MINIFS(E:E, C:C, 100, D:D, "短水路")</f>
-        <v>0</v>
-      </c>
-      <c r="L2" s="5" t="e">
-        <f>INDEX(A:A, MATCH(_xlfn.MINIFS(E:E, C:C, "短水路"), D:D, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="M2" s="1">
-        <f>_xlfn.MINIFS(E:E, C:C, 100, D:D, "長水路")</f>
-        <v>1.1702546296296296E-3</v>
-      </c>
-      <c r="N2" s="5">
-        <f>INDEX(A:A, MATCH(_xlfn.MINIFS(E:E, D:D, "長水路"), E:E, 0))</f>
-        <v>45984</v>
-      </c>
-      <c r="R2" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:18">
+      <c r="J2" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
       <c r="A3" s="5">
         <v>45815</v>
       </c>
@@ -1146,12 +1073,11 @@
       <c r="F3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="G3" s="4"/>
-      <c r="R3" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:18">
+      <c r="J3" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
       <c r="A4" s="5">
         <v>45844</v>
       </c>
@@ -1171,7 +1097,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:18">
+    <row r="5" spans="1:10">
       <c r="A5" s="5">
         <v>45942</v>
       </c>
@@ -1190,11 +1116,11 @@
       <c r="F5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="R5" s="1" t="s">
+      <c r="J5" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:18">
+    <row r="6" spans="1:10">
       <c r="A6" s="5">
         <v>45955</v>
       </c>
@@ -1213,11 +1139,11 @@
       <c r="F6" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="R6" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="7" spans="1:18">
+      <c r="J6" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
       <c r="A7" s="5">
         <v>45984</v>
       </c>
@@ -1237,7 +1163,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:18">
+    <row r="8" spans="1:10">
       <c r="A8" s="5">
         <v>45984</v>
       </c>
@@ -1257,7 +1183,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:18">
+    <row r="9" spans="1:10">
       <c r="A9" s="5">
         <v>46033</v>
       </c>
@@ -1277,7 +1203,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:18">
+    <row r="10" spans="1:10">
       <c r="A10" s="5">
         <v>46053</v>
       </c>
@@ -1297,7 +1223,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:18">
+    <row r="11" spans="1:10">
       <c r="A11" s="5">
         <v>46075</v>
       </c>
@@ -1317,12 +1243,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:18">
+    <row r="12" spans="1:10">
       <c r="A12" s="5">
         <v>46130</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C12" s="1">
         <v>50</v>
@@ -1339,18 +1265,15 @@
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
-  <dataValidations count="4">
+  <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F12" xr:uid="{3070BE14-1306-4592-8D2D-DB0E015D081F}">
-      <formula1>$R$5:$R$6</formula1>
+      <formula1>$J$5:$J$6</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D180" xr:uid="{23738B7B-AE45-45BB-BCCC-23D386156810}">
-      <formula1>$R$2:$R$3</formula1>
+      <formula1>$J$2:$J$3</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M3:M132 K3:K132" xr:uid="{7F673E24-497E-439F-96A3-D1D77BC88705}">
-      <formula1>$P$3:$P$3</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O2:O5" xr:uid="{6C89836D-404C-484C-809D-36328A3188CA}">
-      <formula1>$Q$5:$Q$6</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G5" xr:uid="{6C89836D-404C-484C-809D-36328A3188CA}">
+      <formula1>$I$5:$I$6</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1621,7 +1544,7 @@
         <v>46130</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C11" s="1">
         <v>50</v>
@@ -1699,7 +1622,7 @@
         <v>6</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>8</v>
@@ -1722,7 +1645,7 @@
         <v>6</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>8</v>
@@ -1745,7 +1668,7 @@
         <v>6</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>8</v>
@@ -1765,7 +1688,7 @@
         <v>6</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>8</v>
@@ -1788,7 +1711,7 @@
         <v>6</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>8</v>

--- a/穂果記録.xlsx
+++ b/穂果記録.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2cfbf2d641072903/Desktop/スイミングダッシュボード/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{CBE8A225-3594-412E-B9A9-0CE6028D707E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6E0DD88B-30B8-4B2B-8805-3D6E86956CCD}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="13_ncr:1_{CBE8A225-3594-412E-B9A9-0CE6028D707E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3F94CC35-A700-4066-A8E2-C1D162621734}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2304" yWindow="2304" windowWidth="13716" windowHeight="9960" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="バッタ" sheetId="1" r:id="rId1"/>
@@ -1002,7 +1002,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5195340D-D996-47EB-BD33-2E94CF2465C1}">
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr defaultColWidth="14.8984375" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="15.796875" style="2" bestFit="1" customWidth="1"/>
@@ -1184,28 +1184,12 @@
       </c>
     </row>
     <row r="9" spans="1:10">
-      <c r="A9" s="5">
-        <v>46033</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C9" s="1">
-        <v>50</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E9" s="1">
-        <v>47.55</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>9</v>
-      </c>
+      <c r="A9" s="5"/>
+      <c r="E9" s="7"/>
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="5">
-        <v>46053</v>
+        <v>46033</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>15</v>
@@ -1217,7 +1201,7 @@
         <v>6</v>
       </c>
       <c r="E10" s="1">
-        <v>46.9</v>
+        <v>47.55</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>9</v>
@@ -1225,7 +1209,7 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="5">
-        <v>46075</v>
+        <v>46053</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>15</v>
@@ -1234,10 +1218,10 @@
         <v>50</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E11" s="1">
-        <v>47.42</v>
+        <v>46.9</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>9</v>
@@ -1245,31 +1229,51 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="5">
+        <v>46075</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C12" s="1">
+        <v>50</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E12" s="1">
+        <v>47.42</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="A13" s="5">
         <v>46130</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="B13" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C12" s="1">
-        <v>50</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E12" s="1">
+      <c r="C13" s="1">
+        <v>50</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E13" s="1">
         <v>47.95</v>
       </c>
-      <c r="F12" s="1" t="s">
+      <c r="F13" s="1" t="s">
         <v>8</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F12" xr:uid="{3070BE14-1306-4592-8D2D-DB0E015D081F}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F13" xr:uid="{3070BE14-1306-4592-8D2D-DB0E015D081F}">
       <formula1>$J$5:$J$6</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D180" xr:uid="{23738B7B-AE45-45BB-BCCC-23D386156810}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D181" xr:uid="{23738B7B-AE45-45BB-BCCC-23D386156810}">
       <formula1>$J$2:$J$3</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G5" xr:uid="{6C89836D-404C-484C-809D-36328A3188CA}">

--- a/穂果記録.xlsx
+++ b/穂果記録.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2cfbf2d641072903/Desktop/スイミングダッシュボード/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="13_ncr:1_{CBE8A225-3594-412E-B9A9-0CE6028D707E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3F94CC35-A700-4066-A8E2-C1D162621734}"/>
+  <xr:revisionPtr revIDLastSave="10" documentId="13_ncr:1_{CBE8A225-3594-412E-B9A9-0CE6028D707E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B9181EBF-9CC2-4FB7-B0F9-C4DAAD7135D1}"/>
   <bookViews>
-    <workbookView xWindow="2304" yWindow="2304" windowWidth="13716" windowHeight="9960" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="バッタ" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="23">
   <si>
     <t>日付</t>
     <rPh sb="0" eb="2">
@@ -180,15 +180,18 @@
     <t>3'14"47</t>
     <phoneticPr fontId="1"/>
   </si>
+  <si>
+    <t>1'41"11</t>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="4">
+  <numFmts count="3">
     <numFmt numFmtId="176" formatCode="yyyy&quot;年&quot;m&quot;月&quot;d&quot;日&quot;;@"/>
     <numFmt numFmtId="177" formatCode="0.00_ "/>
-    <numFmt numFmtId="178" formatCode="mm:ss.00"/>
     <numFmt numFmtId="179" formatCode="yyyy/m/d;@"/>
   </numFmts>
   <fonts count="3">
@@ -260,10 +263,10 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1002,7 +1005,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5195340D-D996-47EB-BD33-2E94CF2465C1}">
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:J12"/>
   <sheetFormatPr defaultColWidth="14.8984375" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="15.796875" style="2" bestFit="1" customWidth="1"/>
@@ -1176,20 +1179,36 @@
       <c r="D8" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="E8" s="7">
-        <v>1.1702546296296296E-3</v>
+      <c r="E8" s="8" t="s">
+        <v>22</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:10">
-      <c r="A9" s="5"/>
-      <c r="E9" s="7"/>
+      <c r="A9" s="5">
+        <v>46033</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C9" s="1">
+        <v>50</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E9" s="1">
+        <v>47.55</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="5">
-        <v>46033</v>
+        <v>46053</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>15</v>
@@ -1201,7 +1220,7 @@
         <v>6</v>
       </c>
       <c r="E10" s="1">
-        <v>47.55</v>
+        <v>46.9</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>9</v>
@@ -1209,7 +1228,7 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="5">
-        <v>46053</v>
+        <v>46075</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>15</v>
@@ -1218,10 +1237,10 @@
         <v>50</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E11" s="1">
-        <v>46.9</v>
+        <v>47.42</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>9</v>
@@ -1229,58 +1248,39 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="5">
-        <v>46075</v>
+        <v>46130</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C12" s="1">
         <v>50</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E12" s="1">
-        <v>47.42</v>
+        <v>47.95</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10">
-      <c r="A13" s="5">
-        <v>46130</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C13" s="1">
-        <v>50</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E13" s="1">
-        <v>47.95</v>
-      </c>
-      <c r="F13" s="1" t="s">
         <v>8</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F13" xr:uid="{3070BE14-1306-4592-8D2D-DB0E015D081F}">
-      <formula1>$J$5:$J$6</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D181" xr:uid="{23738B7B-AE45-45BB-BCCC-23D386156810}">
-      <formula1>$J$2:$J$3</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G5" xr:uid="{6C89836D-404C-484C-809D-36328A3188CA}">
       <formula1>$I$5:$I$6</formula1>
     </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F12" xr:uid="{3070BE14-1306-4592-8D2D-DB0E015D081F}">
+      <formula1>$J$5:$J$6</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D180" xr:uid="{23738B7B-AE45-45BB-BCCC-23D386156810}">
+      <formula1>$J$2:$J$3</formula1>
+    </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1613,7 +1613,7 @@
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="8">
+      <c r="A2" s="7">
         <v>45710</v>
       </c>
       <c r="B2" s="1" t="s">
@@ -1636,7 +1636,7 @@
       </c>
     </row>
     <row r="3" spans="1:9">
-      <c r="A3" s="8">
+      <c r="A3" s="7">
         <v>45808</v>
       </c>
       <c r="B3" s="1" t="s">
@@ -1659,7 +1659,7 @@
       </c>
     </row>
     <row r="4" spans="1:9">
-      <c r="A4" s="8">
+      <c r="A4" s="7">
         <v>45899</v>
       </c>
       <c r="B4" s="1" t="s">
@@ -1679,7 +1679,7 @@
       </c>
     </row>
     <row r="5" spans="1:9">
-      <c r="A5" s="8">
+      <c r="A5" s="7">
         <v>45991</v>
       </c>
       <c r="B5" s="1" t="s">
@@ -1702,7 +1702,7 @@
       </c>
     </row>
     <row r="6" spans="1:9">
-      <c r="A6" s="8">
+      <c r="A6" s="7">
         <v>46081</v>
       </c>
       <c r="B6" s="1" t="s">

--- a/穂果記録.xlsx
+++ b/穂果記録.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2cfbf2d641072903/Desktop/スイミングダッシュボード/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="10" documentId="13_ncr:1_{CBE8A225-3594-412E-B9A9-0CE6028D707E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B9181EBF-9CC2-4FB7-B0F9-C4DAAD7135D1}"/>
+  <xr:revisionPtr revIDLastSave="11" documentId="13_ncr:1_{CBE8A225-3594-412E-B9A9-0CE6028D707E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9F347B77-D693-4ACE-82FA-69830134FE61}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="バッタ" sheetId="1" r:id="rId1"/>
@@ -192,7 +192,7 @@
   <numFmts count="3">
     <numFmt numFmtId="176" formatCode="yyyy&quot;年&quot;m&quot;月&quot;d&quot;日&quot;;@"/>
     <numFmt numFmtId="177" formatCode="0.00_ "/>
-    <numFmt numFmtId="179" formatCode="yyyy/m/d;@"/>
+    <numFmt numFmtId="178" formatCode="yyyy/m/d;@"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -263,7 +263,7 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -1625,7 +1625,7 @@
       <c r="D2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="8" t="s">
         <v>16</v>
       </c>
       <c r="F2" s="1" t="s">
@@ -1648,7 +1648,7 @@
       <c r="D3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="8" t="s">
         <v>18</v>
       </c>
       <c r="F3" s="1" t="s">
@@ -1671,7 +1671,7 @@
       <c r="D4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="8" t="s">
         <v>19</v>
       </c>
       <c r="F4" s="1" t="s">
@@ -1691,7 +1691,7 @@
       <c r="D5" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="8" t="s">
         <v>20</v>
       </c>
       <c r="F5" s="1" t="s">
@@ -1714,7 +1714,7 @@
       <c r="D6" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E6" s="8" t="s">
         <v>21</v>
       </c>
       <c r="F6" s="1" t="s">

--- a/穂果記録.xlsx
+++ b/穂果記録.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -712,32 +712,6 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="1" t="n">
-        <v>46137</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>小6</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>50</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>長水路</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>28.32</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>菰野スイミング</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/穂果記録.xlsx
+++ b/穂果記録.xlsx
@@ -1804,7 +1804,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2005,6 +2005,32 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" s="11" t="n">
+        <v>46137</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>小6</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>200</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>171.01</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>菰野スイミング</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/穂果記録.xlsx
+++ b/穂果記録.xlsx
@@ -1804,7 +1804,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1997,35 +1997,9 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>125.01</v>
+        <v>171.01</v>
       </c>
       <c r="F7" t="inlineStr">
-        <is>
-          <t>荒野スイミング</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="11" t="n">
-        <v>46137</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>小6</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>200</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>171.01</v>
-      </c>
-      <c r="F8" t="inlineStr">
         <is>
           <t>菰野スイミング</t>
         </is>

--- a/穂果記録.xlsx
+++ b/穂果記録.xlsx
@@ -1804,7 +1804,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1979,32 +1979,6 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="11" t="n">
-        <v>46137</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>小6</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>200</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>171.01</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>菰野スイミング</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/穂果記録.xlsx
+++ b/穂果記録.xlsx
@@ -9,8 +9,8 @@
     <sheet name="バッタ" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="バック" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="ブレ" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="フリー" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="メドレー" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="メドレー" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="フリー" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -1414,387 +1414,183 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q11"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="14.8984375" defaultRowHeight="14.4"/>
-  <cols>
-    <col width="15.796875" bestFit="1" customWidth="1" style="9" min="1" max="1"/>
-    <col width="14.8984375" customWidth="1" style="1" min="2" max="6"/>
-    <col width="22.796875" customWidth="1" style="1" min="7" max="7"/>
-    <col width="14.8984375" customWidth="1" style="1" min="8" max="8"/>
-    <col width="0.8984375" customWidth="1" style="1" min="9" max="9"/>
-    <col width="27.09765625" customWidth="1" style="1" min="10" max="10"/>
-    <col width="14.8984375" customWidth="1" style="5" min="11" max="11"/>
-    <col width="14.8984375" customWidth="1" style="1" min="12" max="17"/>
-    <col width="9.8984375" customWidth="1" style="1" min="18" max="18"/>
-    <col width="14.8984375" customWidth="1" style="1" min="19" max="16384"/>
-  </cols>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>日付</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>学年</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>距離</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>長水路 or 短水路</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>長水路or短水路</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
         <is>
           <t>タイム</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>会場</t>
         </is>
       </c>
-      <c r="G1" s="6" t="inlineStr">
-        <is>
-          <t>50m ベストタイム(短水路)</t>
-        </is>
-      </c>
-      <c r="H1" s="6" t="inlineStr">
-        <is>
-          <t>50m 更新日</t>
-        </is>
-      </c>
-      <c r="J1" s="6" t="inlineStr">
-        <is>
-          <t>50m ベストタイム(長水路)</t>
-        </is>
-      </c>
-      <c r="K1" s="6" t="inlineStr">
-        <is>
-          <t>50m 更新日</t>
-        </is>
-      </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="n">
-        <v>45788</v>
-      </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t>小5</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="n">
-        <v>50</v>
-      </c>
-      <c r="D2" s="1" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E2" s="1" t="n">
-        <v>47.91</v>
-      </c>
-      <c r="F2" s="1" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-      <c r="G2" s="1">
-        <f>_xlfn.MINIFS(E:E, C:C, 50, D:D, "短水路")</f>
-        <v/>
-      </c>
-      <c r="H2" s="5">
-        <f>INDEX(A:A, MATCH(_xlfn.MINIFS(E:E, D:D, "短水路"), E:E, 0))</f>
-        <v/>
-      </c>
-      <c r="I2" s="5" t="n"/>
-      <c r="J2" s="1">
-        <f>_xlfn.MINIFS(E:E, C:C, 50, D:D, "長水路")</f>
-        <v/>
-      </c>
-      <c r="K2" s="5">
-        <f>INDEX(A:A, MATCH(_xlfn.MINIFS(E:E, D:D, "長水路"), E:E, 0))</f>
-        <v/>
-      </c>
-      <c r="Q2" s="1" t="inlineStr">
-        <is>
-          <t>長水路</t>
+      <c r="A2" s="11" t="n">
+        <v>45710</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>小4</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>200</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>4'43"09</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>菰野スイミング</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="n">
-        <v>45816</v>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>小5</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="n">
-        <v>50</v>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t>長水路</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="n">
-        <v>47.54</v>
-      </c>
-      <c r="F3" s="1" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="n"/>
-      <c r="Q3" s="1" t="inlineStr">
-        <is>
-          <t>短水路</t>
+      <c r="A3" s="11" t="n">
+        <v>45808</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>小5</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>200</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>4'02"71</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>菰野スイミング</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="n">
-        <v>45823</v>
-      </c>
-      <c r="B4" s="1" t="inlineStr">
-        <is>
-          <t>小5</t>
-        </is>
-      </c>
-      <c r="C4" s="1" t="n">
-        <v>50</v>
-      </c>
-      <c r="D4" s="1" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E4" s="1" t="n">
-        <v>44.48</v>
-      </c>
-      <c r="F4" s="1" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
+      <c r="A4" s="11" t="n">
+        <v>45899</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>小5</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>200</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>3'37"53</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>菰野スイミング</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="n">
-        <v>45844</v>
-      </c>
-      <c r="B5" s="1" t="inlineStr">
-        <is>
-          <t>小5</t>
-        </is>
-      </c>
-      <c r="C5" s="1" t="n">
-        <v>50</v>
-      </c>
-      <c r="D5" s="1" t="inlineStr">
-        <is>
-          <t>長水路</t>
-        </is>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>44.39</v>
-      </c>
-      <c r="F5" s="1" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-      <c r="Q5" s="1" t="inlineStr">
+      <c r="A5" s="11" t="n">
+        <v>45991</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>小5</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>200</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>3'21"34</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
         <is>
           <t>菰野スイミング</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="n">
-        <v>45942</v>
-      </c>
-      <c r="B6" s="1" t="inlineStr">
-        <is>
-          <t>小5</t>
-        </is>
-      </c>
-      <c r="C6" s="1" t="n">
-        <v>50</v>
-      </c>
-      <c r="D6" s="1" t="inlineStr">
-        <is>
-          <t>長水路</t>
-        </is>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>40.39</v>
-      </c>
-      <c r="F6" s="1" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-      <c r="Q6" s="1" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="n">
-        <v>45955</v>
-      </c>
-      <c r="B7" s="1" t="inlineStr">
-        <is>
-          <t>小5</t>
-        </is>
-      </c>
-      <c r="C7" s="1" t="n">
-        <v>50</v>
-      </c>
-      <c r="D7" s="1" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>40.5</v>
-      </c>
-      <c r="F7" s="1" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="n">
-        <v>46033</v>
-      </c>
-      <c r="B8" s="1" t="inlineStr">
-        <is>
-          <t>小5</t>
-        </is>
-      </c>
-      <c r="C8" s="1" t="n">
-        <v>50</v>
-      </c>
-      <c r="D8" s="1" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>39.07</v>
-      </c>
-      <c r="F8" s="1" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="n">
-        <v>46053</v>
-      </c>
-      <c r="B9" s="1" t="inlineStr">
-        <is>
-          <t>小5</t>
-        </is>
-      </c>
-      <c r="C9" s="1" t="n">
-        <v>50</v>
-      </c>
-      <c r="D9" s="1" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>38.24</v>
-      </c>
-      <c r="F9" s="1" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="n">
-        <v>46074</v>
-      </c>
-      <c r="B10" s="1" t="inlineStr">
-        <is>
-          <t>小5</t>
-        </is>
-      </c>
-      <c r="C10" s="1" t="n">
-        <v>50</v>
-      </c>
-      <c r="D10" s="1" t="inlineStr">
-        <is>
-          <t>長水路</t>
-        </is>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>37.73</v>
-      </c>
-      <c r="F10" s="1" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="n">
-        <v>46130</v>
-      </c>
-      <c r="B11" s="1" t="inlineStr">
-        <is>
-          <t>小6</t>
-        </is>
-      </c>
-      <c r="C11" s="1" t="n">
-        <v>50</v>
-      </c>
-      <c r="D11" s="1" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>40.28</v>
-      </c>
-      <c r="F11" s="1" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
+      <c r="A6" s="11" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>小5</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>200</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>3'14"47</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>菰野スイミング</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="4">
-    <dataValidation sqref="D2:D180" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
-      <formula1>$Q$2:$Q$3</formula1>
-    </dataValidation>
-    <dataValidation sqref="F2:F11" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
-      <formula1>$Q$5:$Q$6</formula1>
-    </dataValidation>
-    <dataValidation sqref="L2:L132" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
-      <formula1>$O$3:$O$3</formula1>
-    </dataValidation>
-    <dataValidation sqref="N2:N5" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
-      <formula1>$P$5:$P$6</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
@@ -1804,7 +1600,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1841,35 +1637,33 @@
     </row>
     <row r="2">
       <c r="A2" s="11" t="n">
-        <v>45710</v>
+        <v>45788</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>小4</t>
+          <t>小5</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
           <t>短水路</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>4'43"09</t>
-        </is>
+      <c r="E2" t="n">
+        <v>47.91</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>菰野スイミング</t>
+          <t>鈴鹿</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="11" t="n">
-        <v>45808</v>
+        <v>45816</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -1877,27 +1671,25 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>4'02"71</t>
-        </is>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>47.54</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>菰野スイミング</t>
+          <t>鈴鹿</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="11" t="n">
-        <v>45899</v>
+        <v>45823</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -1905,27 +1697,25 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
           <t>短水路</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>3'37"53</t>
-        </is>
+      <c r="E4" t="n">
+        <v>44.48</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>菰野スイミング</t>
+          <t>鈴鹿</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="11" t="n">
-        <v>45991</v>
+        <v>45844</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -1933,27 +1723,25 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>3'21"34</t>
-        </is>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>44.39</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>菰野スイミング</t>
+          <t>鈴鹿</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="11" t="n">
-        <v>46081</v>
+        <v>45942</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -1961,19 +1749,173 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>3'14"47</t>
-        </is>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>40.39</v>
       </c>
       <c r="F6" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="11" t="n">
+        <v>45955</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>小5</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>50</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>40.5</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="11" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>小5</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>50</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>39.07</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="11" t="n">
+        <v>46053</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>小5</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>50</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>38.24</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="11" t="n">
+        <v>46074</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>小5</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>50</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>37.73</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="11" t="n">
+        <v>46130</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>小6</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>50</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>40.28</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="11" t="n">
+        <v>46137</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>中2</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>50</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>65.08</v>
+      </c>
+      <c r="F12" t="inlineStr">
         <is>
           <t>菰野スイミング</t>
         </is>

--- a/穂果記録.xlsx
+++ b/穂果記録.xlsx
@@ -1600,7 +1600,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1921,6 +1921,32 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" s="11" t="n">
+        <v>46137</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>中2</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>50</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>65.08</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>菰野スイミング</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/穂果記録.xlsx
+++ b/穂果記録.xlsx
@@ -1901,7 +1901,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>中2</t>
+          <t>小6</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -1909,11 +1909,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>長水路</t>
+          <t>短水路</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>65.08</v>
+        <v>31.01</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>

--- a/穂果記録.xlsx
+++ b/穂果記録.xlsx
@@ -1913,7 +1913,7 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>31.01</v>
+        <v>3.01</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>

--- a/穂果記録.xlsx
+++ b/穂果記録.xlsx
@@ -1600,7 +1600,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1921,32 +1921,6 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="11" t="n">
-        <v>46137</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>中2</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>50</v>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>長水路</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>65.08</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>菰野スイミング</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/穂果記録.xlsx
+++ b/穂果記録.xlsx
@@ -1913,7 +1913,7 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>3.01</v>
+        <v>31.01</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>

--- a/穂果記録.xlsx
+++ b/穂果記録.xlsx
@@ -1600,7 +1600,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1921,6 +1921,32 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" s="11" t="n">
+        <v>46137</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>小6</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>50</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>21.25</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>菰野スイミング</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/穂果記録.xlsx
+++ b/穂果記録.xlsx
@@ -1600,7 +1600,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1913,35 +1913,9 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>31.01</v>
+        <v>21.25</v>
       </c>
       <c r="F12" t="inlineStr">
-        <is>
-          <t>菰野スイミング</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="11" t="n">
-        <v>46137</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>小6</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>50</v>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>21.25</v>
-      </c>
-      <c r="F13" t="inlineStr">
         <is>
           <t>菰野スイミング</t>
         </is>

--- a/穂果記録.xlsx
+++ b/穂果記録.xlsx
@@ -1600,7 +1600,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1895,32 +1895,6 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="11" t="n">
-        <v>46137</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>小6</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>50</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>21.25</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>菰野スイミング</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/穂果記録.xlsx
+++ b/穂果記録.xlsx
@@ -1600,7 +1600,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1895,6 +1895,32 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" s="11" t="n">
+        <v>46137</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>小6</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>50</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>1861.02</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>菰野スイミング</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/穂果記録.xlsx
+++ b/穂果記録.xlsx
@@ -9,8 +9,8 @@
     <sheet name="バッタ" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="バック" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="ブレ" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="メドレー" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="フリー" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="フリー" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="メドレー" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -1414,7 +1414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1451,35 +1451,33 @@
     </row>
     <row r="2">
       <c r="A2" s="11" t="n">
-        <v>45710</v>
+        <v>45788</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>小4</t>
+          <t>小5</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
           <t>短水路</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>4'43"09</t>
-        </is>
+      <c r="E2" t="n">
+        <v>47.91</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>菰野スイミング</t>
+          <t>鈴鹿</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="11" t="n">
-        <v>45808</v>
+        <v>45816</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -1487,27 +1485,25 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>4'02"71</t>
-        </is>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>47.54</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>菰野スイミング</t>
+          <t>鈴鹿</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="11" t="n">
-        <v>45899</v>
+        <v>45823</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -1515,27 +1511,25 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
           <t>短水路</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>3'37"53</t>
-        </is>
+      <c r="E4" t="n">
+        <v>44.48</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>菰野スイミング</t>
+          <t>鈴鹿</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="11" t="n">
-        <v>45991</v>
+        <v>45844</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -1543,27 +1537,25 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>3'21"34</t>
-        </is>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>44.39</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>菰野スイミング</t>
+          <t>鈴鹿</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="11" t="n">
-        <v>46081</v>
+        <v>45942</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -1571,19 +1563,173 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>3'14"47</t>
-        </is>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>40.39</v>
       </c>
       <c r="F6" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="11" t="n">
+        <v>45955</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>小5</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>50</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>40.5</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="11" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>小5</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>50</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>39.07</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="11" t="n">
+        <v>46053</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>小5</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>50</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>38.24</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="11" t="n">
+        <v>46074</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>小5</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>50</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>37.73</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="11" t="n">
+        <v>46130</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>小6</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>50</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>40.28</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="11" t="n">
+        <v>46137</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>小6</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>50</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>1861.02</v>
+      </c>
+      <c r="F12" t="inlineStr">
         <is>
           <t>菰野スイミング</t>
         </is>
@@ -1600,7 +1746,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1637,33 +1783,35 @@
     </row>
     <row r="2">
       <c r="A2" s="11" t="n">
-        <v>45788</v>
+        <v>45710</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>小5</t>
+          <t>小4</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
           <t>短水路</t>
         </is>
       </c>
-      <c r="E2" t="n">
-        <v>47.91</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>4'43"09</t>
+        </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>鈴鹿</t>
+          <t>菰野スイミング</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="11" t="n">
-        <v>45816</v>
+        <v>45808</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -1671,25 +1819,27 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>長水路</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>47.54</v>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>4'02"71</t>
+        </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>鈴鹿</t>
+          <t>菰野スイミング</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="11" t="n">
-        <v>45823</v>
+        <v>45899</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -1697,25 +1847,27 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
           <t>短水路</t>
         </is>
       </c>
-      <c r="E4" t="n">
-        <v>44.48</v>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>3'37"53</t>
+        </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>鈴鹿</t>
+          <t>菰野スイミング</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="11" t="n">
-        <v>45844</v>
+        <v>45991</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -1723,25 +1875,27 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>長水路</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>44.39</v>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>3'21"34</t>
+        </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>鈴鹿</t>
+          <t>菰野スイミング</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="11" t="n">
-        <v>45942</v>
+        <v>46081</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -1749,33 +1903,35 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>長水路</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>40.39</v>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>3'14"47</t>
+        </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>鈴鹿</t>
+          <t>菰野スイミング</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="11" t="n">
-        <v>45955</v>
+        <v>46137</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>小5</t>
+          <t>小6</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1783,139 +1939,9 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>40.5</v>
+        <v>171.15</v>
       </c>
       <c r="F7" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="11" t="n">
-        <v>46033</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>小5</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>50</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>39.07</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="11" t="n">
-        <v>46053</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>小5</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>50</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>38.24</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="11" t="n">
-        <v>46074</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>小5</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>50</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>長水路</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>37.73</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="11" t="n">
-        <v>46130</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>小6</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>50</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>40.28</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="11" t="n">
-        <v>46137</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>小6</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>50</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>1861.02</v>
-      </c>
-      <c r="F12" t="inlineStr">
         <is>
           <t>菰野スイミング</t>
         </is>

--- a/穂果記録.xlsx
+++ b/穂果記録.xlsx
@@ -9,8 +9,8 @@
     <sheet name="バッタ" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="バック" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="ブレ" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="フリー" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="メドレー" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="メドレー" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="フリー" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -1414,7 +1414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1451,33 +1451,35 @@
     </row>
     <row r="2">
       <c r="A2" s="11" t="n">
-        <v>45788</v>
+        <v>45710</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>小5</t>
+          <t>小4</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
           <t>短水路</t>
         </is>
       </c>
-      <c r="E2" t="n">
-        <v>47.91</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>4'43"09</t>
+        </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>鈴鹿</t>
+          <t>菰野スイミング</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="11" t="n">
-        <v>45816</v>
+        <v>45808</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -1485,25 +1487,27 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>長水路</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>47.54</v>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>4'02"71</t>
+        </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>鈴鹿</t>
+          <t>菰野スイミング</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="11" t="n">
-        <v>45823</v>
+        <v>45899</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -1511,25 +1515,27 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
           <t>短水路</t>
         </is>
       </c>
-      <c r="E4" t="n">
-        <v>44.48</v>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>3'37"53</t>
+        </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>鈴鹿</t>
+          <t>菰野スイミング</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="11" t="n">
-        <v>45844</v>
+        <v>45991</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -1537,25 +1543,27 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>長水路</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>44.39</v>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>3'21"34</t>
+        </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>鈴鹿</t>
+          <t>菰野スイミング</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="11" t="n">
-        <v>45942</v>
+        <v>46081</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -1563,33 +1571,35 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>長水路</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>40.39</v>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>3'14"47</t>
+        </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>鈴鹿</t>
+          <t>菰野スイミング</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="11" t="n">
-        <v>45955</v>
+        <v>46137</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>小5</t>
+          <t>小6</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1597,139 +1607,9 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>40.5</v>
+        <v>171.15</v>
       </c>
       <c r="F7" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="11" t="n">
-        <v>46033</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>小5</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>50</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>39.07</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="11" t="n">
-        <v>46053</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>小5</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>50</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>38.24</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="11" t="n">
-        <v>46074</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>小5</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>50</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>長水路</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>37.73</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="11" t="n">
-        <v>46130</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>小6</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>50</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>40.28</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="11" t="n">
-        <v>46137</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>小6</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>50</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>1861.02</v>
-      </c>
-      <c r="F12" t="inlineStr">
         <is>
           <t>菰野スイミング</t>
         </is>
@@ -1746,7 +1626,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1783,35 +1663,33 @@
     </row>
     <row r="2">
       <c r="A2" s="11" t="n">
-        <v>45710</v>
+        <v>45788</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>小4</t>
+          <t>小5</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
           <t>短水路</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>4'43"09</t>
-        </is>
+      <c r="E2" t="n">
+        <v>47.91</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>菰野スイミング</t>
+          <t>鈴鹿</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="11" t="n">
-        <v>45808</v>
+        <v>45816</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -1819,27 +1697,25 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>4'02"71</t>
-        </is>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>47.54</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>菰野スイミング</t>
+          <t>鈴鹿</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="11" t="n">
-        <v>45899</v>
+        <v>45823</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -1847,27 +1723,25 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
           <t>短水路</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>3'37"53</t>
-        </is>
+      <c r="E4" t="n">
+        <v>44.48</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>菰野スイミング</t>
+          <t>鈴鹿</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="11" t="n">
-        <v>45991</v>
+        <v>45844</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -1875,27 +1749,25 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>3'21"34</t>
-        </is>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>44.39</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>菰野スイミング</t>
+          <t>鈴鹿</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="11" t="n">
-        <v>46081</v>
+        <v>45942</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -1903,45 +1775,173 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>3'14"47</t>
-        </is>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>40.39</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>菰野スイミング</t>
+          <t>鈴鹿</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="11" t="n">
+        <v>45955</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>小5</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>50</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>40.5</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="11" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>小5</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>50</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>39.07</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="11" t="n">
+        <v>46053</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>小5</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>50</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>38.24</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="11" t="n">
+        <v>46074</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>小5</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>50</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>37.73</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="11" t="n">
+        <v>46130</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>小6</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>50</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>40.28</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="11" t="n">
         <v>46137</v>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>小6</t>
         </is>
       </c>
-      <c r="C7" t="n">
-        <v>200</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>171.15</v>
-      </c>
-      <c r="F7" t="inlineStr">
+      <c r="C12" t="n">
+        <v>50</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>31.02</v>
+      </c>
+      <c r="F12" t="inlineStr">
         <is>
           <t>菰野スイミング</t>
         </is>

--- a/穂果記録.xlsx
+++ b/穂果記録.xlsx
@@ -1626,7 +1626,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1921,32 +1921,6 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="11" t="n">
-        <v>46137</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>小6</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>50</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>31.02</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>菰野スイミング</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/穂果記録.xlsx
+++ b/穂果記録.xlsx
@@ -9,8 +9,8 @@
     <sheet name="バッタ" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="バック" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="ブレ" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="メドレー" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="フリー" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="フリー" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="メドレー" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -1414,7 +1414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1451,35 +1451,33 @@
     </row>
     <row r="2">
       <c r="A2" s="11" t="n">
-        <v>45710</v>
+        <v>45788</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>小4</t>
+          <t>小5</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
           <t>短水路</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>4'43"09</t>
-        </is>
+      <c r="E2" t="n">
+        <v>47.91</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>菰野スイミング</t>
+          <t>鈴鹿</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="11" t="n">
-        <v>45808</v>
+        <v>45816</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -1487,27 +1485,25 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>4'02"71</t>
-        </is>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>47.54</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>菰野スイミング</t>
+          <t>鈴鹿</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="11" t="n">
-        <v>45899</v>
+        <v>45823</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -1515,27 +1511,25 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
           <t>短水路</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>3'37"53</t>
-        </is>
+      <c r="E4" t="n">
+        <v>44.48</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>菰野スイミング</t>
+          <t>鈴鹿</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="11" t="n">
-        <v>45991</v>
+        <v>45844</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -1543,27 +1537,25 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>3'21"34</t>
-        </is>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>44.39</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>菰野スイミング</t>
+          <t>鈴鹿</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="11" t="n">
-        <v>46081</v>
+        <v>45942</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -1571,47 +1563,149 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>3'14"47</t>
-        </is>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>40.39</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>菰野スイミング</t>
+          <t>鈴鹿</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="11" t="n">
-        <v>46137</v>
+        <v>45955</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>小5</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>50</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>40.5</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="11" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>小5</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>50</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>39.07</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="11" t="n">
+        <v>46053</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>小5</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>50</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>38.24</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="11" t="n">
+        <v>46074</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>小5</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>50</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>37.73</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="11" t="n">
+        <v>46130</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
           <t>小6</t>
         </is>
       </c>
-      <c r="C7" t="n">
-        <v>200</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>171.15</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>菰野スイミング</t>
+      <c r="C11" t="n">
+        <v>50</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>40.28</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
         </is>
       </c>
     </row>
@@ -1626,7 +1720,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1663,33 +1757,35 @@
     </row>
     <row r="2">
       <c r="A2" s="11" t="n">
-        <v>45788</v>
+        <v>45710</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>小5</t>
+          <t>小4</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
           <t>短水路</t>
         </is>
       </c>
-      <c r="E2" t="n">
-        <v>47.91</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>4'43"09</t>
+        </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>鈴鹿</t>
+          <t>菰野スイミング</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="11" t="n">
-        <v>45816</v>
+        <v>45808</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -1697,25 +1793,27 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>長水路</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>47.54</v>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>4'02"71</t>
+        </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>鈴鹿</t>
+          <t>菰野スイミング</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="11" t="n">
-        <v>45823</v>
+        <v>45899</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -1723,25 +1821,27 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
           <t>短水路</t>
         </is>
       </c>
-      <c r="E4" t="n">
-        <v>44.48</v>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>3'37"53</t>
+        </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>鈴鹿</t>
+          <t>菰野スイミング</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="11" t="n">
-        <v>45844</v>
+        <v>45991</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -1749,25 +1849,27 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>長水路</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>44.39</v>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>3'21"34</t>
+        </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>鈴鹿</t>
+          <t>菰野スイミング</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="11" t="n">
-        <v>45942</v>
+        <v>46081</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -1775,149 +1877,21 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>長水路</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>40.39</v>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>3'14"47</t>
+        </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="11" t="n">
-        <v>45955</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>小5</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>50</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>40.5</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="11" t="n">
-        <v>46033</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>小5</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>50</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>39.07</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="11" t="n">
-        <v>46053</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>小5</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>50</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>38.24</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="11" t="n">
-        <v>46074</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>小5</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>50</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>長水路</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>37.73</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="11" t="n">
-        <v>46130</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>小6</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>50</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>40.28</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
+          <t>菰野スイミング</t>
         </is>
       </c>
     </row>

--- a/穂果記録.xlsx
+++ b/穂果記録.xlsx
@@ -9,8 +9,8 @@
     <sheet name="バッタ" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="バック" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="ブレ" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="フリー" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="メドレー" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="メドレー" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="フリー" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -1414,7 +1414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1451,33 +1451,35 @@
     </row>
     <row r="2">
       <c r="A2" s="11" t="n">
-        <v>45788</v>
+        <v>45710</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>小5</t>
+          <t>小4</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
           <t>短水路</t>
         </is>
       </c>
-      <c r="E2" t="n">
-        <v>47.91</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>4'43"09</t>
+        </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>鈴鹿</t>
+          <t>菰野スイミング</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="11" t="n">
-        <v>45816</v>
+        <v>45808</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -1485,25 +1487,27 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>長水路</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>47.54</v>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>4'02"71</t>
+        </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>鈴鹿</t>
+          <t>菰野スイミング</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="11" t="n">
-        <v>45823</v>
+        <v>45899</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -1511,25 +1515,27 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
           <t>短水路</t>
         </is>
       </c>
-      <c r="E4" t="n">
-        <v>44.48</v>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>3'37"53</t>
+        </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>鈴鹿</t>
+          <t>菰野スイミング</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="11" t="n">
-        <v>45844</v>
+        <v>45991</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -1537,25 +1543,27 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>長水路</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>44.39</v>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>3'21"34</t>
+        </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>鈴鹿</t>
+          <t>菰野スイミング</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="11" t="n">
-        <v>45942</v>
+        <v>46081</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -1563,149 +1571,21 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>長水路</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>40.39</v>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>3'14"47</t>
+        </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="11" t="n">
-        <v>45955</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>小5</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>50</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>40.5</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="11" t="n">
-        <v>46033</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>小5</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>50</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>39.07</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="11" t="n">
-        <v>46053</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>小5</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>50</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>38.24</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="11" t="n">
-        <v>46074</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>小5</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>50</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>長水路</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>37.73</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="11" t="n">
-        <v>46130</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>小6</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>50</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>40.28</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
+          <t>菰野スイミング</t>
         </is>
       </c>
     </row>
@@ -1720,7 +1600,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1757,35 +1637,33 @@
     </row>
     <row r="2">
       <c r="A2" s="11" t="n">
-        <v>45710</v>
+        <v>45788</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>小4</t>
+          <t>小5</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
           <t>短水路</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>4'43"09</t>
-        </is>
+      <c r="E2" t="n">
+        <v>47.91</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>菰野スイミング</t>
+          <t>鈴鹿</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="11" t="n">
-        <v>45808</v>
+        <v>45816</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -1793,27 +1671,25 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>4'02"71</t>
-        </is>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>47.54</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>菰野スイミング</t>
+          <t>鈴鹿</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="11" t="n">
-        <v>45899</v>
+        <v>45823</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -1821,27 +1697,25 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
           <t>短水路</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>3'37"53</t>
-        </is>
+      <c r="E4" t="n">
+        <v>44.48</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>菰野スイミング</t>
+          <t>鈴鹿</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="11" t="n">
-        <v>45991</v>
+        <v>45844</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -1849,27 +1723,25 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>3'21"34</t>
-        </is>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>44.39</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>菰野スイミング</t>
+          <t>鈴鹿</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="11" t="n">
-        <v>46081</v>
+        <v>45942</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -1877,19 +1749,147 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>3'14"47</t>
-        </is>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>40.39</v>
       </c>
       <c r="F6" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="11" t="n">
+        <v>45955</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>小5</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>50</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>40.5</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="11" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>小5</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>50</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>39.07</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="11" t="n">
+        <v>46053</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>小5</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>50</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>38.24</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="11" t="n">
+        <v>46074</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>小5</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>50</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>37.73</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="11" t="n">
+        <v>46130</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>小6</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>50</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>4</v>
+      </c>
+      <c r="F11" t="inlineStr">
         <is>
           <t>菰野スイミング</t>
         </is>

--- a/穂果記録.xlsx
+++ b/穂果記録.xlsx
@@ -1887,7 +1887,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4</v>
+        <v>40.28</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>

--- a/穂果記録.xlsx
+++ b/穂果記録.xlsx
@@ -8,9 +8,9 @@
   <sheets>
     <sheet name="バッタ" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="バック" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="ブレ" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="メドレー" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="フリー" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="メドレー" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="フリー" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="ブレ" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -1042,369 +1042,183 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J12"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="14.8984375" defaultRowHeight="14.4"/>
-  <cols>
-    <col width="15.796875" bestFit="1" customWidth="1" style="9" min="1" max="1"/>
-    <col width="14.8984375" customWidth="1" style="1" min="2" max="10"/>
-    <col width="9.8984375" customWidth="1" style="1" min="11" max="11"/>
-    <col width="14.8984375" customWidth="1" style="1" min="12" max="16384"/>
-  </cols>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>日付</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>学年</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>距離</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>長水路 or 短水路</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>長水路or短水路</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
         <is>
           <t>タイム</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>会場</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="n">
-        <v>45788</v>
-      </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t>小5</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="n">
-        <v>50</v>
-      </c>
-      <c r="D2" s="1" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E2" s="1" t="n">
-        <v>58.87</v>
-      </c>
-      <c r="F2" s="1" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-      <c r="J2" s="1" t="inlineStr">
-        <is>
-          <t>長水路</t>
+      <c r="A2" s="11" t="n">
+        <v>45710</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>小4</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>200</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>4'43"09</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>菰野スイミング</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="n">
-        <v>45815</v>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>小5</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="n">
-        <v>50</v>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t>長水路</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="n">
-        <v>55.01</v>
-      </c>
-      <c r="F3" s="1" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>短水路</t>
+      <c r="A3" s="11" t="n">
+        <v>45808</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>小5</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>200</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>4'02"71</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>菰野スイミング</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="n">
-        <v>45844</v>
-      </c>
-      <c r="B4" s="1" t="inlineStr">
-        <is>
-          <t>小5</t>
-        </is>
-      </c>
-      <c r="C4" s="1" t="n">
-        <v>50</v>
-      </c>
-      <c r="D4" s="1" t="inlineStr">
-        <is>
-          <t>長水路</t>
-        </is>
-      </c>
-      <c r="E4" s="1" t="n">
-        <v>52.08</v>
-      </c>
-      <c r="F4" s="1" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
+      <c r="A4" s="11" t="n">
+        <v>45899</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>小5</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>200</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>3'37"53</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>菰野スイミング</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="n">
-        <v>45942</v>
-      </c>
-      <c r="B5" s="1" t="inlineStr">
-        <is>
-          <t>小5</t>
-        </is>
-      </c>
-      <c r="C5" s="1" t="n">
-        <v>50</v>
-      </c>
-      <c r="D5" s="1" t="inlineStr">
-        <is>
-          <t>長水路</t>
-        </is>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>52.97</v>
-      </c>
-      <c r="F5" s="1" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-      <c r="J5" s="1" t="inlineStr">
+      <c r="A5" s="11" t="n">
+        <v>45991</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>小5</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>200</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>3'21"34</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
         <is>
           <t>菰野スイミング</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="n">
-        <v>45955</v>
-      </c>
-      <c r="B6" s="1" t="inlineStr">
-        <is>
-          <t>小5</t>
-        </is>
-      </c>
-      <c r="C6" s="1" t="n">
-        <v>50</v>
-      </c>
-      <c r="D6" s="1" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>49.74</v>
-      </c>
-      <c r="F6" s="1" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-      <c r="J6" s="1" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="n">
-        <v>45984</v>
-      </c>
-      <c r="B7" s="1" t="inlineStr">
-        <is>
-          <t>小5</t>
-        </is>
-      </c>
-      <c r="C7" s="1" t="n">
-        <v>50</v>
-      </c>
-      <c r="D7" s="1" t="inlineStr">
-        <is>
-          <t>長水路</t>
-        </is>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>49.06</v>
-      </c>
-      <c r="F7" s="1" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="n">
-        <v>45984</v>
-      </c>
-      <c r="B8" s="1" t="inlineStr">
-        <is>
-          <t>小5</t>
-        </is>
-      </c>
-      <c r="C8" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="D8" s="1" t="inlineStr">
-        <is>
-          <t>長水路</t>
-        </is>
-      </c>
-      <c r="E8" s="8" t="inlineStr">
-        <is>
-          <t>1'41"11</t>
-        </is>
-      </c>
-      <c r="F8" s="1" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="n">
-        <v>46033</v>
-      </c>
-      <c r="B9" s="1" t="inlineStr">
-        <is>
-          <t>小5</t>
-        </is>
-      </c>
-      <c r="C9" s="1" t="n">
-        <v>50</v>
-      </c>
-      <c r="D9" s="1" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>47.55</v>
-      </c>
-      <c r="F9" s="1" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="n">
-        <v>46053</v>
-      </c>
-      <c r="B10" s="1" t="inlineStr">
-        <is>
-          <t>小5</t>
-        </is>
-      </c>
-      <c r="C10" s="1" t="n">
-        <v>50</v>
-      </c>
-      <c r="D10" s="1" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46.9</v>
-      </c>
-      <c r="F10" s="1" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="n">
-        <v>46075</v>
-      </c>
-      <c r="B11" s="1" t="inlineStr">
-        <is>
-          <t>小5</t>
-        </is>
-      </c>
-      <c r="C11" s="1" t="n">
-        <v>50</v>
-      </c>
-      <c r="D11" s="1" t="inlineStr">
-        <is>
-          <t>長水路</t>
-        </is>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>47.42</v>
-      </c>
-      <c r="F11" s="1" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="n">
-        <v>46130</v>
-      </c>
-      <c r="B12" s="1" t="inlineStr">
-        <is>
-          <t>小6</t>
-        </is>
-      </c>
-      <c r="C12" s="1" t="n">
-        <v>50</v>
-      </c>
-      <c r="D12" s="1" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>47.95</v>
-      </c>
-      <c r="F12" s="1" t="inlineStr">
+      <c r="A6" s="11" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>小5</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>200</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>3'14"47</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
         <is>
           <t>菰野スイミング</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="3">
-    <dataValidation sqref="G2:G5" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
-      <formula1>$I$5:$I$6</formula1>
-    </dataValidation>
-    <dataValidation sqref="F2:F12" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
-      <formula1>$J$5:$J$6</formula1>
-    </dataValidation>
-    <dataValidation sqref="D2:D180" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
-      <formula1>$J$2:$J$3</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
@@ -1414,7 +1228,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1451,35 +1265,33 @@
     </row>
     <row r="2">
       <c r="A2" s="11" t="n">
-        <v>45710</v>
+        <v>45788</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>小4</t>
+          <t>小5</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
           <t>短水路</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>4'43"09</t>
-        </is>
+      <c r="E2" t="n">
+        <v>47.91</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>菰野スイミング</t>
+          <t>鈴鹿</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="11" t="n">
-        <v>45808</v>
+        <v>45816</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -1487,27 +1299,25 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>4'02"71</t>
-        </is>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>47.54</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>菰野スイミング</t>
+          <t>鈴鹿</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="11" t="n">
-        <v>45899</v>
+        <v>45823</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -1515,27 +1325,25 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
           <t>短水路</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>3'37"53</t>
-        </is>
+      <c r="E4" t="n">
+        <v>44.48</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>菰野スイミング</t>
+          <t>鈴鹿</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="11" t="n">
-        <v>45991</v>
+        <v>45844</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -1543,27 +1351,25 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>3'21"34</t>
-        </is>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>44.39</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>菰野スイミング</t>
+          <t>鈴鹿</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="11" t="n">
-        <v>46081</v>
+        <v>45942</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -1571,19 +1377,147 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>3'14"47</t>
-        </is>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>40.39</v>
       </c>
       <c r="F6" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="11" t="n">
+        <v>45955</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>小5</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>50</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>40.5</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="11" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>小5</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>50</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>39.07</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="11" t="n">
+        <v>46053</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>小5</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>50</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>38.24</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="11" t="n">
+        <v>46074</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>小5</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>50</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>37.73</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="11" t="n">
+        <v>46130</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>小6</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>50</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>40.28</v>
+      </c>
+      <c r="F11" t="inlineStr">
         <is>
           <t>菰野スイミング</t>
         </is>
@@ -1600,7 +1534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1653,7 +1587,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>47.91</v>
+        <v>58.87</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -1663,7 +1597,7 @@
     </row>
     <row r="3">
       <c r="A3" s="11" t="n">
-        <v>45816</v>
+        <v>45815</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -1679,7 +1613,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>47.54</v>
+        <v>55.01</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1689,7 +1623,7 @@
     </row>
     <row r="4">
       <c r="A4" s="11" t="n">
-        <v>45823</v>
+        <v>45844</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -1701,11 +1635,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>短水路</t>
+          <t>長水路</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>44.48</v>
+        <v>52.08</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1715,7 +1649,7 @@
     </row>
     <row r="5">
       <c r="A5" s="11" t="n">
-        <v>45844</v>
+        <v>45942</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -1731,7 +1665,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>44.39</v>
+        <v>52.97</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1741,7 +1675,7 @@
     </row>
     <row r="6">
       <c r="A6" s="11" t="n">
-        <v>45942</v>
+        <v>45955</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -1753,11 +1687,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>長水路</t>
+          <t>短水路</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>40.39</v>
+        <v>49.74</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1767,7 +1701,7 @@
     </row>
     <row r="7">
       <c r="A7" s="11" t="n">
-        <v>45955</v>
+        <v>45984</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -1779,11 +1713,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>短水路</t>
+          <t>長水路</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>40.5</v>
+        <v>49.06</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1793,7 +1727,7 @@
     </row>
     <row r="8">
       <c r="A8" s="11" t="n">
-        <v>46033</v>
+        <v>45984</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -1801,15 +1735,17 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>39.07</v>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>1'41"11</t>
+        </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1819,7 +1755,7 @@
     </row>
     <row r="9">
       <c r="A9" s="11" t="n">
-        <v>46053</v>
+        <v>46033</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1835,7 +1771,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>38.24</v>
+        <v>47.55</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1845,7 +1781,7 @@
     </row>
     <row r="10">
       <c r="A10" s="11" t="n">
-        <v>46074</v>
+        <v>46053</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -1857,11 +1793,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>長水路</t>
+          <t>短水路</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>37.73</v>
+        <v>46.9</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1871,27 +1807,79 @@
     </row>
     <row r="11">
       <c r="A11" s="11" t="n">
+        <v>46075</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>小5</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>50</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>47.42</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="11" t="n">
         <v>46130</v>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>小6</t>
         </is>
       </c>
-      <c r="C11" t="n">
-        <v>50</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>40.28</v>
-      </c>
-      <c r="F11" t="inlineStr">
+      <c r="C12" t="n">
+        <v>50</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>47.95</v>
+      </c>
+      <c r="F12" t="inlineStr">
         <is>
           <t>菰野スイミング</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="11" t="n">
+        <v>46053</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>小5</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>100</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>99.48999999999999</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
         </is>
       </c>
     </row>

--- a/穂果記録.xlsx
+++ b/穂果記録.xlsx
@@ -1534,7 +1534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1883,6 +1883,32 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" s="11" t="n">
+        <v>46053</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>小5</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>100</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>99.48999999999999</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/穂果記録.xlsx
+++ b/穂果記録.xlsx
@@ -1534,7 +1534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1883,32 +1883,6 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="11" t="n">
-        <v>46053</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>小5</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>100</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>99.48999999999999</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/穂果記録.xlsx
+++ b/穂果記録.xlsx
@@ -9,8 +9,8 @@
     <sheet name="バッタ" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="バック" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="メドレー" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="フリー" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="ブレ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="ブレ" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="フリー" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -1228,7 +1228,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1281,7 +1281,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>47.91</v>
+        <v>58.87</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -1291,7 +1291,7 @@
     </row>
     <row r="3">
       <c r="A3" s="11" t="n">
-        <v>45816</v>
+        <v>45815</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>47.54</v>
+        <v>55.01</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1317,7 +1317,7 @@
     </row>
     <row r="4">
       <c r="A4" s="11" t="n">
-        <v>45823</v>
+        <v>45844</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -1329,11 +1329,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>短水路</t>
+          <t>長水路</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>44.48</v>
+        <v>52.08</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
     </row>
     <row r="5">
       <c r="A5" s="11" t="n">
-        <v>45844</v>
+        <v>45942</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>44.39</v>
+        <v>52.97</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
     </row>
     <row r="6">
       <c r="A6" s="11" t="n">
-        <v>45942</v>
+        <v>45955</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -1381,11 +1381,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>長水路</t>
+          <t>短水路</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>40.39</v>
+        <v>49.74</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1395,7 +1395,7 @@
     </row>
     <row r="7">
       <c r="A7" s="11" t="n">
-        <v>45955</v>
+        <v>45984</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -1407,11 +1407,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>短水路</t>
+          <t>長水路</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>40.5</v>
+        <v>49.06</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1421,7 +1421,7 @@
     </row>
     <row r="8">
       <c r="A8" s="11" t="n">
-        <v>46033</v>
+        <v>45984</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -1429,15 +1429,17 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>39.07</v>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>1'41"11</t>
+        </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1447,7 +1449,7 @@
     </row>
     <row r="9">
       <c r="A9" s="11" t="n">
-        <v>46053</v>
+        <v>46033</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1463,7 +1465,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>38.24</v>
+        <v>47.55</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1473,7 +1475,7 @@
     </row>
     <row r="10">
       <c r="A10" s="11" t="n">
-        <v>46074</v>
+        <v>46053</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -1485,11 +1487,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>長水路</t>
+          <t>短水路</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>37.73</v>
+        <v>46.9</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1499,27 +1501,79 @@
     </row>
     <row r="11">
       <c r="A11" s="11" t="n">
+        <v>46075</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>小5</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>50</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>47.42</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="11" t="n">
         <v>46130</v>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>小6</t>
         </is>
       </c>
-      <c r="C11" t="n">
-        <v>50</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>40.28</v>
-      </c>
-      <c r="F11" t="inlineStr">
+      <c r="C12" t="n">
+        <v>50</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>47.95</v>
+      </c>
+      <c r="F12" t="inlineStr">
         <is>
           <t>菰野スイミング</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="11" t="n">
+        <v>46053</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>小5</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>100</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>99.48999999999999</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
         </is>
       </c>
     </row>
@@ -1534,7 +1588,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1587,7 +1641,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>58.87</v>
+        <v>47.91</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -1597,7 +1651,7 @@
     </row>
     <row r="3">
       <c r="A3" s="11" t="n">
-        <v>45815</v>
+        <v>45816</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -1613,7 +1667,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>55.01</v>
+        <v>47.54</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1623,7 +1677,7 @@
     </row>
     <row r="4">
       <c r="A4" s="11" t="n">
-        <v>45844</v>
+        <v>45823</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -1635,11 +1689,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>長水路</t>
+          <t>短水路</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>52.08</v>
+        <v>44.48</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1649,7 +1703,7 @@
     </row>
     <row r="5">
       <c r="A5" s="11" t="n">
-        <v>45942</v>
+        <v>45844</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -1665,7 +1719,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>52.97</v>
+        <v>44.39</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1675,7 +1729,7 @@
     </row>
     <row r="6">
       <c r="A6" s="11" t="n">
-        <v>45955</v>
+        <v>45942</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -1687,11 +1741,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>短水路</t>
+          <t>長水路</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>49.74</v>
+        <v>40.39</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1701,7 +1755,7 @@
     </row>
     <row r="7">
       <c r="A7" s="11" t="n">
-        <v>45984</v>
+        <v>45955</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -1713,11 +1767,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>長水路</t>
+          <t>短水路</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>49.06</v>
+        <v>40.5</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1727,7 +1781,7 @@
     </row>
     <row r="8">
       <c r="A8" s="11" t="n">
-        <v>45984</v>
+        <v>46033</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -1735,17 +1789,15 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>長水路</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>1'41"11</t>
-        </is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>39.07</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1755,7 +1807,7 @@
     </row>
     <row r="9">
       <c r="A9" s="11" t="n">
-        <v>46033</v>
+        <v>46053</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1771,7 +1823,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>47.55</v>
+        <v>38.24</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1781,7 +1833,7 @@
     </row>
     <row r="10">
       <c r="A10" s="11" t="n">
-        <v>46053</v>
+        <v>46074</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -1793,11 +1845,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>短水路</t>
+          <t>長水路</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>46.9</v>
+        <v>37.73</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1807,11 +1859,11 @@
     </row>
     <row r="11">
       <c r="A11" s="11" t="n">
-        <v>46075</v>
+        <v>46130</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>小5</t>
+          <t>小6</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1819,21 +1871,21 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>長水路</t>
+          <t>短水路</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>47.42</v>
+        <v>40.28</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>鈴鹿</t>
+          <t>菰野スイミング</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="11" t="n">
-        <v>46130</v>
+        <v>46145</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -1845,41 +1897,15 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>短水路</t>
+          <t>長水路</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>47.95</v>
+        <v>30.05</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>菰野スイミング</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="11" t="n">
-        <v>46053</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>小5</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>100</v>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>99.48999999999999</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
         </is>
       </c>
     </row>

--- a/穂果記録.xlsx
+++ b/穂果記録.xlsx
@@ -1588,7 +1588,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1883,32 +1883,6 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="11" t="n">
-        <v>46145</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>小6</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>50</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>長水路</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>30.05</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>菰野スイミング</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/穂果記録.xlsx
+++ b/穂果記録.xlsx
@@ -8,9 +8,9 @@
   <sheets>
     <sheet name="バッタ" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="バック" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="メドレー" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="ブレ" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="フリー" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="ブレ" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="フリー" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="メドレー" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -1042,7 +1042,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1079,35 +1079,33 @@
     </row>
     <row r="2">
       <c r="A2" s="11" t="n">
-        <v>45710</v>
+        <v>45788</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>小4</t>
+          <t>小5</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
           <t>短水路</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>4'43"09</t>
-        </is>
+      <c r="E2" t="n">
+        <v>58.87</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>菰野スイミング</t>
+          <t>鈴鹿</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="11" t="n">
-        <v>45808</v>
+        <v>45815</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -1115,27 +1113,25 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>4'02"71</t>
-        </is>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>55.01</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>菰野スイミング</t>
+          <t>鈴鹿</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="11" t="n">
-        <v>45899</v>
+        <v>45844</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -1143,27 +1139,25 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>3'37"53</t>
-        </is>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>52.08</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>菰野スイミング</t>
+          <t>鈴鹿</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="11" t="n">
-        <v>45991</v>
+        <v>45942</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -1171,27 +1165,25 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>3'21"34</t>
-        </is>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>52.97</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>菰野スイミング</t>
+          <t>鈴鹿</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="11" t="n">
-        <v>46081</v>
+        <v>45955</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -1199,21 +1191,203 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
           <t>短水路</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>3'14"47</t>
-        </is>
+      <c r="E6" t="n">
+        <v>49.74</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="11" t="n">
+        <v>45984</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>小5</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>50</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>49.06</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="11" t="n">
+        <v>45984</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>小5</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>100</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>1'41"11</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="11" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>小5</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>50</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>47.55</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="11" t="n">
+        <v>46053</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>小5</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>50</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>46.9</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="11" t="n">
+        <v>46075</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>小5</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>50</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>47.42</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="11" t="n">
+        <v>46130</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>小6</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>50</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>47.95</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
           <t>菰野スイミング</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="11" t="n">
+        <v>46053</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>小5</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>100</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>99.48999999999999</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
         </is>
       </c>
     </row>
@@ -1228,7 +1402,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1281,7 +1455,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>58.87</v>
+        <v>47.91</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -1291,7 +1465,7 @@
     </row>
     <row r="3">
       <c r="A3" s="11" t="n">
-        <v>45815</v>
+        <v>45816</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -1307,7 +1481,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>55.01</v>
+        <v>47.54</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1317,7 +1491,7 @@
     </row>
     <row r="4">
       <c r="A4" s="11" t="n">
-        <v>45844</v>
+        <v>45823</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -1329,11 +1503,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>長水路</t>
+          <t>短水路</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>52.08</v>
+        <v>44.48</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1343,7 +1517,7 @@
     </row>
     <row r="5">
       <c r="A5" s="11" t="n">
-        <v>45942</v>
+        <v>45844</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -1359,7 +1533,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>52.97</v>
+        <v>44.39</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1369,7 +1543,7 @@
     </row>
     <row r="6">
       <c r="A6" s="11" t="n">
-        <v>45955</v>
+        <v>45942</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -1381,11 +1555,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>短水路</t>
+          <t>長水路</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>49.74</v>
+        <v>40.39</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1395,7 +1569,7 @@
     </row>
     <row r="7">
       <c r="A7" s="11" t="n">
-        <v>45984</v>
+        <v>45955</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -1407,11 +1581,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>長水路</t>
+          <t>短水路</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>49.06</v>
+        <v>40.5</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1421,7 +1595,7 @@
     </row>
     <row r="8">
       <c r="A8" s="11" t="n">
-        <v>45984</v>
+        <v>46033</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -1429,17 +1603,15 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>長水路</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>1'41"11</t>
-        </is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>39.07</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1449,7 +1621,7 @@
     </row>
     <row r="9">
       <c r="A9" s="11" t="n">
-        <v>46033</v>
+        <v>46053</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1465,7 +1637,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>47.55</v>
+        <v>38.24</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1475,7 +1647,7 @@
     </row>
     <row r="10">
       <c r="A10" s="11" t="n">
-        <v>46053</v>
+        <v>46074</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -1487,11 +1659,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>短水路</t>
+          <t>長水路</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>46.9</v>
+        <v>37.73</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1501,11 +1673,11 @@
     </row>
     <row r="11">
       <c r="A11" s="11" t="n">
-        <v>46075</v>
+        <v>46130</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>小5</t>
+          <t>小6</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1513,67 +1685,15 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>長水路</t>
+          <t>短水路</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>47.42</v>
+        <v>40.28</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="11" t="n">
-        <v>46130</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>小6</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>50</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>47.95</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
           <t>菰野スイミング</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="11" t="n">
-        <v>46053</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>小5</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>100</v>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>99.48999999999999</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1708,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1625,33 +1745,35 @@
     </row>
     <row r="2">
       <c r="A2" s="11" t="n">
-        <v>45788</v>
+        <v>45710</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>小5</t>
+          <t>小4</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
           <t>短水路</t>
         </is>
       </c>
-      <c r="E2" t="n">
-        <v>47.91</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>4'43"09</t>
+        </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>鈴鹿</t>
+          <t>菰野スイミング</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="11" t="n">
-        <v>45816</v>
+        <v>45808</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -1659,25 +1781,27 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>長水路</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>47.54</v>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>4'02"71</t>
+        </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>鈴鹿</t>
+          <t>菰野スイミング</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="11" t="n">
-        <v>45823</v>
+        <v>45899</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -1685,25 +1809,27 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
           <t>短水路</t>
         </is>
       </c>
-      <c r="E4" t="n">
-        <v>44.48</v>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>3'37"53</t>
+        </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>鈴鹿</t>
+          <t>菰野スイミング</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="11" t="n">
-        <v>45844</v>
+        <v>45991</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -1711,25 +1837,27 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>長水路</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>44.39</v>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>3'21"34</t>
+        </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>鈴鹿</t>
+          <t>菰野スイミング</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="11" t="n">
-        <v>45942</v>
+        <v>46081</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -1737,29 +1865,31 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>長水路</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>40.39</v>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>3'14"47</t>
+        </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>鈴鹿</t>
+          <t>菰野スイミング</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="11" t="n">
-        <v>45955</v>
+        <v>46145</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>小5</t>
+          <t>小6</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -1771,113 +1901,9 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>40.5</v>
+        <v>173.24</v>
       </c>
       <c r="F7" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="11" t="n">
-        <v>46033</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>小5</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>50</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>39.07</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="11" t="n">
-        <v>46053</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>小5</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>50</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>38.24</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="11" t="n">
-        <v>46074</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>小5</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>50</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>長水路</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>37.73</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="11" t="n">
-        <v>46130</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>小6</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>50</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>40.28</v>
-      </c>
-      <c r="F11" t="inlineStr">
         <is>
           <t>菰野スイミング</t>
         </is>

--- a/穂果記録.xlsx
+++ b/穂果記録.xlsx
@@ -1708,7 +1708,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1909,6 +1909,32 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" s="11" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>小6</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>200</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>173.24</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>菰野スイミング</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/穂果記録.xlsx
+++ b/穂果記録.xlsx
@@ -1708,7 +1708,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1909,32 +1909,6 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="11" t="n">
-        <v>46145</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>小6</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>200</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>173.24</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>菰野スイミング</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/穂果記録.xlsx
+++ b/穂果記録.xlsx
@@ -1927,7 +1927,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>173.24</v>
+        <v>170.21</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>

--- a/穂果記録.xlsx
+++ b/穂果記録.xlsx
@@ -1708,7 +1708,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1909,32 +1909,6 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="11" t="n">
-        <v>46145</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>小6</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>200</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>170.21</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>菰野スイミング</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/穂果記録.xlsx
+++ b/穂果記録.xlsx
@@ -9,8 +9,8 @@
     <sheet name="バッタ" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="バック" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="ブレ" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="フリー" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="メドレー" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="メドレー" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="フリー" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -1402,7 +1402,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1439,33 +1439,35 @@
     </row>
     <row r="2">
       <c r="A2" s="11" t="n">
-        <v>45788</v>
+        <v>45710</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>小5</t>
+          <t>小4</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
           <t>短水路</t>
         </is>
       </c>
-      <c r="E2" t="n">
-        <v>47.91</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>4'43"09</t>
+        </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>鈴鹿</t>
+          <t>菰野スイミング</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="11" t="n">
-        <v>45816</v>
+        <v>45808</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -1473,25 +1475,27 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>長水路</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>47.54</v>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>4'02"71</t>
+        </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>鈴鹿</t>
+          <t>菰野スイミング</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="11" t="n">
-        <v>45823</v>
+        <v>45899</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -1499,25 +1503,27 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
           <t>短水路</t>
         </is>
       </c>
-      <c r="E4" t="n">
-        <v>44.48</v>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>3'37"53</t>
+        </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>鈴鹿</t>
+          <t>菰野スイミング</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="11" t="n">
-        <v>45844</v>
+        <v>45991</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -1525,25 +1531,27 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>長水路</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>44.39</v>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>3'21"34</t>
+        </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>鈴鹿</t>
+          <t>菰野スイミング</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="11" t="n">
-        <v>45942</v>
+        <v>46081</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -1551,29 +1559,31 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>長水路</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>40.39</v>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>3'14"47</t>
+        </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>鈴鹿</t>
+          <t>菰野スイミング</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="11" t="n">
-        <v>45955</v>
+        <v>46145</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>小5</t>
+          <t>小6</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -1585,113 +1595,9 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>40.5</v>
+        <v>173.24</v>
       </c>
       <c r="F7" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="11" t="n">
-        <v>46033</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>小5</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>50</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>39.07</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="11" t="n">
-        <v>46053</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>小5</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>50</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>38.24</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="11" t="n">
-        <v>46074</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>小5</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>50</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>長水路</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>37.73</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="11" t="n">
-        <v>46130</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>小6</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>50</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>40.28</v>
-      </c>
-      <c r="F11" t="inlineStr">
         <is>
           <t>菰野スイミング</t>
         </is>
@@ -1708,7 +1614,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1745,35 +1651,33 @@
     </row>
     <row r="2">
       <c r="A2" s="11" t="n">
-        <v>45710</v>
+        <v>45788</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>小4</t>
+          <t>小5</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
           <t>短水路</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>4'43"09</t>
-        </is>
+      <c r="E2" t="n">
+        <v>47.91</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>菰野スイミング</t>
+          <t>鈴鹿</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="11" t="n">
-        <v>45808</v>
+        <v>45816</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -1781,27 +1685,25 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>4'02"71</t>
-        </is>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>47.54</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>菰野スイミング</t>
+          <t>鈴鹿</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="11" t="n">
-        <v>45899</v>
+        <v>45823</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -1809,27 +1711,25 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
           <t>短水路</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>3'37"53</t>
-        </is>
+      <c r="E4" t="n">
+        <v>44.48</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>菰野スイミング</t>
+          <t>鈴鹿</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="11" t="n">
-        <v>45991</v>
+        <v>45844</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -1837,27 +1737,25 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>3'21"34</t>
-        </is>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>44.39</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>菰野スイミング</t>
+          <t>鈴鹿</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="11" t="n">
-        <v>46081</v>
+        <v>45942</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -1865,45 +1763,173 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>3'14"47</t>
-        </is>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>40.39</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>菰野スイミング</t>
+          <t>鈴鹿</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="11" t="n">
+        <v>45955</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>小5</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>50</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>40.5</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="11" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>小5</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>50</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>39.07</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="11" t="n">
+        <v>46053</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>小5</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>50</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>38.24</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="11" t="n">
+        <v>46074</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>小5</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>50</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>37.73</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="11" t="n">
+        <v>46130</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>小6</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>50</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>40.28</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>菰野スイミング</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="11" t="n">
         <v>46145</v>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>小6</t>
         </is>
       </c>
-      <c r="C7" t="n">
-        <v>50</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>173.24</v>
-      </c>
-      <c r="F7" t="inlineStr">
+      <c r="C12" t="n">
+        <v>50</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>33.35</v>
+      </c>
+      <c r="F12" t="inlineStr">
         <is>
           <t>菰野スイミング</t>
         </is>

--- a/穂果記録.xlsx
+++ b/穂果記録.xlsx
@@ -1923,11 +1923,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>短水路</t>
+          <t>長水路</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>33.35</v>
+        <v>35.35</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>

--- a/穂果記録.xlsx
+++ b/穂果記録.xlsx
@@ -1614,7 +1614,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1909,32 +1909,6 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="11" t="n">
-        <v>46145</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>小6</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>50</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>長水路</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>35.35</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>菰野スイミング</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/穂果記録.xlsx
+++ b/穂果記録.xlsx
@@ -1614,7 +1614,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1909,6 +1909,32 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" s="11" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>小6</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>50</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>36.55</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>菰野スイミング</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/穂果記録.xlsx
+++ b/穂果記録.xlsx
@@ -8,9 +8,9 @@
   <sheets>
     <sheet name="バッタ" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="バック" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="ブレ" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="メドレー" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="フリー" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="メドレー" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="フリー" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="ブレ" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -1042,7 +1042,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1079,33 +1079,35 @@
     </row>
     <row r="2">
       <c r="A2" s="11" t="n">
-        <v>45788</v>
+        <v>45710</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>小5</t>
+          <t>小4</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
           <t>短水路</t>
         </is>
       </c>
-      <c r="E2" t="n">
-        <v>58.87</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>4'43"09</t>
+        </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>鈴鹿</t>
+          <t>菰野スイミング</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="11" t="n">
-        <v>45815</v>
+        <v>45808</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -1113,25 +1115,27 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>長水路</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>55.01</v>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>4'02"71</t>
+        </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>鈴鹿</t>
+          <t>菰野スイミング</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="11" t="n">
-        <v>45844</v>
+        <v>45899</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -1139,25 +1143,27 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>長水路</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>52.08</v>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>3'37"53</t>
+        </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>鈴鹿</t>
+          <t>菰野スイミング</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="11" t="n">
-        <v>45942</v>
+        <v>45991</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -1165,25 +1171,27 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>長水路</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>52.97</v>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>3'21"34</t>
+        </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>鈴鹿</t>
+          <t>菰野スイミング</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="11" t="n">
-        <v>45955</v>
+        <v>46081</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -1191,29 +1199,31 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
           <t>短水路</t>
         </is>
       </c>
-      <c r="E6" t="n">
-        <v>49.74</v>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>3'14"47</t>
+        </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>鈴鹿</t>
+          <t>菰野スイミング</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="11" t="n">
-        <v>45984</v>
+        <v>46145</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>小5</t>
+          <t>小6</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -1221,173 +1231,15 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>長水路</t>
+          <t>短水路</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>49.06</v>
+        <v>173.24</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="11" t="n">
-        <v>45984</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>小5</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>100</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>長水路</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>1'41"11</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="11" t="n">
-        <v>46033</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>小5</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>50</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>47.55</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="11" t="n">
-        <v>46053</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>小5</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>50</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>46.9</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="11" t="n">
-        <v>46075</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>小5</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>50</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>長水路</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>47.42</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="11" t="n">
-        <v>46130</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>小6</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>50</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>47.95</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
           <t>菰野スイミング</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="11" t="n">
-        <v>46053</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>小5</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>100</v>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>99.48999999999999</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
         </is>
       </c>
     </row>
@@ -1402,7 +1254,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1439,35 +1291,33 @@
     </row>
     <row r="2">
       <c r="A2" s="11" t="n">
-        <v>45710</v>
+        <v>45788</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>小4</t>
+          <t>小5</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
           <t>短水路</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>4'43"09</t>
-        </is>
+      <c r="E2" t="n">
+        <v>47.91</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>菰野スイミング</t>
+          <t>鈴鹿</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="11" t="n">
-        <v>45808</v>
+        <v>45816</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -1475,27 +1325,25 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>4'02"71</t>
-        </is>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>47.54</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>菰野スイミング</t>
+          <t>鈴鹿</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="11" t="n">
-        <v>45899</v>
+        <v>45823</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -1503,27 +1351,25 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
           <t>短水路</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>3'37"53</t>
-        </is>
+      <c r="E4" t="n">
+        <v>44.48</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>菰野スイミング</t>
+          <t>鈴鹿</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="11" t="n">
-        <v>45991</v>
+        <v>45844</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -1531,27 +1377,25 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>3'21"34</t>
-        </is>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>44.39</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>菰野スイミング</t>
+          <t>鈴鹿</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="11" t="n">
-        <v>46081</v>
+        <v>45942</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -1559,45 +1403,173 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>3'14"47</t>
-        </is>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>40.39</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>菰野スイミング</t>
+          <t>鈴鹿</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="11" t="n">
-        <v>46145</v>
+        <v>45955</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>小5</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>50</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>40.5</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="11" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>小5</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>50</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>39.07</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="11" t="n">
+        <v>46053</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>小5</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>50</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>38.24</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="11" t="n">
+        <v>46074</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>小5</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>50</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>37.73</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="11" t="n">
+        <v>46130</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
           <t>小6</t>
         </is>
       </c>
-      <c r="C7" t="n">
-        <v>50</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>173.24</v>
-      </c>
-      <c r="F7" t="inlineStr">
+      <c r="C11" t="n">
+        <v>50</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>40.28</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>菰野スイミング</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="11" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>小6</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>50</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>36.55</v>
+      </c>
+      <c r="F12" t="inlineStr">
         <is>
           <t>菰野スイミング</t>
         </is>
@@ -1614,7 +1586,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1667,7 +1639,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>47.91</v>
+        <v>58.87</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -1677,7 +1649,7 @@
     </row>
     <row r="3">
       <c r="A3" s="11" t="n">
-        <v>45816</v>
+        <v>45815</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -1693,7 +1665,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>47.54</v>
+        <v>55.01</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1703,7 +1675,7 @@
     </row>
     <row r="4">
       <c r="A4" s="11" t="n">
-        <v>45823</v>
+        <v>45844</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -1715,11 +1687,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>短水路</t>
+          <t>長水路</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>44.48</v>
+        <v>52.08</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1729,7 +1701,7 @@
     </row>
     <row r="5">
       <c r="A5" s="11" t="n">
-        <v>45844</v>
+        <v>45942</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -1745,7 +1717,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>44.39</v>
+        <v>52.97</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1755,7 +1727,7 @@
     </row>
     <row r="6">
       <c r="A6" s="11" t="n">
-        <v>45942</v>
+        <v>45955</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -1767,11 +1739,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>長水路</t>
+          <t>短水路</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>40.39</v>
+        <v>49.74</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1781,7 +1753,7 @@
     </row>
     <row r="7">
       <c r="A7" s="11" t="n">
-        <v>45955</v>
+        <v>45984</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -1793,11 +1765,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>短水路</t>
+          <t>長水路</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>40.5</v>
+        <v>49.06</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1807,7 +1779,7 @@
     </row>
     <row r="8">
       <c r="A8" s="11" t="n">
-        <v>46033</v>
+        <v>45984</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -1815,15 +1787,17 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>39.07</v>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>1'41"11</t>
+        </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1833,7 +1807,7 @@
     </row>
     <row r="9">
       <c r="A9" s="11" t="n">
-        <v>46053</v>
+        <v>46033</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1849,7 +1823,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>38.24</v>
+        <v>47.55</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1859,7 +1833,7 @@
     </row>
     <row r="10">
       <c r="A10" s="11" t="n">
-        <v>46074</v>
+        <v>46053</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -1871,11 +1845,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>長水路</t>
+          <t>短水路</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>37.73</v>
+        <v>46.9</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1885,11 +1859,11 @@
     </row>
     <row r="11">
       <c r="A11" s="11" t="n">
-        <v>46130</v>
+        <v>46075</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>小6</t>
+          <t>小5</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1897,39 +1871,91 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>短水路</t>
+          <t>長水路</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>40.28</v>
+        <v>47.42</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>菰野スイミング</t>
+          <t>鈴鹿</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="11" t="n">
+        <v>46130</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>小6</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>50</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>47.95</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>菰野スイミング</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="11" t="n">
+        <v>46053</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>小5</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>100</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>99.48999999999999</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="11" t="n">
         <v>46152</v>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>小6</t>
         </is>
       </c>
-      <c r="C12" t="n">
-        <v>50</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>36.55</v>
-      </c>
-      <c r="F12" t="inlineStr">
+      <c r="C14" t="n">
+        <v>50</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>45.36</v>
+      </c>
+      <c r="F14" t="inlineStr">
         <is>
           <t>菰野スイミング</t>
         </is>

--- a/穂果記録.xlsx
+++ b/穂果記録.xlsx
@@ -9,8 +9,8 @@
     <sheet name="バッタ" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="バック" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="メドレー" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="フリー" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="ブレ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="ブレ" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="フリー" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -1254,7 +1254,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1307,7 +1307,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>47.91</v>
+        <v>58.87</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -1317,7 +1317,7 @@
     </row>
     <row r="3">
       <c r="A3" s="11" t="n">
-        <v>45816</v>
+        <v>45815</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -1333,7 +1333,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>47.54</v>
+        <v>55.01</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
     </row>
     <row r="4">
       <c r="A4" s="11" t="n">
-        <v>45823</v>
+        <v>45844</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -1355,11 +1355,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>短水路</t>
+          <t>長水路</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>44.48</v>
+        <v>52.08</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
     </row>
     <row r="5">
       <c r="A5" s="11" t="n">
-        <v>45844</v>
+        <v>45942</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>44.39</v>
+        <v>52.97</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1395,7 +1395,7 @@
     </row>
     <row r="6">
       <c r="A6" s="11" t="n">
-        <v>45942</v>
+        <v>45955</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -1407,11 +1407,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>長水路</t>
+          <t>短水路</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>40.39</v>
+        <v>49.74</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1421,7 +1421,7 @@
     </row>
     <row r="7">
       <c r="A7" s="11" t="n">
-        <v>45955</v>
+        <v>45984</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -1433,11 +1433,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>短水路</t>
+          <t>長水路</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>40.5</v>
+        <v>49.06</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1447,7 +1447,7 @@
     </row>
     <row r="8">
       <c r="A8" s="11" t="n">
-        <v>46033</v>
+        <v>45984</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -1455,15 +1455,17 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>39.07</v>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>1'41"11</t>
+        </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1473,7 +1475,7 @@
     </row>
     <row r="9">
       <c r="A9" s="11" t="n">
-        <v>46053</v>
+        <v>46033</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1489,7 +1491,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>38.24</v>
+        <v>47.55</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1499,7 +1501,7 @@
     </row>
     <row r="10">
       <c r="A10" s="11" t="n">
-        <v>46074</v>
+        <v>46053</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -1511,11 +1513,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>長水路</t>
+          <t>短水路</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>37.73</v>
+        <v>46.9</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1525,11 +1527,11 @@
     </row>
     <row r="11">
       <c r="A11" s="11" t="n">
-        <v>46130</v>
+        <v>46075</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>小6</t>
+          <t>小5</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1537,39 +1539,91 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>短水路</t>
+          <t>長水路</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>40.28</v>
+        <v>47.42</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>菰野スイミング</t>
+          <t>鈴鹿</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="11" t="n">
+        <v>46130</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>小6</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>50</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>47.95</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>菰野スイミング</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="11" t="n">
+        <v>46053</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>小5</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>100</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>99.48999999999999</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="11" t="n">
         <v>46152</v>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>小6</t>
         </is>
       </c>
-      <c r="C12" t="n">
-        <v>50</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>36.55</v>
-      </c>
-      <c r="F12" t="inlineStr">
+      <c r="C14" t="n">
+        <v>50</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>45.36</v>
+      </c>
+      <c r="F14" t="inlineStr">
         <is>
           <t>菰野スイミング</t>
         </is>
@@ -1586,7 +1640,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1639,7 +1693,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>58.87</v>
+        <v>47.91</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -1649,7 +1703,7 @@
     </row>
     <row r="3">
       <c r="A3" s="11" t="n">
-        <v>45815</v>
+        <v>45816</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -1665,7 +1719,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>55.01</v>
+        <v>47.54</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1675,7 +1729,7 @@
     </row>
     <row r="4">
       <c r="A4" s="11" t="n">
-        <v>45844</v>
+        <v>45823</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -1687,11 +1741,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>長水路</t>
+          <t>短水路</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>52.08</v>
+        <v>44.48</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1701,7 +1755,7 @@
     </row>
     <row r="5">
       <c r="A5" s="11" t="n">
-        <v>45942</v>
+        <v>45844</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -1717,7 +1771,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>52.97</v>
+        <v>44.39</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1727,7 +1781,7 @@
     </row>
     <row r="6">
       <c r="A6" s="11" t="n">
-        <v>45955</v>
+        <v>45942</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -1739,11 +1793,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>短水路</t>
+          <t>長水路</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>49.74</v>
+        <v>40.39</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1753,7 +1807,7 @@
     </row>
     <row r="7">
       <c r="A7" s="11" t="n">
-        <v>45984</v>
+        <v>45955</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -1765,11 +1819,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>長水路</t>
+          <t>短水路</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>49.06</v>
+        <v>40.5</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1779,7 +1833,7 @@
     </row>
     <row r="8">
       <c r="A8" s="11" t="n">
-        <v>45984</v>
+        <v>46033</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -1787,17 +1841,15 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>長水路</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>1'41"11</t>
-        </is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>39.07</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1807,7 +1859,7 @@
     </row>
     <row r="9">
       <c r="A9" s="11" t="n">
-        <v>46033</v>
+        <v>46053</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1823,7 +1875,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>47.55</v>
+        <v>38.24</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1833,7 +1885,7 @@
     </row>
     <row r="10">
       <c r="A10" s="11" t="n">
-        <v>46053</v>
+        <v>46074</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -1845,11 +1897,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>短水路</t>
+          <t>長水路</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>46.9</v>
+        <v>37.73</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1859,11 +1911,11 @@
     </row>
     <row r="11">
       <c r="A11" s="11" t="n">
-        <v>46075</v>
+        <v>46130</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>小5</t>
+          <t>小6</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1871,21 +1923,21 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>長水路</t>
+          <t>短水路</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>47.42</v>
+        <v>40.28</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>鈴鹿</t>
+          <t>菰野スイミング</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="11" t="n">
-        <v>46130</v>
+        <v>46152</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -1901,63 +1953,11 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>47.95</v>
+        <v>36.55</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>菰野スイミング</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="11" t="n">
-        <v>46053</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>小5</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>100</v>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>99.48999999999999</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="11" t="n">
-        <v>46152</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>小6</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>50</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>45.36</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>菰野スイミング</t>
+          <t>鈴鹿</t>
         </is>
       </c>
     </row>

--- a/穂果記録.xlsx
+++ b/穂果記録.xlsx
@@ -9,8 +9,8 @@
     <sheet name="バッタ" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="バック" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="メドレー" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="ブレ" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="フリー" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="フリー" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="ブレ" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -1254,7 +1254,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1307,7 +1307,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>58.87</v>
+        <v>47.91</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -1317,7 +1317,7 @@
     </row>
     <row r="3">
       <c r="A3" s="11" t="n">
-        <v>45815</v>
+        <v>45816</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -1333,7 +1333,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>55.01</v>
+        <v>47.54</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
     </row>
     <row r="4">
       <c r="A4" s="11" t="n">
-        <v>45844</v>
+        <v>45823</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -1355,11 +1355,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>長水路</t>
+          <t>短水路</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>52.08</v>
+        <v>44.48</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
     </row>
     <row r="5">
       <c r="A5" s="11" t="n">
-        <v>45942</v>
+        <v>45844</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>52.97</v>
+        <v>44.39</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1395,7 +1395,7 @@
     </row>
     <row r="6">
       <c r="A6" s="11" t="n">
-        <v>45955</v>
+        <v>45942</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -1407,11 +1407,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>短水路</t>
+          <t>長水路</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>49.74</v>
+        <v>40.39</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1421,7 +1421,7 @@
     </row>
     <row r="7">
       <c r="A7" s="11" t="n">
-        <v>45984</v>
+        <v>45955</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -1433,11 +1433,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>長水路</t>
+          <t>短水路</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>49.06</v>
+        <v>40.5</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1447,7 +1447,7 @@
     </row>
     <row r="8">
       <c r="A8" s="11" t="n">
-        <v>45984</v>
+        <v>46033</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -1455,17 +1455,15 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>長水路</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>1'41"11</t>
-        </is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>39.07</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1475,7 +1473,7 @@
     </row>
     <row r="9">
       <c r="A9" s="11" t="n">
-        <v>46033</v>
+        <v>46053</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1491,7 +1489,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>47.55</v>
+        <v>38.24</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1501,7 +1499,7 @@
     </row>
     <row r="10">
       <c r="A10" s="11" t="n">
-        <v>46053</v>
+        <v>46074</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -1513,11 +1511,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>短水路</t>
+          <t>長水路</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>46.9</v>
+        <v>37.73</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1527,11 +1525,11 @@
     </row>
     <row r="11">
       <c r="A11" s="11" t="n">
-        <v>46075</v>
+        <v>46130</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>小5</t>
+          <t>小6</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1539,21 +1537,21 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>長水路</t>
+          <t>短水路</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>47.42</v>
+        <v>40.28</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>鈴鹿</t>
+          <t>菰野スイミング</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="11" t="n">
-        <v>46130</v>
+        <v>46152</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -1569,63 +1567,11 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>47.95</v>
+        <v>36.55</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>菰野スイミング</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="11" t="n">
-        <v>46053</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>小5</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>100</v>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>99.48999999999999</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="11" t="n">
-        <v>46152</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>小6</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>50</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>45.36</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>菰野スイミング</t>
+          <t>鈴鹿</t>
         </is>
       </c>
     </row>
@@ -1640,7 +1586,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1693,7 +1639,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>47.91</v>
+        <v>58.87</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -1703,7 +1649,7 @@
     </row>
     <row r="3">
       <c r="A3" s="11" t="n">
-        <v>45816</v>
+        <v>45815</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -1719,7 +1665,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>47.54</v>
+        <v>55.01</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1729,7 +1675,7 @@
     </row>
     <row r="4">
       <c r="A4" s="11" t="n">
-        <v>45823</v>
+        <v>45844</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -1741,11 +1687,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>短水路</t>
+          <t>長水路</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>44.48</v>
+        <v>52.08</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1755,7 +1701,7 @@
     </row>
     <row r="5">
       <c r="A5" s="11" t="n">
-        <v>45844</v>
+        <v>45942</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -1771,7 +1717,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>44.39</v>
+        <v>52.97</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1781,7 +1727,7 @@
     </row>
     <row r="6">
       <c r="A6" s="11" t="n">
-        <v>45942</v>
+        <v>45955</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -1793,11 +1739,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>長水路</t>
+          <t>短水路</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>40.39</v>
+        <v>49.74</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1807,7 +1753,7 @@
     </row>
     <row r="7">
       <c r="A7" s="11" t="n">
-        <v>45955</v>
+        <v>45984</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -1819,11 +1765,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>短水路</t>
+          <t>長水路</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>40.5</v>
+        <v>49.06</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1833,7 +1779,7 @@
     </row>
     <row r="8">
       <c r="A8" s="11" t="n">
-        <v>46033</v>
+        <v>45984</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -1841,15 +1787,17 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>39.07</v>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>1'41"11</t>
+        </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1859,7 +1807,7 @@
     </row>
     <row r="9">
       <c r="A9" s="11" t="n">
-        <v>46053</v>
+        <v>46033</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1875,7 +1823,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>38.24</v>
+        <v>47.55</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1885,7 +1833,7 @@
     </row>
     <row r="10">
       <c r="A10" s="11" t="n">
-        <v>46074</v>
+        <v>46053</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -1897,11 +1845,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>長水路</t>
+          <t>短水路</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>37.73</v>
+        <v>46.9</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1911,11 +1859,11 @@
     </row>
     <row r="11">
       <c r="A11" s="11" t="n">
-        <v>46130</v>
+        <v>46075</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>小6</t>
+          <t>小5</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1923,41 +1871,93 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>短水路</t>
+          <t>長水路</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>40.28</v>
+        <v>47.42</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>菰野スイミング</t>
+          <t>鈴鹿</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="11" t="n">
+        <v>46130</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>小6</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>50</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>47.95</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>菰野スイミング</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="11" t="n">
+        <v>46053</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>小5</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>100</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>99.48999999999999</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="11" t="n">
         <v>46152</v>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>小6</t>
         </is>
       </c>
-      <c r="C12" t="n">
-        <v>50</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>36.55</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
+      <c r="C14" t="n">
+        <v>50</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>45.36</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>菰野スイミング</t>
         </is>
       </c>
     </row>

--- a/穂果記録.xlsx
+++ b/穂果記録.xlsx
@@ -1957,7 +1957,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>菰野スイミング</t>
+          <t>鈴鹿</t>
         </is>
       </c>
     </row>

--- a/穂果記録.xlsx
+++ b/穂果記録.xlsx
@@ -1586,7 +1586,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1961,6 +1961,32 @@
         </is>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" s="11" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>小6</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>100</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>95.26000000000001</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/穂果記録.xlsx
+++ b/穂果記録.xlsx
@@ -1979,7 +1979,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>95.26000000000001</v>
+        <v>95.04000000000001</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>

--- a/穂果記録.xlsx
+++ b/穂果記録.xlsx
@@ -8,9 +8,9 @@
   <sheets>
     <sheet name="バッタ" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="バック" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="メドレー" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="フリー" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="ブレ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="フリー" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="ブレ" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="メドレー" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -1042,7 +1042,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1079,35 +1079,33 @@
     </row>
     <row r="2">
       <c r="A2" s="11" t="n">
-        <v>45710</v>
+        <v>45788</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>小4</t>
+          <t>小5</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
           <t>短水路</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>4'43"09</t>
-        </is>
+      <c r="E2" t="n">
+        <v>47.91</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>菰野スイミング</t>
+          <t>鈴鹿</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="11" t="n">
-        <v>45808</v>
+        <v>45816</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -1115,27 +1113,25 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>4'02"71</t>
-        </is>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>47.54</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>菰野スイミング</t>
+          <t>鈴鹿</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="11" t="n">
-        <v>45899</v>
+        <v>45823</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -1143,27 +1139,25 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
           <t>短水路</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>3'37"53</t>
-        </is>
+      <c r="E4" t="n">
+        <v>44.48</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>菰野スイミング</t>
+          <t>鈴鹿</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="11" t="n">
-        <v>45991</v>
+        <v>45844</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -1171,27 +1165,25 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>3'21"34</t>
-        </is>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>44.39</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>菰野スイミング</t>
+          <t>鈴鹿</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="11" t="n">
-        <v>46081</v>
+        <v>45942</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -1199,47 +1191,175 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>3'14"47</t>
-        </is>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>40.39</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>菰野スイミング</t>
+          <t>鈴鹿</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="11" t="n">
-        <v>46145</v>
+        <v>45955</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>小5</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>50</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>40.5</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="11" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>小5</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>50</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>39.07</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="11" t="n">
+        <v>46053</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>小5</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>50</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>38.24</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="11" t="n">
+        <v>46074</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>小5</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>50</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>37.73</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="11" t="n">
+        <v>46130</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
           <t>小6</t>
         </is>
       </c>
-      <c r="C7" t="n">
-        <v>50</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>173.24</v>
-      </c>
-      <c r="F7" t="inlineStr">
+      <c r="C11" t="n">
+        <v>50</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>40.28</v>
+      </c>
+      <c r="F11" t="inlineStr">
         <is>
           <t>菰野スイミング</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="11" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>小6</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>50</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>36.55</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
         </is>
       </c>
     </row>
@@ -1254,7 +1374,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1307,7 +1427,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>47.91</v>
+        <v>58.87</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -1317,7 +1437,7 @@
     </row>
     <row r="3">
       <c r="A3" s="11" t="n">
-        <v>45816</v>
+        <v>45815</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -1333,7 +1453,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>47.54</v>
+        <v>55.01</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1343,7 +1463,7 @@
     </row>
     <row r="4">
       <c r="A4" s="11" t="n">
-        <v>45823</v>
+        <v>45844</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -1355,11 +1475,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>短水路</t>
+          <t>長水路</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>44.48</v>
+        <v>52.08</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1369,7 +1489,7 @@
     </row>
     <row r="5">
       <c r="A5" s="11" t="n">
-        <v>45844</v>
+        <v>45942</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -1385,7 +1505,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>44.39</v>
+        <v>52.97</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1395,7 +1515,7 @@
     </row>
     <row r="6">
       <c r="A6" s="11" t="n">
-        <v>45942</v>
+        <v>45955</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -1407,11 +1527,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>長水路</t>
+          <t>短水路</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>40.39</v>
+        <v>49.74</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1421,7 +1541,7 @@
     </row>
     <row r="7">
       <c r="A7" s="11" t="n">
-        <v>45955</v>
+        <v>45984</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -1433,11 +1553,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>短水路</t>
+          <t>長水路</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>40.5</v>
+        <v>49.06</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1447,7 +1567,7 @@
     </row>
     <row r="8">
       <c r="A8" s="11" t="n">
-        <v>46033</v>
+        <v>45984</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -1455,15 +1575,17 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>39.07</v>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>1'41"11</t>
+        </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1473,7 +1595,7 @@
     </row>
     <row r="9">
       <c r="A9" s="11" t="n">
-        <v>46053</v>
+        <v>46033</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1489,7 +1611,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>38.24</v>
+        <v>47.55</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1499,7 +1621,7 @@
     </row>
     <row r="10">
       <c r="A10" s="11" t="n">
-        <v>46074</v>
+        <v>46053</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -1511,11 +1633,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>長水路</t>
+          <t>短水路</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>37.73</v>
+        <v>46.9</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1525,11 +1647,11 @@
     </row>
     <row r="11">
       <c r="A11" s="11" t="n">
-        <v>46130</v>
+        <v>46075</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>小6</t>
+          <t>小5</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1537,39 +1659,117 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>短水路</t>
+          <t>長水路</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>40.28</v>
+        <v>47.42</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>菰野スイミング</t>
+          <t>鈴鹿</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="11" t="n">
+        <v>46130</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>小6</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>50</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>47.95</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>菰野スイミング</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="11" t="n">
+        <v>46053</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>小5</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>100</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>99.48999999999999</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="11" t="n">
         <v>46152</v>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>小6</t>
         </is>
       </c>
-      <c r="C12" t="n">
-        <v>50</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>36.55</v>
-      </c>
-      <c r="F12" t="inlineStr">
+      <c r="C14" t="n">
+        <v>50</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>45.36</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="11" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>小6</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>100</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>95.04000000000001</v>
+      </c>
+      <c r="F15" t="inlineStr">
         <is>
           <t>鈴鹿</t>
         </is>
@@ -1586,7 +1786,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1623,33 +1823,35 @@
     </row>
     <row r="2">
       <c r="A2" s="11" t="n">
-        <v>45788</v>
+        <v>45710</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>小5</t>
+          <t>小4</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
           <t>短水路</t>
         </is>
       </c>
-      <c r="E2" t="n">
-        <v>58.87</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>4'43"09</t>
+        </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>鈴鹿</t>
+          <t>菰野スイミング</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="11" t="n">
-        <v>45815</v>
+        <v>45808</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -1657,25 +1859,27 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>長水路</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>55.01</v>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>4'02"71</t>
+        </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>鈴鹿</t>
+          <t>菰野スイミング</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="11" t="n">
-        <v>45844</v>
+        <v>45899</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -1683,25 +1887,27 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>長水路</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>52.08</v>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>3'37"53</t>
+        </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>鈴鹿</t>
+          <t>菰野スイミング</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="11" t="n">
-        <v>45942</v>
+        <v>45991</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -1709,25 +1915,27 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>長水路</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>52.97</v>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>3'21"34</t>
+        </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>鈴鹿</t>
+          <t>菰野スイミング</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="11" t="n">
-        <v>45955</v>
+        <v>46081</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -1735,29 +1943,31 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
           <t>短水路</t>
         </is>
       </c>
-      <c r="E6" t="n">
-        <v>49.74</v>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>3'14"47</t>
+        </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>鈴鹿</t>
+          <t>菰野スイミング</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="11" t="n">
-        <v>45984</v>
+        <v>46145</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>小5</t>
+          <t>小6</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -1765,225 +1975,41 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>長水路</t>
+          <t>短水路</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>49.06</v>
+        <v>173.24</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>鈴鹿</t>
+          <t>菰野スイミング</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="11" t="n">
-        <v>45984</v>
+        <v>46172</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>小5</t>
+          <t>小6</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>長水路</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>1'41"11</t>
-        </is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>193.81</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="11" t="n">
-        <v>46033</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>小5</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>50</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>47.55</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="11" t="n">
-        <v>46053</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>小5</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>50</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>46.9</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="11" t="n">
-        <v>46075</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>小5</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>50</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>長水路</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>47.42</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="11" t="n">
-        <v>46130</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>小6</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>50</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>47.95</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
           <t>菰野スイミング</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="11" t="n">
-        <v>46053</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>小5</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>100</v>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>99.48999999999999</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="11" t="n">
-        <v>46152</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>小6</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>50</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>45.36</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="11" t="n">
-        <v>46152</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>小6</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>100</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>95.04000000000001</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
         </is>
       </c>
     </row>

--- a/穂果記録.xlsx
+++ b/穂果記録.xlsx
@@ -9,8 +9,8 @@
     <sheet name="バッタ" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="バック" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="フリー" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="ブレ" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="メドレー" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="メドレー" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="ブレ" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -1374,7 +1374,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1411,33 +1411,35 @@
     </row>
     <row r="2">
       <c r="A2" s="11" t="n">
-        <v>45788</v>
+        <v>45710</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>小5</t>
+          <t>小4</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
           <t>短水路</t>
         </is>
       </c>
-      <c r="E2" t="n">
-        <v>58.87</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>4'43"09</t>
+        </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>鈴鹿</t>
+          <t>菰野スイミング</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="11" t="n">
-        <v>45815</v>
+        <v>45808</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -1445,25 +1447,27 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>長水路</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>55.01</v>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>4'02"71</t>
+        </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>鈴鹿</t>
+          <t>菰野スイミング</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="11" t="n">
-        <v>45844</v>
+        <v>45899</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -1471,25 +1475,27 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>長水路</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>52.08</v>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>3'37"53</t>
+        </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>鈴鹿</t>
+          <t>菰野スイミング</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="11" t="n">
-        <v>45942</v>
+        <v>45991</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -1497,25 +1503,27 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>長水路</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>52.97</v>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>3'21"34</t>
+        </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>鈴鹿</t>
+          <t>菰野スイミング</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="11" t="n">
-        <v>45955</v>
+        <v>46081</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -1523,29 +1531,31 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
           <t>短水路</t>
         </is>
       </c>
-      <c r="E6" t="n">
-        <v>49.74</v>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>3'14"47</t>
+        </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>鈴鹿</t>
+          <t>菰野スイミング</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="11" t="n">
-        <v>45984</v>
+        <v>46145</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>小5</t>
+          <t>小6</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -1553,225 +1563,41 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>長水路</t>
+          <t>短水路</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>49.06</v>
+        <v>173.24</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>鈴鹿</t>
+          <t>菰野スイミング</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="11" t="n">
-        <v>45984</v>
+        <v>46172</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>小5</t>
+          <t>小6</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>長水路</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>1'41"11</t>
-        </is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>193.81</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="11" t="n">
-        <v>46033</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>小5</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>50</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>47.55</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="11" t="n">
-        <v>46053</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>小5</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>50</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>46.9</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="11" t="n">
-        <v>46075</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>小5</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>50</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>長水路</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>47.42</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="11" t="n">
-        <v>46130</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>小6</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>50</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>47.95</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
           <t>菰野スイミング</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="11" t="n">
-        <v>46053</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>小5</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>100</v>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>99.48999999999999</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="11" t="n">
-        <v>46152</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>小6</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>50</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>45.36</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="11" t="n">
-        <v>46152</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>小6</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>100</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>95.04000000000001</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
         </is>
       </c>
     </row>
@@ -1786,7 +1612,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1823,35 +1649,33 @@
     </row>
     <row r="2">
       <c r="A2" s="11" t="n">
-        <v>45710</v>
+        <v>45788</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>小4</t>
+          <t>小5</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
           <t>短水路</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>4'43"09</t>
-        </is>
+      <c r="E2" t="n">
+        <v>58.87</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>菰野スイミング</t>
+          <t>鈴鹿</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="11" t="n">
-        <v>45808</v>
+        <v>45815</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -1859,27 +1683,25 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>4'02"71</t>
-        </is>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>55.01</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>菰野スイミング</t>
+          <t>鈴鹿</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="11" t="n">
-        <v>45899</v>
+        <v>45844</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -1887,27 +1709,25 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>3'37"53</t>
-        </is>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>52.08</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>菰野スイミング</t>
+          <t>鈴鹿</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="11" t="n">
-        <v>45991</v>
+        <v>45942</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -1915,27 +1735,25 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>3'21"34</t>
-        </is>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>52.97</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>菰野スイミング</t>
+          <t>鈴鹿</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="11" t="n">
-        <v>46081</v>
+        <v>45955</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -1943,31 +1761,29 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
           <t>短水路</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>3'14"47</t>
-        </is>
+      <c r="E6" t="n">
+        <v>49.74</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>菰野スイミング</t>
+          <t>鈴鹿</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="11" t="n">
-        <v>46145</v>
+        <v>45984</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>小6</t>
+          <t>小5</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -1975,41 +1791,251 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>短水路</t>
+          <t>長水路</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>173.24</v>
+        <v>49.06</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>菰野スイミング</t>
+          <t>鈴鹿</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="11" t="n">
-        <v>46172</v>
+        <v>45984</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
+          <t>小5</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>100</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>1'41"11</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="11" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>小5</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>50</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>47.55</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="11" t="n">
+        <v>46053</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>小5</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>50</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>46.9</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="11" t="n">
+        <v>46075</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>小5</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>50</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>47.42</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="11" t="n">
+        <v>46130</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
           <t>小6</t>
         </is>
       </c>
-      <c r="C8" t="n">
-        <v>200</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>193.81</v>
-      </c>
-      <c r="F8" t="inlineStr">
+      <c r="C12" t="n">
+        <v>50</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>47.95</v>
+      </c>
+      <c r="F12" t="inlineStr">
         <is>
           <t>菰野スイミング</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="11" t="n">
+        <v>46053</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>小5</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>100</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>99.48999999999999</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="11" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>小6</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>50</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>45.36</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="11" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>小6</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>100</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>95.04000000000001</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="11" t="n">
+        <v>46179</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>小6</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>100</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100.1</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
         </is>
       </c>
     </row>

--- a/穂果記録.xlsx
+++ b/穂果記録.xlsx
@@ -1612,7 +1612,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2039,6 +2039,32 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" s="11" t="n">
+        <v>46180</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>小6</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>50</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>46.87</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/穂果記録.xlsx
+++ b/穂果記録.xlsx
@@ -1612,7 +1612,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2065,6 +2065,32 @@
         </is>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" s="11" t="n">
+        <v>46187</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>小6</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>50</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/穂果記録.xlsx
+++ b/穂果記録.xlsx
@@ -2083,7 +2083,7 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.11</v>
+        <v>45.11</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>

--- a/穂果記録.xlsx
+++ b/穂果記録.xlsx
@@ -8,9 +8,9 @@
   <sheets>
     <sheet name="バッタ" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="バック" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="フリー" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="メドレー" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="ブレ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="メドレー" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="ブレ" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="フリー" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -1042,7 +1042,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1079,33 +1079,35 @@
     </row>
     <row r="2">
       <c r="A2" s="11" t="n">
-        <v>45788</v>
+        <v>45710</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>小5</t>
+          <t>小4</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
           <t>短水路</t>
         </is>
       </c>
-      <c r="E2" t="n">
-        <v>47.91</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>4'43"09</t>
+        </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>鈴鹿</t>
+          <t>菰野スイミング</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="11" t="n">
-        <v>45816</v>
+        <v>45808</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -1113,25 +1115,27 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>長水路</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>47.54</v>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>4'02"71</t>
+        </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>鈴鹿</t>
+          <t>菰野スイミング</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="11" t="n">
-        <v>45823</v>
+        <v>45899</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -1139,25 +1143,27 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
           <t>短水路</t>
         </is>
       </c>
-      <c r="E4" t="n">
-        <v>44.48</v>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>3'37"53</t>
+        </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>鈴鹿</t>
+          <t>菰野スイミング</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="11" t="n">
-        <v>45844</v>
+        <v>45991</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -1165,25 +1171,27 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>長水路</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>44.39</v>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>3'21"34</t>
+        </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>鈴鹿</t>
+          <t>菰野スイミング</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="11" t="n">
-        <v>45942</v>
+        <v>46081</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -1191,29 +1199,31 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>長水路</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>40.39</v>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>3'14"47</t>
+        </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>鈴鹿</t>
+          <t>菰野スイミング</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="11" t="n">
-        <v>45955</v>
+        <v>46145</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>小5</t>
+          <t>小6</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -1225,25 +1235,25 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>40.5</v>
+        <v>173.24</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>鈴鹿</t>
+          <t>菰野スイミング</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="11" t="n">
-        <v>46033</v>
+        <v>46172</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>小5</t>
+          <t>小6</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1251,115 +1261,11 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>39.07</v>
+        <v>193.81</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="11" t="n">
-        <v>46053</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>小5</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>50</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>38.24</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="11" t="n">
-        <v>46074</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>小5</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>50</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>長水路</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>37.73</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="11" t="n">
-        <v>46130</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>小6</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>50</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>40.28</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
           <t>菰野スイミング</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="11" t="n">
-        <v>46152</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>小6</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>50</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>36.55</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
         </is>
       </c>
     </row>
@@ -1374,7 +1280,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1411,35 +1317,33 @@
     </row>
     <row r="2">
       <c r="A2" s="11" t="n">
-        <v>45710</v>
+        <v>45788</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>小4</t>
+          <t>小5</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
           <t>短水路</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>4'43"09</t>
-        </is>
+      <c r="E2" t="n">
+        <v>58.87</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>菰野スイミング</t>
+          <t>鈴鹿</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="11" t="n">
-        <v>45808</v>
+        <v>45815</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -1447,27 +1351,25 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>4'02"71</t>
-        </is>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>55.01</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>菰野スイミング</t>
+          <t>鈴鹿</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="11" t="n">
-        <v>45899</v>
+        <v>45844</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -1475,27 +1377,25 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>3'37"53</t>
-        </is>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>52.08</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>菰野スイミング</t>
+          <t>鈴鹿</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="11" t="n">
-        <v>45991</v>
+        <v>45942</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -1503,27 +1403,25 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>3'21"34</t>
-        </is>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>52.97</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>菰野スイミング</t>
+          <t>鈴鹿</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="11" t="n">
-        <v>46081</v>
+        <v>45955</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -1531,31 +1429,29 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
           <t>短水路</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>3'14"47</t>
-        </is>
+      <c r="E6" t="n">
+        <v>49.74</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>菰野スイミング</t>
+          <t>鈴鹿</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="11" t="n">
-        <v>46145</v>
+        <v>45984</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>小6</t>
+          <t>小5</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -1563,41 +1459,303 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>短水路</t>
+          <t>長水路</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>173.24</v>
+        <v>49.06</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>菰野スイミング</t>
+          <t>鈴鹿</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="11" t="n">
-        <v>46172</v>
+        <v>45984</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
+          <t>小5</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>100</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>1'41"11</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="11" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>小5</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>50</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>47.55</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="11" t="n">
+        <v>46053</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>小5</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>50</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>46.9</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="11" t="n">
+        <v>46075</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>小5</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>50</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>47.42</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="11" t="n">
+        <v>46130</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
           <t>小6</t>
         </is>
       </c>
-      <c r="C8" t="n">
-        <v>200</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>193.81</v>
-      </c>
-      <c r="F8" t="inlineStr">
+      <c r="C12" t="n">
+        <v>50</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>47.95</v>
+      </c>
+      <c r="F12" t="inlineStr">
         <is>
           <t>菰野スイミング</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="11" t="n">
+        <v>46053</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>小5</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>100</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>99.48999999999999</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="11" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>小6</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>50</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>45.36</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="11" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>小6</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>100</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>95.04000000000001</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="11" t="n">
+        <v>46179</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>小6</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>100</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100.1</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="11" t="n">
+        <v>46180</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>小6</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>50</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>46.87</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="11" t="n">
+        <v>46187</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>小6</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>50</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>45.11</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
         </is>
       </c>
     </row>
@@ -1612,7 +1770,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1665,7 +1823,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>58.87</v>
+        <v>47.91</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -1675,7 +1833,7 @@
     </row>
     <row r="3">
       <c r="A3" s="11" t="n">
-        <v>45815</v>
+        <v>45816</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -1691,7 +1849,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>55.01</v>
+        <v>47.54</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1701,7 +1859,7 @@
     </row>
     <row r="4">
       <c r="A4" s="11" t="n">
-        <v>45844</v>
+        <v>45823</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -1713,11 +1871,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>長水路</t>
+          <t>短水路</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>52.08</v>
+        <v>44.48</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1727,7 +1885,7 @@
     </row>
     <row r="5">
       <c r="A5" s="11" t="n">
-        <v>45942</v>
+        <v>45844</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -1743,7 +1901,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>52.97</v>
+        <v>44.39</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1753,7 +1911,7 @@
     </row>
     <row r="6">
       <c r="A6" s="11" t="n">
-        <v>45955</v>
+        <v>45942</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -1765,11 +1923,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>短水路</t>
+          <t>長水路</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>49.74</v>
+        <v>40.39</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1779,7 +1937,7 @@
     </row>
     <row r="7">
       <c r="A7" s="11" t="n">
-        <v>45984</v>
+        <v>45955</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -1791,11 +1949,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>長水路</t>
+          <t>短水路</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>49.06</v>
+        <v>40.5</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1805,7 +1963,7 @@
     </row>
     <row r="8">
       <c r="A8" s="11" t="n">
-        <v>45984</v>
+        <v>46033</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -1813,17 +1971,15 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>長水路</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>1'41"11</t>
-        </is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>39.07</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1833,7 +1989,7 @@
     </row>
     <row r="9">
       <c r="A9" s="11" t="n">
-        <v>46033</v>
+        <v>46053</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1849,7 +2005,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>47.55</v>
+        <v>38.24</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1859,7 +2015,7 @@
     </row>
     <row r="10">
       <c r="A10" s="11" t="n">
-        <v>46053</v>
+        <v>46074</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -1871,11 +2027,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>短水路</t>
+          <t>長水路</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>46.9</v>
+        <v>37.73</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1885,11 +2041,11 @@
     </row>
     <row r="11">
       <c r="A11" s="11" t="n">
-        <v>46075</v>
+        <v>46130</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>小5</t>
+          <t>小6</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1897,21 +2053,21 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>長水路</t>
+          <t>短水路</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>47.42</v>
+        <v>40.28</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>鈴鹿</t>
+          <t>菰野スイミング</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="11" t="n">
-        <v>46130</v>
+        <v>46152</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -1927,25 +2083,25 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>47.95</v>
+        <v>36.55</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>菰野スイミング</t>
+          <t>鈴鹿</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="11" t="n">
-        <v>46053</v>
+        <v>46187</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>小5</t>
+          <t>小6</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1953,139 +2109,9 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>99.48999999999999</v>
+        <v>96.61</v>
       </c>
       <c r="F13" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="11" t="n">
-        <v>46152</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>小6</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>50</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>45.36</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="11" t="n">
-        <v>46152</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>小6</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>100</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>95.04000000000001</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="11" t="n">
-        <v>46179</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>小6</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>100</v>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>長水路</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>100.1</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="11" t="n">
-        <v>46180</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>小6</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>50</v>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>長水路</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>46.87</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="11" t="n">
-        <v>46187</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>小6</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>50</v>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>45.11</v>
-      </c>
-      <c r="F18" t="inlineStr">
         <is>
           <t>鈴鹿</t>
         </is>

--- a/穂果記録.xlsx
+++ b/穂果記録.xlsx
@@ -1770,7 +1770,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2117,6 +2117,32 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" s="11" t="n">
+        <v>46187</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>小6</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>50</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>96.61</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/穂果記録.xlsx
+++ b/穂果記録.xlsx
@@ -1770,7 +1770,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2143,6 +2143,32 @@
         </is>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" s="11" t="n">
+        <v>46187</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>小6</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>50</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>96.61</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/穂果記録.xlsx
+++ b/穂果記録.xlsx
@@ -1770,7 +1770,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2143,32 +2143,6 @@
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="11" t="n">
-        <v>46187</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>小6</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>50</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>96.61</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/穂果記録.xlsx
+++ b/穂果記録.xlsx
@@ -1770,7 +1770,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2117,32 +2117,6 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="11" t="n">
-        <v>46187</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>小6</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>50</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>96.61</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/穂果記録.xlsx
+++ b/穂果記録.xlsx
@@ -1770,7 +1770,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2091,32 +2091,6 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="11" t="n">
-        <v>46187</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>小6</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>50</v>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>96.61</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/穂果記録.xlsx
+++ b/穂果記録.xlsx
@@ -9,8 +9,8 @@
     <sheet name="バッタ" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="バック" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="メドレー" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="ブレ" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="フリー" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="フリー" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="ブレ" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -1280,7 +1280,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1333,7 +1333,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>58.87</v>
+        <v>47.91</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
     </row>
     <row r="3">
       <c r="A3" s="11" t="n">
-        <v>45815</v>
+        <v>45816</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>55.01</v>
+        <v>47.54</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
     </row>
     <row r="4">
       <c r="A4" s="11" t="n">
-        <v>45844</v>
+        <v>45823</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -1381,11 +1381,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>長水路</t>
+          <t>短水路</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>52.08</v>
+        <v>44.48</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1395,7 +1395,7 @@
     </row>
     <row r="5">
       <c r="A5" s="11" t="n">
-        <v>45942</v>
+        <v>45844</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -1411,7 +1411,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>52.97</v>
+        <v>44.39</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1421,7 +1421,7 @@
     </row>
     <row r="6">
       <c r="A6" s="11" t="n">
-        <v>45955</v>
+        <v>45942</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -1433,11 +1433,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>短水路</t>
+          <t>長水路</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>49.74</v>
+        <v>40.39</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1447,7 +1447,7 @@
     </row>
     <row r="7">
       <c r="A7" s="11" t="n">
-        <v>45984</v>
+        <v>45955</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -1459,11 +1459,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>長水路</t>
+          <t>短水路</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>49.06</v>
+        <v>40.5</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1473,7 +1473,7 @@
     </row>
     <row r="8">
       <c r="A8" s="11" t="n">
-        <v>45984</v>
+        <v>46033</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -1481,17 +1481,15 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>長水路</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>1'41"11</t>
-        </is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>39.07</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1501,7 +1499,7 @@
     </row>
     <row r="9">
       <c r="A9" s="11" t="n">
-        <v>46033</v>
+        <v>46053</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1517,7 +1515,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>47.55</v>
+        <v>38.24</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1527,7 +1525,7 @@
     </row>
     <row r="10">
       <c r="A10" s="11" t="n">
-        <v>46053</v>
+        <v>46074</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -1539,11 +1537,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>短水路</t>
+          <t>長水路</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>46.9</v>
+        <v>37.73</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1553,11 +1551,11 @@
     </row>
     <row r="11">
       <c r="A11" s="11" t="n">
-        <v>46075</v>
+        <v>46130</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>小5</t>
+          <t>小6</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1565,21 +1563,21 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>長水路</t>
+          <t>短水路</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>47.42</v>
+        <v>40.28</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>鈴鹿</t>
+          <t>菰野スイミング</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="11" t="n">
-        <v>46130</v>
+        <v>46152</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -1595,165 +1593,9 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>47.95</v>
+        <v>36.55</v>
       </c>
       <c r="F12" t="inlineStr">
-        <is>
-          <t>菰野スイミング</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="11" t="n">
-        <v>46053</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>小5</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>100</v>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>99.48999999999999</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="11" t="n">
-        <v>46152</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>小6</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>50</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>45.36</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="11" t="n">
-        <v>46152</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>小6</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>100</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>95.04000000000001</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="11" t="n">
-        <v>46179</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>小6</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>100</v>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>長水路</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>100.1</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="11" t="n">
-        <v>46180</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>小6</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>50</v>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>長水路</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>46.87</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="11" t="n">
-        <v>46187</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>小6</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>50</v>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>45.11</v>
-      </c>
-      <c r="F18" t="inlineStr">
         <is>
           <t>鈴鹿</t>
         </is>
@@ -1770,7 +1612,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1823,7 +1665,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>47.91</v>
+        <v>58.87</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -1833,7 +1675,7 @@
     </row>
     <row r="3">
       <c r="A3" s="11" t="n">
-        <v>45816</v>
+        <v>45815</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -1849,7 +1691,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>47.54</v>
+        <v>55.01</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1859,7 +1701,7 @@
     </row>
     <row r="4">
       <c r="A4" s="11" t="n">
-        <v>45823</v>
+        <v>45844</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -1871,11 +1713,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>短水路</t>
+          <t>長水路</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>44.48</v>
+        <v>52.08</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1885,7 +1727,7 @@
     </row>
     <row r="5">
       <c r="A5" s="11" t="n">
-        <v>45844</v>
+        <v>45942</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -1901,7 +1743,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>44.39</v>
+        <v>52.97</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1911,7 +1753,7 @@
     </row>
     <row r="6">
       <c r="A6" s="11" t="n">
-        <v>45942</v>
+        <v>45955</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -1923,11 +1765,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>長水路</t>
+          <t>短水路</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>40.39</v>
+        <v>49.74</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1937,7 +1779,7 @@
     </row>
     <row r="7">
       <c r="A7" s="11" t="n">
-        <v>45955</v>
+        <v>45984</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -1949,11 +1791,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>短水路</t>
+          <t>長水路</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>40.5</v>
+        <v>49.06</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1963,7 +1805,7 @@
     </row>
     <row r="8">
       <c r="A8" s="11" t="n">
-        <v>46033</v>
+        <v>45984</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -1971,15 +1813,17 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>39.07</v>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>1'41"11</t>
+        </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1989,7 +1833,7 @@
     </row>
     <row r="9">
       <c r="A9" s="11" t="n">
-        <v>46053</v>
+        <v>46033</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -2005,7 +1849,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>38.24</v>
+        <v>47.55</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -2015,7 +1859,7 @@
     </row>
     <row r="10">
       <c r="A10" s="11" t="n">
-        <v>46074</v>
+        <v>46053</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -2027,11 +1871,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>長水路</t>
+          <t>短水路</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>37.73</v>
+        <v>46.9</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -2041,11 +1885,11 @@
     </row>
     <row r="11">
       <c r="A11" s="11" t="n">
-        <v>46130</v>
+        <v>46075</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>小6</t>
+          <t>小5</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -2053,39 +1897,221 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>短水路</t>
+          <t>長水路</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>40.28</v>
+        <v>47.42</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>菰野スイミング</t>
+          <t>鈴鹿</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="11" t="n">
+        <v>46130</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>小6</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>50</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>47.95</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>菰野スイミング</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="11" t="n">
+        <v>46053</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>小5</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>100</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>99.48999999999999</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="11" t="n">
         <v>46152</v>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>小6</t>
         </is>
       </c>
-      <c r="C12" t="n">
-        <v>50</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>36.55</v>
-      </c>
-      <c r="F12" t="inlineStr">
+      <c r="C14" t="n">
+        <v>50</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>45.36</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="11" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>小6</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>100</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>95.04000000000001</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="11" t="n">
+        <v>46179</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>小6</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>100</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100.1</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="11" t="n">
+        <v>46180</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>小6</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>50</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>46.87</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="11" t="n">
+        <v>46187</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>小6</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>50</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>45.11</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="11" t="n">
+        <v>46187</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>小6</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>100</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>96.61</v>
+      </c>
+      <c r="F19" t="inlineStr">
         <is>
           <t>鈴鹿</t>
         </is>

--- a/穂果記録.xlsx
+++ b/穂果記録.xlsx
@@ -6,11 +6,11 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="2304" yWindow="2304" windowWidth="13716" windowHeight="9960" tabRatio="600" firstSheet="0" activeTab="4" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="バッタ" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="バック" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="メドレー" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="フリー" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="ブレ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="バック" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="メドレー" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="フリー" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="ブレ" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="バッタ" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -450,262 +450,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L6"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="14.8984375" defaultRowHeight="14.4"/>
-  <cols>
-    <col width="15.796875" bestFit="1" customWidth="1" style="9" min="1" max="1"/>
-    <col width="14.8984375" customWidth="1" style="1" min="2" max="15"/>
-    <col width="9.8984375" customWidth="1" style="1" min="16" max="16"/>
-    <col width="14.8984375" customWidth="1" style="1" min="17" max="16384"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>日付</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>学年</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>距離</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>長水路 or 短水路</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>タイム</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>会場</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>50m ベストタイム(短水路)</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>50m 更新日</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>50m ベストタイム(長水路)</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>50m 更新日</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="5" t="n">
-        <v>45823</v>
-      </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t>小5</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="n">
-        <v>50</v>
-      </c>
-      <c r="D2" s="1" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E2" s="1" t="n">
-        <v>54.97</v>
-      </c>
-      <c r="F2" s="1" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-      <c r="G2" s="1">
-        <f>_xlfn.MINIFS(E:E, C:C, 50, D:D, "短水路")</f>
-        <v/>
-      </c>
-      <c r="H2" s="5">
-        <f>INDEX(A:A, MATCH(_xlfn.MINIFS(E:E, D:D, "短水路"), E:E, 0))</f>
-        <v/>
-      </c>
-      <c r="I2" s="1">
-        <f>_xlfn.MINIFS(E:E, C:C, 50, D:D, "長水路")</f>
-        <v/>
-      </c>
-      <c r="J2" s="5">
-        <f>INDEX(A:A, MATCH(_xlfn.MINIFS(E:E, D:D, "長水路"), E:E, 0))</f>
-        <v/>
-      </c>
-      <c r="L2" s="1" t="inlineStr">
-        <is>
-          <t>長水路</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="5" t="n">
-        <v>45956</v>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>小5</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="n">
-        <v>50</v>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t>長水路</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="n">
-        <v>48.27</v>
-      </c>
-      <c r="F3" s="1" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="n"/>
-      <c r="L3" s="1" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="5" t="n">
-        <v>46033</v>
-      </c>
-      <c r="B4" s="1" t="inlineStr">
-        <is>
-          <t>小5</t>
-        </is>
-      </c>
-      <c r="C4" s="1" t="n">
-        <v>50</v>
-      </c>
-      <c r="D4" s="1" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E4" s="1" t="n">
-        <v>44.97</v>
-      </c>
-      <c r="F4" s="1" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="n">
-        <v>46075</v>
-      </c>
-      <c r="B5" s="1" t="inlineStr">
-        <is>
-          <t>小5</t>
-        </is>
-      </c>
-      <c r="C5" s="1" t="n">
-        <v>50</v>
-      </c>
-      <c r="D5" s="1" t="inlineStr">
-        <is>
-          <t>長水路</t>
-        </is>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>44.65</v>
-      </c>
-      <c r="F5" s="1" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-      <c r="L5" s="1" t="inlineStr">
-        <is>
-          <t>菰野スイミング</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="n">
-        <v>46130</v>
-      </c>
-      <c r="B6" s="1" t="inlineStr">
-        <is>
-          <t>小6</t>
-        </is>
-      </c>
-      <c r="C6" s="1" t="n">
-        <v>50</v>
-      </c>
-      <c r="D6" s="1" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>47.17</v>
-      </c>
-      <c r="F6" s="1" t="inlineStr">
-        <is>
-          <t>菰野スイミング</t>
-        </is>
-      </c>
-      <c r="L6" s="1" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <dataValidations count="5">
-    <dataValidation sqref="D7:D178" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
-      <formula1>#REF!</formula1>
-    </dataValidation>
-    <dataValidation sqref="F7:F132" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
-      <formula1>$O$3:$O$3</formula1>
-    </dataValidation>
-    <dataValidation sqref="K7:K132" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
-      <formula1>$L$3:$L$3</formula1>
-    </dataValidation>
-    <dataValidation sqref="F2:F6" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
-      <formula1>$L$5:$L$6</formula1>
-    </dataValidation>
-    <dataValidation sqref="D2:D6" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
-      <formula1>$L$2:$L$3</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:P9"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="14.8984375" defaultRowHeight="14.4"/>
   <cols>
@@ -1036,7 +780,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1266,6 +1010,338 @@
       <c r="F8" t="inlineStr">
         <is>
           <t>菰野スイミング</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>日付</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>学年</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>距離</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>長水路or短水路</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>タイム</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>会場</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="11" t="n">
+        <v>45788</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>小5</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>50</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>47.91</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="11" t="n">
+        <v>45816</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>小5</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>50</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>47.54</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="11" t="n">
+        <v>45823</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>小5</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>50</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>44.48</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="11" t="n">
+        <v>45844</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>小5</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>50</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>44.39</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="11" t="n">
+        <v>45942</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>小5</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>50</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>40.39</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="11" t="n">
+        <v>45955</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>小5</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>50</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>40.5</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="11" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>小5</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>50</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>39.07</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="11" t="n">
+        <v>46053</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>小5</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>50</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>38.24</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="11" t="n">
+        <v>46074</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>小5</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>50</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>37.73</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="11" t="n">
+        <v>46130</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>小6</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>50</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>40.28</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>菰野スイミング</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="11" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>小6</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>50</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>36.55</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
         </is>
       </c>
     </row>
@@ -1280,7 +1356,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1333,7 +1409,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>47.91</v>
+        <v>58.87</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -1343,7 +1419,7 @@
     </row>
     <row r="3">
       <c r="A3" s="11" t="n">
-        <v>45816</v>
+        <v>45815</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -1359,7 +1435,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>47.54</v>
+        <v>55.01</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1369,7 +1445,7 @@
     </row>
     <row r="4">
       <c r="A4" s="11" t="n">
-        <v>45823</v>
+        <v>45844</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -1381,11 +1457,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>短水路</t>
+          <t>長水路</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>44.48</v>
+        <v>52.08</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1395,7 +1471,7 @@
     </row>
     <row r="5">
       <c r="A5" s="11" t="n">
-        <v>45844</v>
+        <v>45942</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -1411,7 +1487,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>44.39</v>
+        <v>52.97</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1421,7 +1497,7 @@
     </row>
     <row r="6">
       <c r="A6" s="11" t="n">
-        <v>45942</v>
+        <v>45955</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -1433,11 +1509,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>長水路</t>
+          <t>短水路</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>40.39</v>
+        <v>49.74</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1447,7 +1523,7 @@
     </row>
     <row r="7">
       <c r="A7" s="11" t="n">
-        <v>45955</v>
+        <v>45984</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -1459,11 +1535,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>短水路</t>
+          <t>長水路</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>40.5</v>
+        <v>49.06</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1473,7 +1549,7 @@
     </row>
     <row r="8">
       <c r="A8" s="11" t="n">
-        <v>46033</v>
+        <v>45984</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -1481,15 +1557,17 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>39.07</v>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>1'41"11</t>
+        </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1499,7 +1577,7 @@
     </row>
     <row r="9">
       <c r="A9" s="11" t="n">
-        <v>46053</v>
+        <v>46033</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1515,7 +1593,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>38.24</v>
+        <v>47.55</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1525,7 +1603,7 @@
     </row>
     <row r="10">
       <c r="A10" s="11" t="n">
-        <v>46074</v>
+        <v>46053</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -1537,11 +1615,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>長水路</t>
+          <t>短水路</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>37.73</v>
+        <v>46.9</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1551,11 +1629,11 @@
     </row>
     <row r="11">
       <c r="A11" s="11" t="n">
-        <v>46130</v>
+        <v>46075</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>小6</t>
+          <t>小5</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1563,39 +1641,221 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>短水路</t>
+          <t>長水路</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>40.28</v>
+        <v>47.42</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>菰野スイミング</t>
+          <t>鈴鹿</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="11" t="n">
+        <v>46130</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>小6</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>50</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>47.95</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>菰野スイミング</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="11" t="n">
+        <v>46053</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>小5</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>100</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>99.48999999999999</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="11" t="n">
         <v>46152</v>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>小6</t>
         </is>
       </c>
-      <c r="C12" t="n">
-        <v>50</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>36.55</v>
-      </c>
-      <c r="F12" t="inlineStr">
+      <c r="C14" t="n">
+        <v>50</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>45.36</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="11" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>小6</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>100</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>95.04000000000001</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="11" t="n">
+        <v>46179</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>小6</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>100</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100.1</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="11" t="n">
+        <v>46180</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>小6</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>50</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>46.87</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="11" t="n">
+        <v>46187</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>小6</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>50</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>45.11</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="11" t="n">
+        <v>46187</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>小6</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>100</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>96.61</v>
+      </c>
+      <c r="F19" t="inlineStr">
         <is>
           <t>鈴鹿</t>
         </is>
@@ -1612,7 +1872,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1649,7 +1909,7 @@
     </row>
     <row r="2">
       <c r="A2" s="11" t="n">
-        <v>45788</v>
+        <v>45823</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -1665,7 +1925,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>58.87</v>
+        <v>54.97</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -1675,7 +1935,7 @@
     </row>
     <row r="3">
       <c r="A3" s="11" t="n">
-        <v>45815</v>
+        <v>45956</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -1691,7 +1951,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>55.01</v>
+        <v>48.27</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1701,7 +1961,7 @@
     </row>
     <row r="4">
       <c r="A4" s="11" t="n">
-        <v>45844</v>
+        <v>46033</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -1713,11 +1973,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>長水路</t>
+          <t>短水路</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>52.08</v>
+        <v>44.97</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1727,7 +1987,7 @@
     </row>
     <row r="5">
       <c r="A5" s="11" t="n">
-        <v>45942</v>
+        <v>46075</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -1743,7 +2003,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>52.97</v>
+        <v>44.65</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1753,11 +2013,11 @@
     </row>
     <row r="6">
       <c r="A6" s="11" t="n">
-        <v>45955</v>
+        <v>46130</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>小5</t>
+          <t>小6</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -1769,21 +2029,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>49.74</v>
+        <v>47.17</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>鈴鹿</t>
+          <t>菰野スイミング</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="11" t="n">
-        <v>45984</v>
+        <v>46187</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>小5</t>
+          <t>小6</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -1791,327 +2051,13 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>長水路</t>
+          <t>短水路</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>49.06</v>
+        <v>42.92</v>
       </c>
       <c r="F7" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="11" t="n">
-        <v>45984</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>小5</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>100</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>長水路</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>1'41"11</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="11" t="n">
-        <v>46033</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>小5</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>50</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>47.55</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="11" t="n">
-        <v>46053</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>小5</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>50</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>46.9</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="11" t="n">
-        <v>46075</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>小5</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>50</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>長水路</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>47.42</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="11" t="n">
-        <v>46130</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>小6</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>50</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>47.95</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>菰野スイミング</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="11" t="n">
-        <v>46053</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>小5</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>100</v>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>99.48999999999999</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="11" t="n">
-        <v>46152</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>小6</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>50</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>45.36</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="11" t="n">
-        <v>46152</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>小6</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>100</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>95.04000000000001</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="11" t="n">
-        <v>46179</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>小6</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>100</v>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>長水路</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>100.1</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="11" t="n">
-        <v>46180</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>小6</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>50</v>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>長水路</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>46.87</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="11" t="n">
-        <v>46187</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>小6</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>50</v>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>45.11</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="11" t="n">
-        <v>46187</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>小6</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>100</v>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>96.61</v>
-      </c>
-      <c r="F19" t="inlineStr">
         <is>
           <t>鈴鹿</t>
         </is>

--- a/穂果記録.xlsx
+++ b/穂果記録.xlsx
@@ -8,9 +8,9 @@
   <sheets>
     <sheet name="バック" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="メドレー" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="フリー" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="ブレ" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="バッタ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="ブレ" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="バッタ" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="フリー" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -1024,7 +1024,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1077,7 +1077,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>47.91</v>
+        <v>58.87</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -1087,7 +1087,7 @@
     </row>
     <row r="3">
       <c r="A3" s="11" t="n">
-        <v>45816</v>
+        <v>45815</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -1103,7 +1103,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>47.54</v>
+        <v>55.01</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
     </row>
     <row r="4">
       <c r="A4" s="11" t="n">
-        <v>45823</v>
+        <v>45844</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -1125,11 +1125,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>短水路</t>
+          <t>長水路</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>44.48</v>
+        <v>52.08</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
     </row>
     <row r="5">
       <c r="A5" s="11" t="n">
-        <v>45844</v>
+        <v>45942</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -1155,7 +1155,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>44.39</v>
+        <v>52.97</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1165,7 +1165,7 @@
     </row>
     <row r="6">
       <c r="A6" s="11" t="n">
-        <v>45942</v>
+        <v>45955</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -1177,11 +1177,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>長水路</t>
+          <t>短水路</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>40.39</v>
+        <v>49.74</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1191,7 +1191,7 @@
     </row>
     <row r="7">
       <c r="A7" s="11" t="n">
-        <v>45955</v>
+        <v>45984</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -1203,11 +1203,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>短水路</t>
+          <t>長水路</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>40.5</v>
+        <v>49.06</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
     </row>
     <row r="8">
       <c r="A8" s="11" t="n">
-        <v>46033</v>
+        <v>45984</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -1225,15 +1225,17 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>39.07</v>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>1'41"11</t>
+        </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1243,7 +1245,7 @@
     </row>
     <row r="9">
       <c r="A9" s="11" t="n">
-        <v>46053</v>
+        <v>46033</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1259,7 +1261,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>38.24</v>
+        <v>47.55</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1269,7 +1271,7 @@
     </row>
     <row r="10">
       <c r="A10" s="11" t="n">
-        <v>46074</v>
+        <v>46053</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -1281,11 +1283,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>長水路</t>
+          <t>短水路</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>37.73</v>
+        <v>46.9</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1295,11 +1297,11 @@
     </row>
     <row r="11">
       <c r="A11" s="11" t="n">
-        <v>46130</v>
+        <v>46075</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>小6</t>
+          <t>小5</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1307,39 +1309,221 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>短水路</t>
+          <t>長水路</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>40.28</v>
+        <v>47.42</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>菰野スイミング</t>
+          <t>鈴鹿</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="11" t="n">
+        <v>46130</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>小6</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>50</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>47.95</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>菰野スイミング</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="11" t="n">
+        <v>46053</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>小5</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>100</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>99.48999999999999</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="11" t="n">
         <v>46152</v>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>小6</t>
         </is>
       </c>
-      <c r="C12" t="n">
-        <v>50</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>36.55</v>
-      </c>
-      <c r="F12" t="inlineStr">
+      <c r="C14" t="n">
+        <v>50</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>45.36</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="11" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>小6</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>100</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>95.04000000000001</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="11" t="n">
+        <v>46179</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>小6</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>100</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100.1</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="11" t="n">
+        <v>46180</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>小6</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>50</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>46.87</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="11" t="n">
+        <v>46187</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>小6</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>50</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>45.11</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="11" t="n">
+        <v>46187</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>小6</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>100</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>96.61</v>
+      </c>
+      <c r="F19" t="inlineStr">
         <is>
           <t>鈴鹿</t>
         </is>
@@ -1356,7 +1540,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1393,7 +1577,7 @@
     </row>
     <row r="2">
       <c r="A2" s="11" t="n">
-        <v>45788</v>
+        <v>45823</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -1409,7 +1593,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>58.87</v>
+        <v>54.97</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -1419,7 +1603,7 @@
     </row>
     <row r="3">
       <c r="A3" s="11" t="n">
-        <v>45815</v>
+        <v>45956</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -1435,7 +1619,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>55.01</v>
+        <v>48.27</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1445,7 +1629,7 @@
     </row>
     <row r="4">
       <c r="A4" s="11" t="n">
-        <v>45844</v>
+        <v>46033</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -1457,11 +1641,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>長水路</t>
+          <t>短水路</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>52.08</v>
+        <v>44.97</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1471,7 +1655,7 @@
     </row>
     <row r="5">
       <c r="A5" s="11" t="n">
-        <v>45942</v>
+        <v>46075</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -1487,7 +1671,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>52.97</v>
+        <v>44.65</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1497,11 +1681,11 @@
     </row>
     <row r="6">
       <c r="A6" s="11" t="n">
-        <v>45955</v>
+        <v>46130</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>小5</t>
+          <t>小6</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -1513,21 +1697,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>49.74</v>
+        <v>47.17</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>鈴鹿</t>
+          <t>菰野スイミング</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="11" t="n">
-        <v>45984</v>
+        <v>46187</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>小5</t>
+          <t>小6</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -1535,327 +1719,13 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>長水路</t>
+          <t>短水路</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>49.06</v>
+        <v>42.92</v>
       </c>
       <c r="F7" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="11" t="n">
-        <v>45984</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>小5</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>100</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>長水路</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>1'41"11</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="11" t="n">
-        <v>46033</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>小5</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>50</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>47.55</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="11" t="n">
-        <v>46053</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>小5</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>50</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>46.9</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="11" t="n">
-        <v>46075</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>小5</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>50</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>長水路</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>47.42</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="11" t="n">
-        <v>46130</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>小6</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>50</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>47.95</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>菰野スイミング</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="11" t="n">
-        <v>46053</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>小5</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>100</v>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>99.48999999999999</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="11" t="n">
-        <v>46152</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>小6</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>50</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>45.36</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="11" t="n">
-        <v>46152</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>小6</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>100</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>95.04000000000001</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="11" t="n">
-        <v>46179</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>小6</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>100</v>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>長水路</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>100.1</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="11" t="n">
-        <v>46180</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>小6</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>50</v>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>長水路</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>46.87</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="11" t="n">
-        <v>46187</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>小6</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>50</v>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>45.11</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="11" t="n">
-        <v>46187</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>小6</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>100</v>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>96.61</v>
-      </c>
-      <c r="F19" t="inlineStr">
         <is>
           <t>鈴鹿</t>
         </is>
@@ -1872,7 +1742,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1909,7 +1779,7 @@
     </row>
     <row r="2">
       <c r="A2" s="11" t="n">
-        <v>45823</v>
+        <v>45788</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -1925,7 +1795,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>54.97</v>
+        <v>47.91</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -1935,7 +1805,7 @@
     </row>
     <row r="3">
       <c r="A3" s="11" t="n">
-        <v>45956</v>
+        <v>45816</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -1951,7 +1821,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>48.27</v>
+        <v>47.54</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1961,7 +1831,7 @@
     </row>
     <row r="4">
       <c r="A4" s="11" t="n">
-        <v>46033</v>
+        <v>45823</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -1977,7 +1847,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>44.97</v>
+        <v>44.48</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1987,7 +1857,7 @@
     </row>
     <row r="5">
       <c r="A5" s="11" t="n">
-        <v>46075</v>
+        <v>45844</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -2003,7 +1873,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>44.65</v>
+        <v>44.39</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -2013,11 +1883,11 @@
     </row>
     <row r="6">
       <c r="A6" s="11" t="n">
-        <v>46130</v>
+        <v>45942</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>小6</t>
+          <t>小5</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -2025,39 +1895,195 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>短水路</t>
+          <t>長水路</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>47.17</v>
+        <v>40.39</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>菰野スイミング</t>
+          <t>鈴鹿</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="11" t="n">
-        <v>46187</v>
+        <v>45955</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>小5</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>50</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>40.5</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="11" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>小5</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>50</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>39.07</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="11" t="n">
+        <v>46053</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>小5</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>50</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>38.24</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="11" t="n">
+        <v>46074</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>小5</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>50</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>37.73</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="11" t="n">
+        <v>46130</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
           <t>小6</t>
         </is>
       </c>
-      <c r="C7" t="n">
-        <v>50</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>42.92</v>
-      </c>
-      <c r="F7" t="inlineStr">
+      <c r="C11" t="n">
+        <v>50</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>40.28</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>菰野スイミング</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="11" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>小6</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>50</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>36.55</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="11" t="n">
+        <v>46207</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>小6</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>50</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>36.89</v>
+      </c>
+      <c r="F13" t="inlineStr">
         <is>
           <t>鈴鹿</t>
         </is>

--- a/穂果記録.xlsx
+++ b/穂果記録.xlsx
@@ -8,9 +8,9 @@
   <sheets>
     <sheet name="バック" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="メドレー" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="ブレ" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="バッタ" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="フリー" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="バッタ" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="フリー" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="ブレ" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -1024,7 +1024,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1061,7 +1061,7 @@
     </row>
     <row r="2">
       <c r="A2" s="11" t="n">
-        <v>45788</v>
+        <v>45823</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -1077,7 +1077,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>58.87</v>
+        <v>54.97</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -1087,7 +1087,7 @@
     </row>
     <row r="3">
       <c r="A3" s="11" t="n">
-        <v>45815</v>
+        <v>45956</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -1103,7 +1103,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>55.01</v>
+        <v>48.27</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
     </row>
     <row r="4">
       <c r="A4" s="11" t="n">
-        <v>45844</v>
+        <v>46033</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -1125,11 +1125,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>長水路</t>
+          <t>短水路</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>52.08</v>
+        <v>44.97</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
     </row>
     <row r="5">
       <c r="A5" s="11" t="n">
-        <v>45942</v>
+        <v>46075</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -1155,7 +1155,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>52.97</v>
+        <v>44.65</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1165,11 +1165,11 @@
     </row>
     <row r="6">
       <c r="A6" s="11" t="n">
-        <v>45955</v>
+        <v>46130</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>小5</t>
+          <t>小6</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -1181,21 +1181,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>49.74</v>
+        <v>47.17</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>鈴鹿</t>
+          <t>菰野スイミング</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="11" t="n">
-        <v>45984</v>
+        <v>46187</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>小5</t>
+          <t>小6</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -1203,327 +1203,13 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>長水路</t>
+          <t>短水路</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>49.06</v>
+        <v>42.92</v>
       </c>
       <c r="F7" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="11" t="n">
-        <v>45984</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>小5</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>100</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>長水路</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>1'41"11</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="11" t="n">
-        <v>46033</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>小5</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>50</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>47.55</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="11" t="n">
-        <v>46053</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>小5</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>50</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>46.9</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="11" t="n">
-        <v>46075</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>小5</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>50</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>長水路</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>47.42</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="11" t="n">
-        <v>46130</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>小6</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>50</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>47.95</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>菰野スイミング</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="11" t="n">
-        <v>46053</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>小5</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>100</v>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>99.48999999999999</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="11" t="n">
-        <v>46152</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>小6</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>50</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>45.36</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="11" t="n">
-        <v>46152</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>小6</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>100</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>95.04000000000001</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="11" t="n">
-        <v>46179</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>小6</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>100</v>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>長水路</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>100.1</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="11" t="n">
-        <v>46180</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>小6</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>50</v>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>長水路</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>46.87</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="11" t="n">
-        <v>46187</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>小6</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>50</v>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>45.11</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="11" t="n">
-        <v>46187</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>小6</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>100</v>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>96.61</v>
-      </c>
-      <c r="F19" t="inlineStr">
         <is>
           <t>鈴鹿</t>
         </is>
@@ -1540,7 +1226,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1577,7 +1263,7 @@
     </row>
     <row r="2">
       <c r="A2" s="11" t="n">
-        <v>45823</v>
+        <v>45788</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -1593,7 +1279,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>54.97</v>
+        <v>47.91</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -1603,7 +1289,7 @@
     </row>
     <row r="3">
       <c r="A3" s="11" t="n">
-        <v>45956</v>
+        <v>45816</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -1619,7 +1305,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>48.27</v>
+        <v>47.54</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1629,7 +1315,7 @@
     </row>
     <row r="4">
       <c r="A4" s="11" t="n">
-        <v>46033</v>
+        <v>45823</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -1645,7 +1331,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>44.97</v>
+        <v>44.48</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1655,7 +1341,7 @@
     </row>
     <row r="5">
       <c r="A5" s="11" t="n">
-        <v>46075</v>
+        <v>45844</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -1671,7 +1357,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>44.65</v>
+        <v>44.39</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1681,11 +1367,11 @@
     </row>
     <row r="6">
       <c r="A6" s="11" t="n">
-        <v>46130</v>
+        <v>45942</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>小6</t>
+          <t>小5</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -1693,39 +1379,195 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>短水路</t>
+          <t>長水路</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>47.17</v>
+        <v>40.39</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>菰野スイミング</t>
+          <t>鈴鹿</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="11" t="n">
-        <v>46187</v>
+        <v>45955</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>小5</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>50</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>40.5</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="11" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>小5</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>50</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>39.07</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="11" t="n">
+        <v>46053</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>小5</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>50</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>38.24</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="11" t="n">
+        <v>46074</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>小5</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>50</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>37.73</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="11" t="n">
+        <v>46130</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
           <t>小6</t>
         </is>
       </c>
-      <c r="C7" t="n">
-        <v>50</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>42.92</v>
-      </c>
-      <c r="F7" t="inlineStr">
+      <c r="C11" t="n">
+        <v>50</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>40.28</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>菰野スイミング</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="11" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>小6</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>50</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>36.55</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="11" t="n">
+        <v>46207</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>小6</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>50</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>36.89</v>
+      </c>
+      <c r="F13" t="inlineStr">
         <is>
           <t>鈴鹿</t>
         </is>
@@ -1742,7 +1584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1795,7 +1637,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>47.91</v>
+        <v>58.87</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -1805,7 +1647,7 @@
     </row>
     <row r="3">
       <c r="A3" s="11" t="n">
-        <v>45816</v>
+        <v>45815</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -1821,7 +1663,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>47.54</v>
+        <v>55.01</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1831,7 +1673,7 @@
     </row>
     <row r="4">
       <c r="A4" s="11" t="n">
-        <v>45823</v>
+        <v>45844</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -1843,11 +1685,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>短水路</t>
+          <t>長水路</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>44.48</v>
+        <v>52.08</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1857,7 +1699,7 @@
     </row>
     <row r="5">
       <c r="A5" s="11" t="n">
-        <v>45844</v>
+        <v>45942</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -1873,7 +1715,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>44.39</v>
+        <v>52.97</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1883,7 +1725,7 @@
     </row>
     <row r="6">
       <c r="A6" s="11" t="n">
-        <v>45942</v>
+        <v>45955</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -1895,11 +1737,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>長水路</t>
+          <t>短水路</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>40.39</v>
+        <v>49.74</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1909,7 +1751,7 @@
     </row>
     <row r="7">
       <c r="A7" s="11" t="n">
-        <v>45955</v>
+        <v>45984</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -1921,11 +1763,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>短水路</t>
+          <t>長水路</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>40.5</v>
+        <v>49.06</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1935,7 +1777,7 @@
     </row>
     <row r="8">
       <c r="A8" s="11" t="n">
-        <v>46033</v>
+        <v>45984</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -1943,15 +1785,17 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>39.07</v>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>1'41"11</t>
+        </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1961,7 +1805,7 @@
     </row>
     <row r="9">
       <c r="A9" s="11" t="n">
-        <v>46053</v>
+        <v>46033</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1977,7 +1821,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>38.24</v>
+        <v>47.55</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1987,7 +1831,7 @@
     </row>
     <row r="10">
       <c r="A10" s="11" t="n">
-        <v>46074</v>
+        <v>46053</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -1999,11 +1843,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>長水路</t>
+          <t>短水路</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>37.73</v>
+        <v>46.9</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -2013,11 +1857,11 @@
     </row>
     <row r="11">
       <c r="A11" s="11" t="n">
-        <v>46130</v>
+        <v>46075</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>小6</t>
+          <t>小5</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -2025,21 +1869,21 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>短水路</t>
+          <t>長水路</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>40.28</v>
+        <v>47.42</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>菰野スイミング</t>
+          <t>鈴鹿</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="11" t="n">
-        <v>46152</v>
+        <v>46130</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -2055,35 +1899,217 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>36.55</v>
+        <v>47.95</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>鈴鹿</t>
+          <t>菰野スイミング</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="11" t="n">
+        <v>46053</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>小5</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>100</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>99.48999999999999</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="11" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>小6</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>50</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>45.36</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="11" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>小6</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>100</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>95.04000000000001</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="11" t="n">
+        <v>46179</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>小6</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>100</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100.1</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="11" t="n">
+        <v>46180</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>小6</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>50</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>46.87</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="11" t="n">
+        <v>46187</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>小6</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>50</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>45.11</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="11" t="n">
+        <v>46187</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>小6</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>100</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>96.61</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="11" t="n">
         <v>46207</v>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>小6</t>
         </is>
       </c>
-      <c r="C13" t="n">
-        <v>50</v>
-      </c>
-      <c r="D13" t="inlineStr">
+      <c r="C20" t="n">
+        <v>50</v>
+      </c>
+      <c r="D20" t="inlineStr">
         <is>
           <t>長水路</t>
         </is>
       </c>
-      <c r="E13" t="n">
-        <v>36.89</v>
-      </c>
-      <c r="F13" t="inlineStr">
+      <c r="E20" t="n">
+        <v>45.87</v>
+      </c>
+      <c r="F20" t="inlineStr">
         <is>
           <t>鈴鹿</t>
         </is>

--- a/穂果記録.xlsx
+++ b/穂果記録.xlsx
@@ -8,9 +8,9 @@
   <sheets>
     <sheet name="バック" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="メドレー" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="バッタ" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="フリー" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="ブレ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="フリー" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="ブレ" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="バッタ" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -1024,7 +1024,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1061,7 +1061,7 @@
     </row>
     <row r="2">
       <c r="A2" s="11" t="n">
-        <v>45823</v>
+        <v>45788</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -1077,7 +1077,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>54.97</v>
+        <v>47.91</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -1087,7 +1087,7 @@
     </row>
     <row r="3">
       <c r="A3" s="11" t="n">
-        <v>45956</v>
+        <v>45816</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -1103,7 +1103,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>48.27</v>
+        <v>47.54</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
     </row>
     <row r="4">
       <c r="A4" s="11" t="n">
-        <v>46033</v>
+        <v>45823</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>44.97</v>
+        <v>44.48</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
     </row>
     <row r="5">
       <c r="A5" s="11" t="n">
-        <v>46075</v>
+        <v>45844</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -1155,7 +1155,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>44.65</v>
+        <v>44.39</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1165,11 +1165,11 @@
     </row>
     <row r="6">
       <c r="A6" s="11" t="n">
-        <v>46130</v>
+        <v>45942</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>小6</t>
+          <t>小5</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -1177,39 +1177,195 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>短水路</t>
+          <t>長水路</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>47.17</v>
+        <v>40.39</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>菰野スイミング</t>
+          <t>鈴鹿</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="11" t="n">
-        <v>46187</v>
+        <v>45955</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>小5</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>50</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>40.5</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="11" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>小5</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>50</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>39.07</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="11" t="n">
+        <v>46053</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>小5</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>50</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>38.24</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="11" t="n">
+        <v>46074</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>小5</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>50</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>37.73</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="11" t="n">
+        <v>46130</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
           <t>小6</t>
         </is>
       </c>
-      <c r="C7" t="n">
-        <v>50</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>42.92</v>
-      </c>
-      <c r="F7" t="inlineStr">
+      <c r="C11" t="n">
+        <v>50</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>40.28</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>菰野スイミング</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="11" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>小6</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>50</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>36.55</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="11" t="n">
+        <v>46207</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>小6</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>50</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>36.89</v>
+      </c>
+      <c r="F13" t="inlineStr">
         <is>
           <t>鈴鹿</t>
         </is>
@@ -1226,7 +1382,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1279,7 +1435,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>47.91</v>
+        <v>58.87</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -1289,7 +1445,7 @@
     </row>
     <row r="3">
       <c r="A3" s="11" t="n">
-        <v>45816</v>
+        <v>45815</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -1305,7 +1461,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>47.54</v>
+        <v>55.01</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1315,7 +1471,7 @@
     </row>
     <row r="4">
       <c r="A4" s="11" t="n">
-        <v>45823</v>
+        <v>45844</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -1327,11 +1483,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>短水路</t>
+          <t>長水路</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>44.48</v>
+        <v>52.08</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1341,7 +1497,7 @@
     </row>
     <row r="5">
       <c r="A5" s="11" t="n">
-        <v>45844</v>
+        <v>45942</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -1357,7 +1513,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>44.39</v>
+        <v>52.97</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1367,7 +1523,7 @@
     </row>
     <row r="6">
       <c r="A6" s="11" t="n">
-        <v>45942</v>
+        <v>45955</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -1379,11 +1535,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>長水路</t>
+          <t>短水路</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>40.39</v>
+        <v>49.74</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1393,7 +1549,7 @@
     </row>
     <row r="7">
       <c r="A7" s="11" t="n">
-        <v>45955</v>
+        <v>45984</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -1405,11 +1561,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>短水路</t>
+          <t>長水路</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>40.5</v>
+        <v>49.06</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1419,7 +1575,7 @@
     </row>
     <row r="8">
       <c r="A8" s="11" t="n">
-        <v>46033</v>
+        <v>45984</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -1427,15 +1583,17 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>39.07</v>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>1'41"11</t>
+        </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1445,7 +1603,7 @@
     </row>
     <row r="9">
       <c r="A9" s="11" t="n">
-        <v>46053</v>
+        <v>46033</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1461,7 +1619,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>38.24</v>
+        <v>47.55</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1471,7 +1629,7 @@
     </row>
     <row r="10">
       <c r="A10" s="11" t="n">
-        <v>46074</v>
+        <v>46053</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -1483,11 +1641,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>長水路</t>
+          <t>短水路</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>37.73</v>
+        <v>46.9</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1497,11 +1655,11 @@
     </row>
     <row r="11">
       <c r="A11" s="11" t="n">
-        <v>46130</v>
+        <v>46075</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>小6</t>
+          <t>小5</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1509,21 +1667,21 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>短水路</t>
+          <t>長水路</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>40.28</v>
+        <v>47.42</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>菰野スイミング</t>
+          <t>鈴鹿</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="11" t="n">
-        <v>46152</v>
+        <v>46130</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -1539,35 +1697,217 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>36.55</v>
+        <v>47.95</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>鈴鹿</t>
+          <t>菰野スイミング</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="11" t="n">
+        <v>46053</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>小5</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>100</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>99.48999999999999</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="11" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>小6</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>50</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>45.36</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="11" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>小6</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>100</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>95.04000000000001</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="11" t="n">
+        <v>46179</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>小6</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>100</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100.1</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="11" t="n">
+        <v>46180</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>小6</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>50</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>46.87</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="11" t="n">
+        <v>46187</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>小6</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>50</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>45.11</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="11" t="n">
+        <v>46187</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>小6</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>100</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>96.61</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="11" t="n">
         <v>46207</v>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>小6</t>
         </is>
       </c>
-      <c r="C13" t="n">
-        <v>50</v>
-      </c>
-      <c r="D13" t="inlineStr">
+      <c r="C20" t="n">
+        <v>50</v>
+      </c>
+      <c r="D20" t="inlineStr">
         <is>
           <t>長水路</t>
         </is>
       </c>
-      <c r="E13" t="n">
-        <v>36.89</v>
-      </c>
-      <c r="F13" t="inlineStr">
+      <c r="E20" t="n">
+        <v>45.87</v>
+      </c>
+      <c r="F20" t="inlineStr">
         <is>
           <t>鈴鹿</t>
         </is>
@@ -1584,7 +1924,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1621,7 +1961,7 @@
     </row>
     <row r="2">
       <c r="A2" s="11" t="n">
-        <v>45788</v>
+        <v>45823</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -1637,7 +1977,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>58.87</v>
+        <v>54.97</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -1647,7 +1987,7 @@
     </row>
     <row r="3">
       <c r="A3" s="11" t="n">
-        <v>45815</v>
+        <v>45956</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -1663,7 +2003,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>55.01</v>
+        <v>48.27</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1673,7 +2013,7 @@
     </row>
     <row r="4">
       <c r="A4" s="11" t="n">
-        <v>45844</v>
+        <v>46033</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -1685,11 +2025,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>長水路</t>
+          <t>短水路</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>52.08</v>
+        <v>44.97</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1699,7 +2039,7 @@
     </row>
     <row r="5">
       <c r="A5" s="11" t="n">
-        <v>45942</v>
+        <v>46075</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -1715,7 +2055,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>52.97</v>
+        <v>44.65</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1725,11 +2065,11 @@
     </row>
     <row r="6">
       <c r="A6" s="11" t="n">
-        <v>45955</v>
+        <v>46130</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>小5</t>
+          <t>小6</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -1741,21 +2081,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>49.74</v>
+        <v>47.17</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>鈴鹿</t>
+          <t>菰野スイミング</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="11" t="n">
-        <v>45984</v>
+        <v>46187</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>小5</t>
+          <t>小6</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -1763,11 +2103,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>長水路</t>
+          <t>短水路</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>49.06</v>
+        <v>42.92</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1777,339 +2117,25 @@
     </row>
     <row r="8">
       <c r="A8" s="11" t="n">
-        <v>45984</v>
+        <v>46208</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>小5</t>
+          <t>小6</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
           <t>長水路</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>1'41"11</t>
-        </is>
+      <c r="E8" t="n">
+        <v>44.13</v>
       </c>
       <c r="F8" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="11" t="n">
-        <v>46033</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>小5</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>50</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>47.55</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="11" t="n">
-        <v>46053</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>小5</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>50</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>46.9</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="11" t="n">
-        <v>46075</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>小5</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>50</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>長水路</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>47.42</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="11" t="n">
-        <v>46130</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>小6</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>50</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>47.95</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>菰野スイミング</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="11" t="n">
-        <v>46053</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>小5</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>100</v>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>99.48999999999999</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="11" t="n">
-        <v>46152</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>小6</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>50</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>45.36</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="11" t="n">
-        <v>46152</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>小6</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>100</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>95.04000000000001</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="11" t="n">
-        <v>46179</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>小6</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>100</v>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>長水路</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>100.1</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="11" t="n">
-        <v>46180</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>小6</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>50</v>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>長水路</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>46.87</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="11" t="n">
-        <v>46187</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>小6</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>50</v>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>45.11</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="11" t="n">
-        <v>46187</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>小6</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>100</v>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>96.61</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="11" t="n">
-        <v>46207</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>小6</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>50</v>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>長水路</t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>45.87</v>
-      </c>
-      <c r="F20" t="inlineStr">
         <is>
           <t>鈴鹿</t>
         </is>

--- a/穂果記録.xlsx
+++ b/穂果記録.xlsx
@@ -6,11 +6,11 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="2304" yWindow="2304" windowWidth="13716" windowHeight="9960" tabRatio="600" firstSheet="0" activeTab="4" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="バック" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="メドレー" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="フリー" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="ブレ" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="バッタ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="メドレー" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="フリー" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="ブレ" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="バッタ" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="バック" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -450,333 +450,235 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P9"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="14.8984375" defaultRowHeight="14.4"/>
-  <cols>
-    <col width="15.796875" bestFit="1" customWidth="1" style="9" min="1" max="1"/>
-    <col width="14.8984375" customWidth="1" style="1" min="2" max="4"/>
-    <col width="14.8984375" customWidth="1" style="10" min="5" max="5"/>
-    <col width="14.8984375" customWidth="1" style="1" min="6" max="6"/>
-    <col width="22.5" customWidth="1" style="1" min="7" max="7"/>
-    <col width="18.5" customWidth="1" style="1" min="8" max="8"/>
-    <col width="14.8984375" customWidth="1" style="1" min="9" max="16"/>
-    <col width="9.8984375" customWidth="1" style="1" min="17" max="17"/>
-    <col width="14.8984375" customWidth="1" style="1" min="18" max="16384"/>
-  </cols>
+  <dimension ref="A1:F8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>日付</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>学年</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>距離</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>長水路 or 短水路</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>長水路or短水路</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
         <is>
           <t>タイム</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>会場</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>50m ベストタイム(短水路)</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>50m 更新日</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>50m ベストタイム(長水路)</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>50m 更新日</t>
-        </is>
-      </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="n">
-        <v>45788</v>
-      </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t>小5</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="n">
-        <v>50</v>
-      </c>
-      <c r="D2" s="1" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="n">
-        <v>54.97</v>
-      </c>
-      <c r="F2" s="1" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-      <c r="G2" s="1">
-        <f>_xlfn.MINIFS(E:E, C:C, 50, D:D, "短水路")</f>
-        <v/>
-      </c>
-      <c r="H2" s="5">
-        <f>INDEX(A:A, MATCH(_xlfn.MINIFS(E:E, D:D, "短水路"), E:E, 0))</f>
-        <v/>
-      </c>
-      <c r="I2" s="1">
-        <f>_xlfn.MINIFS(E:E, C:C, 50, D:D, "長水路")</f>
-        <v/>
-      </c>
-      <c r="J2" s="5">
-        <f>INDEX(A:A, MATCH(_xlfn.MINIFS(E:E, D:D, "長水路"), E:E, 0))</f>
-        <v/>
-      </c>
-      <c r="P2" s="1" t="inlineStr">
-        <is>
-          <t>長水路</t>
+      <c r="A2" s="11" t="n">
+        <v>45710</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>小4</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>200</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>4'43"09</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>菰野スイミング</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="n">
-        <v>45815</v>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>小5</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="n">
-        <v>50</v>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t>長水路</t>
-        </is>
-      </c>
-      <c r="E3" s="10" t="n">
-        <v>52.8</v>
-      </c>
-      <c r="F3" s="1" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="n"/>
-      <c r="P3" s="1" t="inlineStr">
-        <is>
-          <t>短水路</t>
+      <c r="A3" s="11" t="n">
+        <v>45808</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>小5</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>200</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>4'02"71</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>菰野スイミング</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="n">
-        <v>45823</v>
-      </c>
-      <c r="B4" s="1" t="inlineStr">
-        <is>
-          <t>小5</t>
-        </is>
-      </c>
-      <c r="C4" s="1" t="n">
-        <v>50</v>
-      </c>
-      <c r="D4" s="1" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E4" s="10" t="n">
-        <v>51.07</v>
-      </c>
-      <c r="F4" s="1" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
+      <c r="A4" s="11" t="n">
+        <v>45899</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>小5</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>200</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>3'37"53</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>菰野スイミング</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="n">
-        <v>45844</v>
-      </c>
-      <c r="B5" s="1" t="inlineStr">
-        <is>
-          <t>小5</t>
-        </is>
-      </c>
-      <c r="C5" s="1" t="n">
-        <v>50</v>
-      </c>
-      <c r="D5" s="1" t="inlineStr">
-        <is>
-          <t>長水路</t>
-        </is>
-      </c>
-      <c r="E5" s="10" t="n">
-        <v>50.06</v>
-      </c>
-      <c r="F5" s="1" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-      <c r="P5" s="1" t="inlineStr">
+      <c r="A5" s="11" t="n">
+        <v>45991</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>小5</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>200</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>3'21"34</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
         <is>
           <t>菰野スイミング</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="n">
-        <v>45956</v>
-      </c>
-      <c r="B6" s="1" t="inlineStr">
-        <is>
-          <t>小5</t>
-        </is>
-      </c>
-      <c r="C6" s="1" t="n">
-        <v>50</v>
-      </c>
-      <c r="D6" s="1" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E6" s="10" t="n">
-        <v>46.12</v>
-      </c>
-      <c r="F6" s="1" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-      <c r="P6" s="1" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
+      <c r="A6" s="11" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>小5</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>200</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>3'14"47</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>菰野スイミング</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="n">
-        <v>45984</v>
-      </c>
-      <c r="B7" s="1" t="inlineStr">
-        <is>
-          <t>小5</t>
-        </is>
-      </c>
-      <c r="C7" s="1" t="n">
-        <v>50</v>
-      </c>
-      <c r="D7" s="1" t="inlineStr">
-        <is>
-          <t>長水路</t>
-        </is>
-      </c>
-      <c r="E7" s="10" t="n">
-        <v>45.67</v>
-      </c>
-      <c r="F7" s="1" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
+      <c r="A7" s="11" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>小6</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>50</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>173.24</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>菰野スイミング</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="n">
-        <v>46075</v>
-      </c>
-      <c r="B8" s="1" t="inlineStr">
-        <is>
-          <t>小5</t>
-        </is>
-      </c>
-      <c r="C8" s="1" t="n">
-        <v>50</v>
-      </c>
-      <c r="D8" s="1" t="inlineStr">
-        <is>
-          <t>長水路</t>
-        </is>
-      </c>
-      <c r="E8" s="10" t="n">
-        <v>44.84</v>
-      </c>
-      <c r="F8" s="1" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="n">
-        <v>46130</v>
-      </c>
-      <c r="B9" s="1" t="inlineStr">
+      <c r="A8" s="11" t="n">
+        <v>46172</v>
+      </c>
+      <c r="B8" t="inlineStr">
         <is>
           <t>小6</t>
         </is>
       </c>
-      <c r="C9" s="1" t="n">
-        <v>50</v>
-      </c>
-      <c r="D9" s="1" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E9" s="10" t="n">
-        <v>45.97</v>
-      </c>
-      <c r="F9" s="1" t="inlineStr">
+      <c r="C8" t="n">
+        <v>200</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>193.81</v>
+      </c>
+      <c r="F8" t="inlineStr">
         <is>
           <t>菰野スイミング</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="4">
-    <dataValidation sqref="D2:D181" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
-      <formula1>$P$2:$P$3</formula1>
-    </dataValidation>
-    <dataValidation sqref="F2:F181" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
-      <formula1>$P$5:$P$6</formula1>
-    </dataValidation>
-    <dataValidation sqref="K2:K132" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
-      <formula1>$N$3:$N$3</formula1>
-    </dataValidation>
-    <dataValidation sqref="M2:M181" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
-      <formula1>$O$5:$O$6</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
@@ -786,7 +688,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -823,35 +725,33 @@
     </row>
     <row r="2">
       <c r="A2" s="11" t="n">
-        <v>45710</v>
+        <v>45788</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>小4</t>
+          <t>小5</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
           <t>短水路</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>4'43"09</t>
-        </is>
+      <c r="E2" t="n">
+        <v>47.91</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>菰野スイミング</t>
+          <t>鈴鹿</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="11" t="n">
-        <v>45808</v>
+        <v>45816</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -859,27 +759,25 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>4'02"71</t>
-        </is>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>47.54</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>菰野スイミング</t>
+          <t>鈴鹿</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="11" t="n">
-        <v>45899</v>
+        <v>45823</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -887,27 +785,25 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
           <t>短水路</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>3'37"53</t>
-        </is>
+      <c r="E4" t="n">
+        <v>44.48</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>菰野スイミング</t>
+          <t>鈴鹿</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="11" t="n">
-        <v>45991</v>
+        <v>45844</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -915,27 +811,25 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>3'21"34</t>
-        </is>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>44.39</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>菰野スイミング</t>
+          <t>鈴鹿</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="11" t="n">
-        <v>46081</v>
+        <v>45942</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -943,31 +837,29 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>3'14"47</t>
-        </is>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>40.39</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>菰野スイミング</t>
+          <t>鈴鹿</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="11" t="n">
-        <v>46145</v>
+        <v>45955</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>小6</t>
+          <t>小5</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -979,37 +871,167 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>173.24</v>
+        <v>40.5</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>菰野スイミング</t>
+          <t>鈴鹿</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="11" t="n">
-        <v>46172</v>
+        <v>46033</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
+          <t>小5</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>50</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>39.07</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="11" t="n">
+        <v>46053</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>小5</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>50</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>38.24</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="11" t="n">
+        <v>46074</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>小5</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>50</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>37.73</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="11" t="n">
+        <v>46130</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
           <t>小6</t>
         </is>
       </c>
-      <c r="C8" t="n">
-        <v>200</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>193.81</v>
-      </c>
-      <c r="F8" t="inlineStr">
+      <c r="C11" t="n">
+        <v>50</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>40.28</v>
+      </c>
+      <c r="F11" t="inlineStr">
         <is>
           <t>菰野スイミング</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="11" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>小6</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>50</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>36.55</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="11" t="n">
+        <v>46207</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>小6</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>50</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>36.89</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
         </is>
       </c>
     </row>
@@ -1024,7 +1046,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1077,7 +1099,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>47.91</v>
+        <v>58.87</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -1087,7 +1109,7 @@
     </row>
     <row r="3">
       <c r="A3" s="11" t="n">
-        <v>45816</v>
+        <v>45815</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -1103,7 +1125,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>47.54</v>
+        <v>55.01</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1113,7 +1135,7 @@
     </row>
     <row r="4">
       <c r="A4" s="11" t="n">
-        <v>45823</v>
+        <v>45844</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -1125,11 +1147,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>短水路</t>
+          <t>長水路</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>44.48</v>
+        <v>52.08</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1139,7 +1161,7 @@
     </row>
     <row r="5">
       <c r="A5" s="11" t="n">
-        <v>45844</v>
+        <v>45942</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -1155,7 +1177,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>44.39</v>
+        <v>52.97</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1165,7 +1187,7 @@
     </row>
     <row r="6">
       <c r="A6" s="11" t="n">
-        <v>45942</v>
+        <v>45955</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -1177,11 +1199,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>長水路</t>
+          <t>短水路</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>40.39</v>
+        <v>49.74</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1191,7 +1213,7 @@
     </row>
     <row r="7">
       <c r="A7" s="11" t="n">
-        <v>45955</v>
+        <v>45984</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -1203,11 +1225,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>短水路</t>
+          <t>長水路</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>40.5</v>
+        <v>49.06</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1217,7 +1239,7 @@
     </row>
     <row r="8">
       <c r="A8" s="11" t="n">
-        <v>46033</v>
+        <v>45984</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -1225,15 +1247,17 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>39.07</v>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>1'41"11</t>
+        </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1243,7 +1267,7 @@
     </row>
     <row r="9">
       <c r="A9" s="11" t="n">
-        <v>46053</v>
+        <v>46033</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1259,7 +1283,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>38.24</v>
+        <v>47.55</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1269,7 +1293,7 @@
     </row>
     <row r="10">
       <c r="A10" s="11" t="n">
-        <v>46074</v>
+        <v>46053</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -1281,11 +1305,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>長水路</t>
+          <t>短水路</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>37.73</v>
+        <v>46.9</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1295,11 +1319,11 @@
     </row>
     <row r="11">
       <c r="A11" s="11" t="n">
-        <v>46130</v>
+        <v>46075</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>小6</t>
+          <t>小5</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1307,21 +1331,21 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>短水路</t>
+          <t>長水路</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>40.28</v>
+        <v>47.42</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>菰野スイミング</t>
+          <t>鈴鹿</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="11" t="n">
-        <v>46152</v>
+        <v>46130</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -1337,35 +1361,217 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>36.55</v>
+        <v>47.95</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>鈴鹿</t>
+          <t>菰野スイミング</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="11" t="n">
+        <v>46053</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>小5</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>100</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>99.48999999999999</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="11" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>小6</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>50</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>45.36</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="11" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>小6</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>100</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>95.04000000000001</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="11" t="n">
+        <v>46179</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>小6</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>100</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100.1</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="11" t="n">
+        <v>46180</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>小6</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>50</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>46.87</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="11" t="n">
+        <v>46187</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>小6</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>50</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>45.11</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="11" t="n">
+        <v>46187</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>小6</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>100</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>96.61</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="11" t="n">
         <v>46207</v>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>小6</t>
         </is>
       </c>
-      <c r="C13" t="n">
-        <v>50</v>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>長水路</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>36.89</v>
-      </c>
-      <c r="F13" t="inlineStr">
+      <c r="C20" t="n">
+        <v>50</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>45.87</v>
+      </c>
+      <c r="F20" t="inlineStr">
         <is>
           <t>鈴鹿</t>
         </is>
@@ -1382,7 +1588,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1419,7 +1625,7 @@
     </row>
     <row r="2">
       <c r="A2" s="11" t="n">
-        <v>45788</v>
+        <v>45823</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -1435,7 +1641,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>58.87</v>
+        <v>54.97</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -1445,7 +1651,7 @@
     </row>
     <row r="3">
       <c r="A3" s="11" t="n">
-        <v>45815</v>
+        <v>45956</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -1461,7 +1667,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>55.01</v>
+        <v>48.27</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1471,7 +1677,7 @@
     </row>
     <row r="4">
       <c r="A4" s="11" t="n">
-        <v>45844</v>
+        <v>46033</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -1483,11 +1689,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>長水路</t>
+          <t>短水路</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>52.08</v>
+        <v>44.97</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1497,7 +1703,7 @@
     </row>
     <row r="5">
       <c r="A5" s="11" t="n">
-        <v>45942</v>
+        <v>46075</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -1513,7 +1719,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>52.97</v>
+        <v>44.65</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1523,11 +1729,11 @@
     </row>
     <row r="6">
       <c r="A6" s="11" t="n">
-        <v>45955</v>
+        <v>46130</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>小5</t>
+          <t>小6</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -1539,21 +1745,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>49.74</v>
+        <v>47.17</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>鈴鹿</t>
+          <t>菰野スイミング</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="11" t="n">
-        <v>45984</v>
+        <v>46187</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>小5</t>
+          <t>小6</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -1561,11 +1767,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>長水路</t>
+          <t>短水路</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>49.06</v>
+        <v>42.92</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1575,339 +1781,25 @@
     </row>
     <row r="8">
       <c r="A8" s="11" t="n">
-        <v>45984</v>
+        <v>46208</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>小5</t>
+          <t>小6</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
           <t>長水路</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>1'41"11</t>
-        </is>
+      <c r="E8" t="n">
+        <v>44.13</v>
       </c>
       <c r="F8" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="11" t="n">
-        <v>46033</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>小5</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>50</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>47.55</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="11" t="n">
-        <v>46053</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>小5</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>50</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>46.9</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="11" t="n">
-        <v>46075</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>小5</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>50</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>長水路</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>47.42</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="11" t="n">
-        <v>46130</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>小6</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>50</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>47.95</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>菰野スイミング</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="11" t="n">
-        <v>46053</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>小5</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>100</v>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>99.48999999999999</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="11" t="n">
-        <v>46152</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>小6</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>50</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>45.36</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="11" t="n">
-        <v>46152</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>小6</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>100</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>95.04000000000001</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="11" t="n">
-        <v>46179</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>小6</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>100</v>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>長水路</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>100.1</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="11" t="n">
-        <v>46180</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>小6</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>50</v>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>長水路</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>46.87</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="11" t="n">
-        <v>46187</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>小6</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>50</v>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>45.11</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="11" t="n">
-        <v>46187</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>小6</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>100</v>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>96.61</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="11" t="n">
-        <v>46207</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>小6</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>50</v>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>長水路</t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>45.87</v>
-      </c>
-      <c r="F20" t="inlineStr">
         <is>
           <t>鈴鹿</t>
         </is>
@@ -1924,7 +1816,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1961,7 +1853,7 @@
     </row>
     <row r="2">
       <c r="A2" s="11" t="n">
-        <v>45823</v>
+        <v>45788</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -1987,7 +1879,7 @@
     </row>
     <row r="3">
       <c r="A3" s="11" t="n">
-        <v>45956</v>
+        <v>45815</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -2003,7 +1895,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>48.27</v>
+        <v>52.8</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -2013,7 +1905,7 @@
     </row>
     <row r="4">
       <c r="A4" s="11" t="n">
-        <v>46033</v>
+        <v>45823</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -2029,7 +1921,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>44.97</v>
+        <v>51.07</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -2039,7 +1931,7 @@
     </row>
     <row r="5">
       <c r="A5" s="11" t="n">
-        <v>46075</v>
+        <v>45844</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -2055,7 +1947,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>44.65</v>
+        <v>50.06</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -2065,11 +1957,11 @@
     </row>
     <row r="6">
       <c r="A6" s="11" t="n">
-        <v>46130</v>
+        <v>45956</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>小6</t>
+          <t>小5</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -2081,21 +1973,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>47.17</v>
+        <v>46.12</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>菰野スイミング</t>
+          <t>鈴鹿</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="11" t="n">
-        <v>46187</v>
+        <v>45984</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>小6</t>
+          <t>小5</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -2103,11 +1995,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>短水路</t>
+          <t>長水路</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>42.92</v>
+        <v>45.67</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -2117,25 +2009,77 @@
     </row>
     <row r="8">
       <c r="A8" s="11" t="n">
+        <v>46075</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>小5</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>50</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>44.84</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="11" t="n">
+        <v>46130</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>小6</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>50</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>45.97</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>菰野スイミング</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="11" t="n">
         <v>46208</v>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>小6</t>
         </is>
       </c>
-      <c r="C8" t="n">
-        <v>50</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>長水路</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>44.13</v>
-      </c>
-      <c r="F8" t="inlineStr">
+      <c r="C10" t="n">
+        <v>50</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>41.68</v>
+      </c>
+      <c r="F10" t="inlineStr">
         <is>
           <t>鈴鹿</t>
         </is>
